--- a/spec/fixtures/batch_submission_manifest_object_test.xlsx
+++ b/spec/fixtures/batch_submission_manifest_object_test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11010"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10111"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/smc101/vagrant/morphosource-vagrant/scripts/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/smc101/vagrant/morphosource-vagrant/MorphoSource_SF/spec/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71838628-DD3C-8B4B-AF38-E07F72E7D0F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55242DF4-4ACD-474E-B4B0-23B1A332E8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="278">
   <si>
     <t>Field Section</t>
   </si>
@@ -188,12 +188,6 @@
   </si>
   <si>
     <t>Shading correction</t>
-  </si>
-  <si>
-    <t>Filter material</t>
-  </si>
-  <si>
-    <t>Filter thickness</t>
   </si>
   <si>
     <t>Frame averaging</t>
@@ -534,15 +528,6 @@
 Gynandromorph: Gynandromorph</t>
   </si>
   <si>
-    <t>Molybdenum: Molybdenum
-Aluminum: Aluminum
-Copper: Copper
-Rhodium: Rhodium
-Niobium: Niobium
-Europium: Europium
-Lead: Lead</t>
-  </si>
-  <si>
     <t>Reflection: Reflection
 Transmission: Transmission</t>
   </si>
@@ -733,12 +718,6 @@
     <t>imaging_event.ct.shading_correction</t>
   </si>
   <si>
-    <t>imaging_event.ct.filter_material</t>
-  </si>
-  <si>
-    <t>imaging_event.ct.filter_thickness</t>
-  </si>
-  <si>
     <t>imaging_event.ct.frame_averaging</t>
   </si>
   <si>
@@ -907,9 +886,6 @@
     <t>url</t>
   </si>
   <si>
-    <t>Molybdenum</t>
-  </si>
-  <si>
     <t>Scolomastax</t>
   </si>
   <si>
@@ -938,6 +914,12 @@
   </si>
   <si>
     <t>bbb</t>
+  </si>
+  <si>
+    <t>Filter</t>
+  </si>
+  <si>
+    <t>imaging_event.ct.ie_filter</t>
   </si>
 </sst>
 </file>
@@ -1376,7 +1358,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06ED7EC9-286B-1D49-A57D-A989376D77CC}">
-  <dimension ref="A1:CI10"/>
+  <dimension ref="A1:CH10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="28.6640625" customWidth="1"/>
@@ -1384,7 +1366,7 @@
     <col min="7" max="7" width="21.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:87" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:86" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1615,13 +1597,13 @@
         <v>11</v>
       </c>
       <c r="BZ1" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CA1" s="6" t="s">
         <v>12</v>
       </c>
       <c r="CB1" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CC1" s="6" t="s">
         <v>13</v>
@@ -1629,8 +1611,8 @@
       <c r="CD1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="CE1" s="6" t="s">
-        <v>13</v>
+      <c r="CE1" s="24" t="s">
+        <v>14</v>
       </c>
       <c r="CF1" s="24" t="s">
         <v>14</v>
@@ -1641,11 +1623,8 @@
       <c r="CH1" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="CI1" s="24" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="2" spans="1:87" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:86" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>15</v>
       </c>
@@ -1790,165 +1769,162 @@
         <v>55</v>
       </c>
       <c r="BD2" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="BE2" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="BE2" s="6" t="s">
+      <c r="BF2" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="BF2" s="6" t="s">
+      <c r="BG2" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="BG2" s="6" t="s">
+      <c r="BH2" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="BH2" s="6" t="s">
+      <c r="BI2" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="BI2" s="6" t="s">
+      <c r="BJ2" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="BJ2" s="6" t="s">
+      <c r="BK2" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="BK2" s="6" t="s">
+      <c r="BL2" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="BL2" s="6" t="s">
+      <c r="BM2" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="BM2" s="6" t="s">
+      <c r="BN2" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="BN2" s="6" t="s">
+      <c r="BO2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="BO2" s="6" t="s">
+      <c r="BP2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="BP2" s="6" t="s">
+      <c r="BQ2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="BQ2" s="6" t="s">
+      <c r="BR2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="BR2" s="6" t="s">
+      <c r="BS2" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="BS2" s="6" t="s">
+      <c r="BT2" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="BT2" s="6" t="s">
+      <c r="BU2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="BU2" s="6" t="s">
+      <c r="BV2" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="BV2" s="6" t="s">
+      <c r="BW2" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="BW2" s="6" t="s">
+      <c r="BX2" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="BX2" s="6" t="s">
+      <c r="BY2" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="BY2" s="6" t="s">
+      <c r="BZ2" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="BZ2" s="6" t="s">
+      <c r="CA2" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="CA2" s="6" t="s">
+      <c r="CB2" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="CB2" s="6" t="s">
+      <c r="CC2" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="CC2" s="6" t="s">
+      <c r="CD2" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="CD2" s="6" t="s">
+      <c r="CE2" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="CF2" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="CG2" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="CH2" s="24" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:86" ht="139.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="CE2" s="6" t="s">
+      <c r="B3" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="CF2" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="CG2" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="CH2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="CI2" s="24" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:87" ht="139.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="7" t="s">
+      <c r="C3" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="D3" s="10" t="s">
         <v>85</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>87</v>
       </c>
       <c r="E3" s="9"/>
       <c r="F3" s="10"/>
       <c r="G3" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H3" s="10"/>
       <c r="I3" s="11"/>
       <c r="J3" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K3" s="12"/>
       <c r="L3" s="12"/>
       <c r="M3" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="O3" s="13" t="s">
         <v>90</v>
-      </c>
-      <c r="N3" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="O3" s="13" t="s">
-        <v>92</v>
       </c>
       <c r="P3" s="14"/>
       <c r="Q3" s="14"/>
       <c r="R3" s="13" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="S3" s="13" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="T3" s="2"/>
       <c r="U3" s="13" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="V3" s="13"/>
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
       <c r="Y3" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="Z3" s="15" t="s">
+      <c r="AB3" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="AA3" s="15" t="s">
+      <c r="AC3" s="13" t="s">
         <v>98</v>
-      </c>
-      <c r="AB3" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="AC3" s="13" t="s">
-        <v>100</v>
       </c>
       <c r="AD3" s="14"/>
       <c r="AE3" s="2"/>
@@ -1965,7 +1941,7 @@
       <c r="AP3" s="16"/>
       <c r="AQ3" s="16"/>
       <c r="AR3" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AS3" s="17"/>
       <c r="AT3" s="17"/>
@@ -1973,141 +1949,138 @@
       <c r="AV3" s="6"/>
       <c r="AW3" s="6"/>
       <c r="AX3" s="18" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AY3" s="18"/>
       <c r="AZ3" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="BA3" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="BB3" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="BA3" s="19" t="s">
+      <c r="BC3" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="BB3" s="19" t="s">
+      <c r="BD3" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="BC3" s="19" t="s">
+      <c r="BE3" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="BD3" s="19" t="s">
+      <c r="BF3" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="BE3" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="BF3" s="19" t="s">
+      <c r="BG3" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="BG3" s="19" t="s">
+      <c r="BH3" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="BH3" s="19" t="s">
+      <c r="BI3" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="BI3" s="19" t="s">
+      <c r="BJ3" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="BJ3" s="19" t="s">
+      <c r="BK3" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="BK3" s="19" t="s">
+      <c r="BL3" s="18"/>
+      <c r="BM3" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="BL3" s="18" t="s">
+      <c r="BN3" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="BM3" s="18"/>
-      <c r="BN3" s="18" t="s">
+      <c r="BO3" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="BO3" s="20" t="s">
+      <c r="BP3" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="BP3" s="20" t="s">
+      <c r="BQ3" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="BQ3" s="20" t="s">
+      <c r="BR3" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="BR3" s="20" t="s">
+      <c r="BS3" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="BS3" s="18" t="s">
+      <c r="BT3" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="BT3" s="18" t="s">
+      <c r="BU3" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="BU3" s="18" t="s">
+      <c r="BV3" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="BV3" s="18" t="s">
+      <c r="BW3" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="BW3" s="18" t="s">
+      <c r="BX3" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="BX3" s="18" t="s">
+      <c r="BY3" s="19"/>
+      <c r="BZ3" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="BY3" s="18" t="s">
+      <c r="CA3" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="BZ3" s="19"/>
-      <c r="CA3" s="18" t="s">
+      <c r="CB3" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="CB3" s="18" t="s">
+      <c r="CC3" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="CD3" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="CC3" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="CD3" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="CE3" s="19" t="s">
-        <v>130</v>
-      </c>
+      <c r="CE3" s="24"/>
       <c r="CF3" s="24"/>
       <c r="CG3" s="24"/>
       <c r="CH3" s="24"/>
-      <c r="CI3" s="24"/>
     </row>
-    <row r="4" spans="1:87" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:86" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>131</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>133</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
       <c r="K4" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="P4" s="14"/>
       <c r="Q4" s="14"/>
@@ -2119,13 +2092,13 @@
       <c r="W4" s="2"/>
       <c r="X4" s="2"/>
       <c r="Y4" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="Z4" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AA4" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AB4" s="2"/>
       <c r="AC4" s="2"/>
@@ -2182,289 +2155,285 @@
       <c r="CB4" s="6"/>
       <c r="CC4" s="6"/>
       <c r="CD4" s="6"/>
-      <c r="CE4" s="6"/>
+      <c r="CE4" s="24"/>
       <c r="CF4" s="24"/>
       <c r="CG4" s="24"/>
       <c r="CH4" s="24"/>
-      <c r="CI4" s="24"/>
     </row>
-    <row r="5" spans="1:87" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:86" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="F5" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="M5" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="N5" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="W5" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="X5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA5" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AB5" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AC5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AD5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AE5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF5" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="AG5" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="AH5" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="AI5" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="AJ5" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="AK5" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="AL5" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="K5" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="L5" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="M5" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="N5" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q5" s="2" t="s">
+      <c r="AM5" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="AN5" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="AO5" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="AP5" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="AQ5" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="AR5" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="AS5" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="AT5" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="AU5" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="AV5" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="AW5" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="AX5" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="AY5" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="AZ5" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="R5" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="W5" s="2" t="s">
+      <c r="BA5" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="X5" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y5" s="2" t="s">
+      <c r="BB5" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="BC5" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="BD5" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="BE5" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="BF5" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="BG5" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="BH5" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="BI5" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="BJ5" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="BK5" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BL5" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="BM5" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="BN5" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="Z5" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="AA5" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="AB5" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="AC5" s="2" t="s">
+      <c r="BO5" s="23" t="s">
         <v>139</v>
-      </c>
-      <c r="AD5" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AE5" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AF5" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="AG5" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="AH5" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="AI5" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="AJ5" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="AK5" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="AL5" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="AM5" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="AN5" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="AO5" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="AP5" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="AQ5" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="AR5" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="AS5" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="AT5" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="AU5" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="AV5" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="AW5" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="AX5" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="AY5" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="AZ5" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="BA5" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="BB5" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="BC5" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="BD5" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="BE5" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="BF5" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="BG5" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="BH5" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="BI5" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="BJ5" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="BK5" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="BL5" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="BM5" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="BN5" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="BO5" s="23" t="s">
-        <v>143</v>
       </c>
       <c r="BP5" s="23" t="s">
         <v>141</v>
       </c>
       <c r="BQ5" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="BR5" s="23" t="s">
-        <v>141</v>
+        <v>139</v>
+      </c>
+      <c r="BR5" s="6" t="s">
+        <v>137</v>
       </c>
       <c r="BS5" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BT5" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BU5" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BV5" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="BT5" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="BU5" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="BV5" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="BW5" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BX5" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="BY5" s="6" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="BZ5" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="CA5" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="CB5" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="CC5" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="CD5" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="CE5" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
+      </c>
+      <c r="CE5" s="24" t="s">
+        <v>136</v>
       </c>
       <c r="CF5" s="24" t="s">
         <v>138</v>
       </c>
       <c r="CG5" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="CH5" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="CI5" s="24" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
-    <row r="6" spans="1:87" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:86" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
@@ -2477,7 +2446,7 @@
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
@@ -2491,13 +2460,13 @@
       <c r="AA6" s="2"/>
       <c r="AB6" s="2"/>
       <c r="AC6" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="AD6" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="AE6" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="AD6" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="AE6" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="AF6" s="21"/>
       <c r="AG6" s="21"/>
@@ -2511,7 +2480,7 @@
       <c r="AO6" s="21"/>
       <c r="AP6" s="21"/>
       <c r="AQ6" s="21" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AR6" s="21"/>
       <c r="AS6" s="3"/>
@@ -2525,9 +2494,7 @@
       <c r="BA6" s="6"/>
       <c r="BB6" s="6"/>
       <c r="BC6" s="6"/>
-      <c r="BD6" s="6" t="s">
-        <v>153</v>
-      </c>
+      <c r="BD6" s="6"/>
       <c r="BE6" s="6"/>
       <c r="BF6" s="6"/>
       <c r="BG6" s="6"/>
@@ -2535,349 +2502,345 @@
       <c r="BI6" s="6"/>
       <c r="BJ6" s="6"/>
       <c r="BK6" s="6"/>
-      <c r="BL6" s="6"/>
+      <c r="BL6" s="6" t="s">
+        <v>151</v>
+      </c>
       <c r="BM6" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="BN6" s="6" t="s">
-        <v>155</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="BN6" s="6"/>
       <c r="BO6" s="6"/>
       <c r="BP6" s="6"/>
       <c r="BQ6" s="6"/>
-      <c r="BR6" s="6"/>
-      <c r="BS6" s="6" t="s">
-        <v>156</v>
-      </c>
+      <c r="BR6" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="BS6" s="6"/>
       <c r="BT6" s="6"/>
       <c r="BU6" s="6"/>
       <c r="BV6" s="6"/>
       <c r="BW6" s="6"/>
       <c r="BX6" s="6"/>
-      <c r="BY6" s="6"/>
+      <c r="BY6" s="6" t="s">
+        <v>154</v>
+      </c>
       <c r="BZ6" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="CA6" s="6" t="s">
-        <v>158</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="CA6" s="6"/>
       <c r="CB6" s="6"/>
       <c r="CC6" s="6"/>
-      <c r="CD6" s="6"/>
-      <c r="CE6" s="6" t="s">
-        <v>159</v>
-      </c>
+      <c r="CD6" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="CE6" s="24"/>
       <c r="CF6" s="24"/>
       <c r="CG6" s="24"/>
       <c r="CH6" s="24"/>
-      <c r="CI6" s="24"/>
     </row>
-    <row r="7" spans="1:87" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:86" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="44" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B7" s="45" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="G7" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="H7" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="I7" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="J7" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="K7" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="I7" s="25" t="s">
+      <c r="L7" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="J7" s="12" t="s">
+      <c r="M7" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="N7" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="O7" s="26" t="s">
         <v>169</v>
       </c>
-      <c r="M7" s="12" t="s">
+      <c r="P7" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="N7" s="12" t="s">
+      <c r="Q7" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="O7" s="26" t="s">
+      <c r="R7" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="P7" s="26" t="s">
+      <c r="S7" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="Q7" s="26" t="s">
+      <c r="T7" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="U7" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="V7" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="W7" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="U7" s="2" t="s">
+      <c r="X7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="Y7" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="Z7" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="X7" s="2" t="s">
+      <c r="AA7" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="Y7" s="26" t="s">
+      <c r="AB7" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="Z7" s="26" t="s">
+      <c r="AC7" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="AA7" s="26" t="s">
+      <c r="AD7" s="26" t="s">
         <v>184</v>
       </c>
-      <c r="AB7" s="2" t="s">
+      <c r="AE7" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="AC7" s="2" t="s">
+      <c r="AF7" s="27" t="s">
         <v>186</v>
       </c>
-      <c r="AD7" s="26" t="s">
+      <c r="AG7" s="27" t="s">
         <v>187</v>
       </c>
-      <c r="AE7" s="2" t="s">
+      <c r="AH7" s="27" t="s">
         <v>188</v>
       </c>
-      <c r="AF7" s="27" t="s">
+      <c r="AI7" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="AG7" s="27" t="s">
+      <c r="AJ7" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="AH7" s="27" t="s">
+      <c r="AK7" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="AI7" s="27" t="s">
+      <c r="AL7" s="27" t="s">
         <v>192</v>
       </c>
-      <c r="AJ7" s="27" t="s">
+      <c r="AM7" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="AK7" s="27" t="s">
+      <c r="AN7" s="27" t="s">
         <v>194</v>
       </c>
-      <c r="AL7" s="27" t="s">
+      <c r="AO7" s="27" t="s">
         <v>195</v>
       </c>
-      <c r="AM7" s="27" t="s">
+      <c r="AP7" s="27" t="s">
         <v>196</v>
       </c>
-      <c r="AN7" s="27" t="s">
+      <c r="AQ7" s="27" t="s">
         <v>197</v>
       </c>
-      <c r="AO7" s="27" t="s">
+      <c r="AR7" s="27" t="s">
         <v>198</v>
       </c>
-      <c r="AP7" s="27" t="s">
+      <c r="AS7" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="AQ7" s="27" t="s">
+      <c r="AT7" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="AR7" s="27" t="s">
+      <c r="AU7" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="AS7" s="29" t="s">
+      <c r="AV7" s="29" t="s">
         <v>202</v>
       </c>
-      <c r="AT7" s="29" t="s">
+      <c r="AW7" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="AU7" s="29" t="s">
+      <c r="AX7" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="AV7" s="29" t="s">
+      <c r="AY7" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="AW7" s="29" t="s">
+      <c r="AZ7" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="AX7" s="6" t="s">
+      <c r="BA7" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="AY7" s="6" t="s">
+      <c r="BB7" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="AZ7" s="29" t="s">
+      <c r="BC7" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="BA7" s="29" t="s">
+      <c r="BD7" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="BE7" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="BB7" s="29" t="s">
+      <c r="BF7" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="BC7" s="29" t="s">
+      <c r="BG7" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="BD7" s="6" t="s">
+      <c r="BH7" s="29" t="s">
         <v>213</v>
       </c>
-      <c r="BE7" s="6" t="s">
+      <c r="BI7" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="BF7" s="29" t="s">
+      <c r="BJ7" s="29" t="s">
         <v>215</v>
       </c>
-      <c r="BG7" s="29" t="s">
+      <c r="BK7" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="BH7" s="29" t="s">
+      <c r="BL7" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="BI7" s="29" t="s">
+      <c r="BM7" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="BJ7" s="29" t="s">
+      <c r="BN7" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="BK7" s="29" t="s">
+      <c r="BO7" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="BL7" s="6" t="s">
+      <c r="BP7" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="BM7" s="6" t="s">
+      <c r="BQ7" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="BN7" s="6" t="s">
+      <c r="BR7" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="BO7" s="6" t="s">
+      <c r="BS7" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="BP7" s="6" t="s">
+      <c r="BT7" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="BQ7" s="6" t="s">
+      <c r="BU7" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="BR7" s="6" t="s">
+      <c r="BV7" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="BS7" s="6" t="s">
+      <c r="BW7" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="BT7" s="6" t="s">
+      <c r="BX7" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="BU7" s="6" t="s">
+      <c r="BY7" s="28" t="s">
         <v>230</v>
       </c>
-      <c r="BV7" s="6" t="s">
+      <c r="BZ7" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="BW7" s="6" t="s">
+      <c r="CA7" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="BX7" s="6" t="s">
+      <c r="CB7" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="BY7" s="6" t="s">
+      <c r="CC7" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="BZ7" s="28" t="s">
+      <c r="CD7" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="CA7" s="6" t="s">
+      <c r="CE7" s="29" t="s">
         <v>236</v>
       </c>
-      <c r="CB7" s="6" t="s">
+      <c r="CF7" s="29" t="s">
         <v>237</v>
       </c>
-      <c r="CC7" s="6" t="s">
+      <c r="CG7" s="29" t="s">
         <v>238</v>
       </c>
-      <c r="CD7" s="6" t="s">
+      <c r="CH7" s="29" t="s">
         <v>239</v>
       </c>
-      <c r="CE7" s="6" t="s">
+    </row>
+    <row r="8" spans="1:86" ht="17" x14ac:dyDescent="0.2">
+      <c r="A8" s="44" t="s">
+        <v>271</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>272</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>248</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>264</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>249</v>
+      </c>
+      <c r="F8" s="29" t="s">
         <v>240</v>
-      </c>
-      <c r="CF7" s="29" t="s">
-        <v>241</v>
-      </c>
-      <c r="CG7" s="29" t="s">
-        <v>242</v>
-      </c>
-      <c r="CH7" s="29" t="s">
-        <v>243</v>
-      </c>
-      <c r="CI7" s="29" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="8" spans="1:87" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="44" t="s">
-        <v>277</v>
-      </c>
-      <c r="B8" s="46" t="s">
-        <v>278</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>253</v>
-      </c>
-      <c r="D8" s="41" t="s">
-        <v>269</v>
-      </c>
-      <c r="E8" s="29" t="s">
-        <v>254</v>
-      </c>
-      <c r="F8" s="29" t="s">
-        <v>245</v>
       </c>
       <c r="H8" s="43"/>
       <c r="I8" s="34"/>
       <c r="J8" s="29"/>
       <c r="K8" s="29" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="L8" s="29"/>
       <c r="M8" s="35" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="N8" s="35" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="O8" s="29" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="P8" s="29" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="Q8" s="35" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="R8" s="29" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="S8" s="30"/>
       <c r="T8" s="30"/>
@@ -2887,7 +2850,7 @@
         <v>44177</v>
       </c>
       <c r="X8" s="42" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="Y8" s="30">
         <v>2.169024E-2</v>
@@ -2902,26 +2865,26 @@
         <v>8</v>
       </c>
       <c r="AC8" s="35" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AD8" s="29" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="AE8" s="35"/>
       <c r="AF8" s="35" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="AG8" s="35" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="AH8" s="36">
         <v>44177</v>
       </c>
       <c r="AI8" s="35" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="AJ8" s="35" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="AK8" s="29">
         <v>88</v>
@@ -2930,38 +2893,38 @@
         <v>88</v>
       </c>
       <c r="AM8" s="35" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="AN8" s="35" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="AO8" s="35" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="AP8" s="35" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="AQ8" s="37" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="AR8" s="29" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="AS8" s="29" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="AT8" s="29" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="AU8" s="29"/>
       <c r="AV8" s="35" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AW8" s="29" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="AX8" s="39" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="AY8" s="40">
         <v>44500</v>
@@ -2970,49 +2933,49 @@
         <v>0.200098</v>
       </c>
       <c r="BA8" s="29" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="BB8" s="29" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="BC8" s="29" t="s">
-        <v>250</v>
-      </c>
-      <c r="BD8" t="s">
-        <v>271</v>
-      </c>
-      <c r="BE8">
+        <v>245</v>
+      </c>
+      <c r="BD8">
         <v>888</v>
       </c>
+      <c r="BE8" s="30">
+        <v>3</v>
+      </c>
       <c r="BF8" s="30">
-        <v>3</v>
+        <v>1680</v>
       </c>
       <c r="BG8" s="30">
-        <v>1680</v>
+        <v>70</v>
       </c>
       <c r="BH8" s="30">
-        <v>70</v>
+        <v>1.4E-2</v>
       </c>
       <c r="BI8" s="30">
-        <v>1.4E-2</v>
-      </c>
-      <c r="BJ8" s="30">
         <v>200</v>
       </c>
+      <c r="BJ8" s="35" t="s">
+        <v>259</v>
+      </c>
       <c r="BK8" s="35" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="BL8" s="35" t="s">
-        <v>264</v>
-      </c>
-      <c r="BM8" s="35" t="s">
-        <v>262</v>
-      </c>
-      <c r="BN8" s="29" t="s">
-        <v>263</v>
-      </c>
-      <c r="BO8" s="29">
+        <v>257</v>
+      </c>
+      <c r="BM8" s="29" t="s">
+        <v>258</v>
+      </c>
+      <c r="BN8" s="29">
         <v>88</v>
+      </c>
+      <c r="BO8">
+        <v>1</v>
       </c>
       <c r="BP8">
         <v>1</v>
@@ -3020,68 +2983,65 @@
       <c r="BQ8">
         <v>1</v>
       </c>
-      <c r="BR8">
-        <v>1</v>
+      <c r="BR8" t="s">
+        <v>260</v>
       </c>
       <c r="BS8" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="BT8" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="BU8" t="s">
-        <v>264</v>
-      </c>
-      <c r="BV8" t="s">
-        <v>264</v>
-      </c>
-      <c r="BW8">
+        <v>259</v>
+      </c>
+      <c r="BV8">
         <v>88</v>
       </c>
+      <c r="BW8" t="s">
+        <v>245</v>
+      </c>
       <c r="BX8" t="s">
-        <v>250</v>
-      </c>
-      <c r="BY8" t="s">
-        <v>250</v>
-      </c>
-      <c r="BZ8" s="29" t="s">
-        <v>266</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="BY8" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="BZ8" s="35"/>
       <c r="CA8" s="35"/>
       <c r="CB8" s="35"/>
       <c r="CC8" s="35"/>
       <c r="CD8" s="35"/>
-      <c r="CE8" s="35"/>
-      <c r="CF8" s="29" t="s">
-        <v>251</v>
-      </c>
-      <c r="CG8" s="36">
+      <c r="CE8" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="CF8" s="36">
         <v>44500</v>
       </c>
+      <c r="CG8" s="35" t="s">
+        <v>262</v>
+      </c>
       <c r="CH8" s="35" t="s">
-        <v>267</v>
-      </c>
-      <c r="CI8" s="35" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
-    <row r="9" spans="1:87" ht="17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:86" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="33"/>
       <c r="B9" s="38"/>
       <c r="C9" s="35" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="D9" s="41" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="H9" s="43"/>
       <c r="I9" s="34"/>
@@ -3089,22 +3049,22 @@
       <c r="K9" s="29"/>
       <c r="L9" s="29"/>
       <c r="M9" s="35" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="N9" s="35" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="O9" s="29" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="P9" s="29" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="Q9" s="35" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="R9" s="29" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="S9" s="30"/>
       <c r="T9" s="30"/>
@@ -3127,10 +3087,10 @@
         <v>8</v>
       </c>
       <c r="AC9" s="35" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AD9" s="29" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="AE9" s="35"/>
       <c r="AF9" s="29"/>
@@ -3144,29 +3104,29 @@
       <c r="AN9" s="29"/>
       <c r="AO9" s="29"/>
       <c r="AP9" s="35" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="AQ9" s="37" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="AR9" s="29" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="AS9" s="29" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="AT9" s="29" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="AU9" s="29"/>
       <c r="AV9" s="35" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AW9" s="29" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="AX9" s="39" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="AY9" s="40">
         <v>44501</v>
@@ -3175,130 +3135,127 @@
         <v>0.200098</v>
       </c>
       <c r="BA9" s="29" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="BB9" s="29" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="BC9" s="29" t="s">
-        <v>250</v>
-      </c>
-      <c r="BD9" t="s">
-        <v>271</v>
-      </c>
-      <c r="BE9">
+        <v>245</v>
+      </c>
+      <c r="BD9">
         <v>888</v>
       </c>
+      <c r="BE9" s="30">
+        <v>3</v>
+      </c>
       <c r="BF9" s="30">
-        <v>3</v>
+        <v>1680</v>
       </c>
       <c r="BG9" s="30">
-        <v>1680</v>
+        <v>70</v>
       </c>
       <c r="BH9" s="30">
-        <v>70</v>
+        <v>1.54E-2</v>
       </c>
       <c r="BI9" s="30">
-        <v>1.54E-2</v>
-      </c>
-      <c r="BJ9" s="30">
         <v>220</v>
       </c>
+      <c r="BJ9" s="35" t="s">
+        <v>259</v>
+      </c>
       <c r="BK9" s="35" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="BL9" s="35" t="s">
-        <v>264</v>
-      </c>
-      <c r="BM9" s="35" t="s">
-        <v>262</v>
-      </c>
-      <c r="BN9" s="29" t="s">
-        <v>263</v>
-      </c>
-      <c r="BO9" s="29">
+        <v>257</v>
+      </c>
+      <c r="BM9" s="29" t="s">
+        <v>258</v>
+      </c>
+      <c r="BN9" s="29">
         <v>89</v>
       </c>
+      <c r="BR9" t="s">
+        <v>260</v>
+      </c>
       <c r="BS9" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="BT9" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="BU9" t="s">
-        <v>264</v>
-      </c>
-      <c r="BV9" t="s">
-        <v>264</v>
-      </c>
-      <c r="BW9">
+        <v>259</v>
+      </c>
+      <c r="BV9">
         <v>89</v>
       </c>
+      <c r="BW9" t="s">
+        <v>245</v>
+      </c>
       <c r="BX9" t="s">
-        <v>250</v>
-      </c>
-      <c r="BY9" t="s">
-        <v>250</v>
-      </c>
-      <c r="BZ9" s="29" t="s">
-        <v>266</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="BY9" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="BZ9" s="35"/>
       <c r="CA9" s="35"/>
       <c r="CB9" s="35"/>
       <c r="CC9" s="35"/>
       <c r="CD9" s="35"/>
-      <c r="CE9" s="35"/>
-      <c r="CF9" s="29" t="s">
-        <v>251</v>
-      </c>
-      <c r="CG9" s="36">
+      <c r="CE9" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="CF9" s="36">
         <v>44501</v>
       </c>
+      <c r="CG9" s="35" t="s">
+        <v>262</v>
+      </c>
       <c r="CH9" s="35" t="s">
-        <v>267</v>
-      </c>
-      <c r="CI9" s="35" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
-    <row r="10" spans="1:87" ht="17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:86" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="33"/>
       <c r="B10" s="33"/>
       <c r="C10" s="29" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="D10" s="41" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F10" s="29" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H10" s="43"/>
       <c r="I10" s="34" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="K10" s="29"/>
       <c r="L10" s="29"/>
       <c r="M10" s="35" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="N10" s="35" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="O10" s="29" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="P10" s="29" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="Q10" s="35" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="R10" s="29" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="S10" s="30"/>
       <c r="T10" s="30"/>
@@ -3321,10 +3278,10 @@
         <v>8</v>
       </c>
       <c r="AC10" s="35" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AD10" s="29" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="AE10" s="35"/>
       <c r="AF10" s="29"/>
@@ -3340,29 +3297,29 @@
       <c r="AN10" s="29"/>
       <c r="AO10" s="29"/>
       <c r="AP10" s="35" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="AQ10" s="37" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="AR10" s="29" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="AS10" s="29" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="AT10" s="29" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="AU10" s="29"/>
       <c r="AV10" s="35" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AW10" s="29" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="AX10" s="39" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="AY10" s="40">
         <v>44502</v>
@@ -3371,49 +3328,49 @@
         <v>0.200098</v>
       </c>
       <c r="BA10" s="29" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="BB10" s="29" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="BC10" s="29" t="s">
-        <v>250</v>
-      </c>
-      <c r="BD10" t="s">
-        <v>271</v>
-      </c>
-      <c r="BE10">
+        <v>245</v>
+      </c>
+      <c r="BD10">
         <v>888</v>
       </c>
+      <c r="BE10" s="30">
+        <v>3</v>
+      </c>
       <c r="BF10" s="30">
-        <v>3</v>
+        <v>1680</v>
       </c>
       <c r="BG10" s="30">
-        <v>1680</v>
+        <v>70</v>
       </c>
       <c r="BH10" s="30">
-        <v>70</v>
+        <v>1.4E-2</v>
       </c>
       <c r="BI10" s="30">
-        <v>1.4E-2</v>
-      </c>
-      <c r="BJ10" s="30">
         <v>200</v>
       </c>
+      <c r="BJ10" s="35" t="s">
+        <v>259</v>
+      </c>
       <c r="BK10" s="35" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="BL10" s="35" t="s">
-        <v>264</v>
-      </c>
-      <c r="BM10" s="35" t="s">
-        <v>262</v>
-      </c>
-      <c r="BN10" s="29" t="s">
-        <v>263</v>
-      </c>
-      <c r="BO10" s="29">
+        <v>257</v>
+      </c>
+      <c r="BM10" s="29" t="s">
+        <v>258</v>
+      </c>
+      <c r="BN10" s="29">
         <v>90</v>
+      </c>
+      <c r="BO10">
+        <v>1</v>
       </c>
       <c r="BP10">
         <v>1</v>
@@ -3421,49 +3378,46 @@
       <c r="BQ10">
         <v>1</v>
       </c>
-      <c r="BR10">
-        <v>1</v>
+      <c r="BR10" t="s">
+        <v>260</v>
       </c>
       <c r="BS10" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="BT10" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="BU10" t="s">
-        <v>264</v>
-      </c>
-      <c r="BV10" t="s">
-        <v>264</v>
-      </c>
-      <c r="BW10">
+        <v>259</v>
+      </c>
+      <c r="BV10">
         <v>90</v>
       </c>
+      <c r="BW10" t="s">
+        <v>245</v>
+      </c>
       <c r="BX10" t="s">
-        <v>250</v>
-      </c>
-      <c r="BY10" t="s">
-        <v>250</v>
-      </c>
-      <c r="BZ10" s="29" t="s">
-        <v>266</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="BY10" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="BZ10" s="35"/>
       <c r="CA10" s="35"/>
       <c r="CB10" s="35"/>
       <c r="CC10" s="35"/>
       <c r="CD10" s="35"/>
-      <c r="CE10" s="35"/>
-      <c r="CF10" s="29" t="s">
-        <v>251</v>
-      </c>
-      <c r="CG10" s="36">
+      <c r="CE10" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="CF10" s="36">
         <v>44502</v>
       </c>
+      <c r="CG10" s="35" t="s">
+        <v>262</v>
+      </c>
       <c r="CH10" s="35" t="s">
-        <v>267</v>
-      </c>
-      <c r="CI10" s="35" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>

--- a/spec/fixtures/batch_submission_manifest_object_test.xlsx
+++ b/spec/fixtures/batch_submission_manifest_object_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/smc101/vagrant/morphosource-vagrant/MorphoSource_SF/spec/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55242DF4-4ACD-474E-B4B0-23B1A332E8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D2DB81-763A-6C40-BF19-8DC1348CA67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="283">
   <si>
     <t>Field Section</t>
   </si>
@@ -921,12 +921,28 @@
   <si>
     <t>imaging_event.ct.ie_filter</t>
   </si>
+  <si>
+    <t>Whether this file was created with minimal or no processing (raw) or whether software processing was used to create the file (derived). Raw files only have Imaging Event metadata to describe how the media was initially imaged, derived files have imaging event and processing event metadata to describe both how the media was initially imaged and how it was subsequently processed.</t>
+  </si>
+  <si>
+    <t>Raw: Raw
+Derived: Derived</t>
+  </si>
+  <si>
+    <t>media.raw_or_derived</t>
+  </si>
+  <si>
+    <t>Derived</t>
+  </si>
+  <si>
+    <t>Raw</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -985,6 +1001,10 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="12">
@@ -1067,7 +1087,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1143,6 +1163,12 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1358,15 +1384,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06ED7EC9-286B-1D49-A57D-A989376D77CC}">
-  <dimension ref="A1:CH10"/>
+  <dimension ref="A1:CI10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="28.6640625" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" customWidth="1"/>
-    <col min="7" max="7" width="21.33203125" customWidth="1"/>
+    <col min="6" max="7" width="13.83203125" customWidth="1"/>
+    <col min="8" max="8" width="21.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:86" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:87" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1385,16 +1411,16 @@
       <c r="F1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="47" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12" t="s">
-        <v>3</v>
-      </c>
+      <c r="I1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="12"/>
       <c r="K1" s="12" t="s">
         <v>3</v>
       </c>
@@ -1407,8 +1433,8 @@
       <c r="N1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>4</v>
+      <c r="O1" s="12" t="s">
+        <v>3</v>
       </c>
       <c r="P1" s="2" t="s">
         <v>4</v>
@@ -1438,7 +1464,7 @@
         <v>4</v>
       </c>
       <c r="Y1" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z1" s="2" t="s">
         <v>5</v>
@@ -1453,13 +1479,13 @@
         <v>5</v>
       </c>
       <c r="AD1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="AF1" s="21" t="s">
-        <v>8</v>
       </c>
       <c r="AG1" s="21" t="s">
         <v>8</v>
@@ -1497,8 +1523,8 @@
       <c r="AR1" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="AS1" s="3" t="s">
-        <v>9</v>
+      <c r="AS1" s="21" t="s">
+        <v>8</v>
       </c>
       <c r="AT1" s="3" t="s">
         <v>9</v>
@@ -1506,8 +1532,8 @@
       <c r="AU1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="AV1" s="6" t="s">
-        <v>10</v>
+      <c r="AV1" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="AW1" s="6" t="s">
         <v>10</v>
@@ -1519,7 +1545,7 @@
         <v>10</v>
       </c>
       <c r="AZ1" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA1" s="6" t="s">
         <v>11</v>
@@ -1597,13 +1623,13 @@
         <v>11</v>
       </c>
       <c r="BZ1" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CA1" s="6" t="s">
         <v>12</v>
       </c>
       <c r="CB1" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CC1" s="6" t="s">
         <v>13</v>
@@ -1611,8 +1637,8 @@
       <c r="CD1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="CE1" s="24" t="s">
-        <v>14</v>
+      <c r="CE1" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="CF1" s="24" t="s">
         <v>14</v>
@@ -1623,8 +1649,11 @@
       <c r="CH1" s="24" t="s">
         <v>14</v>
       </c>
+      <c r="CI1" s="24" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:86" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:87" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>15</v>
       </c>
@@ -1635,234 +1664,235 @@
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="G2" s="48"/>
       <c r="H2" s="5"/>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="5"/>
+      <c r="J2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="12"/>
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="12"/>
+      <c r="P2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="V2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="W2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="X2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AE2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AF2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AF2" s="21" t="s">
+      <c r="AG2" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="AG2" s="21" t="s">
+      <c r="AH2" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="AH2" s="21" t="s">
+      <c r="AI2" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="AI2" s="21" t="s">
+      <c r="AJ2" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="AJ2" s="21" t="s">
+      <c r="AK2" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="AK2" s="21" t="s">
+      <c r="AL2" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="AL2" s="21" t="s">
+      <c r="AM2" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="AM2" s="21" t="s">
+      <c r="AN2" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="AN2" s="21" t="s">
+      <c r="AO2" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="AO2" s="21" t="s">
+      <c r="AP2" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="AP2" s="21" t="s">
+      <c r="AQ2" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="AQ2" s="21" t="s">
+      <c r="AR2" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="AR2" s="21" t="s">
+      <c r="AS2" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="AS2" s="3" t="s">
+      <c r="AT2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="AT2" s="3" t="s">
+      <c r="AU2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AU2" s="3" t="s">
+      <c r="AV2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="AV2" s="6" t="s">
+      <c r="AW2" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="AW2" s="6" t="s">
+      <c r="AX2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="AX2" s="6" t="s">
+      <c r="AY2" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="AY2" s="6" t="s">
+      <c r="AZ2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AZ2" s="6" t="s">
+      <c r="BA2" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="BA2" s="6" t="s">
+      <c r="BB2" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="BB2" s="6" t="s">
+      <c r="BC2" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="BC2" s="6" t="s">
+      <c r="BD2" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="BD2" s="6" t="s">
+      <c r="BE2" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="BE2" s="6" t="s">
+      <c r="BF2" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="BF2" s="6" t="s">
+      <c r="BG2" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="BG2" s="6" t="s">
+      <c r="BH2" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="BH2" s="6" t="s">
+      <c r="BI2" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="BI2" s="6" t="s">
+      <c r="BJ2" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="BJ2" s="6" t="s">
+      <c r="BK2" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="BK2" s="6" t="s">
+      <c r="BL2" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="BL2" s="6" t="s">
+      <c r="BM2" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="BM2" s="6" t="s">
+      <c r="BN2" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="BN2" s="6" t="s">
+      <c r="BO2" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="BO2" s="6" t="s">
+      <c r="BP2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="BP2" s="6" t="s">
+      <c r="BQ2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="BQ2" s="6" t="s">
+      <c r="BR2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="BR2" s="6" t="s">
+      <c r="BS2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="BS2" s="6" t="s">
+      <c r="BT2" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="BT2" s="6" t="s">
+      <c r="BU2" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="BU2" s="6" t="s">
+      <c r="BV2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="BV2" s="6" t="s">
+      <c r="BW2" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="BW2" s="6" t="s">
+      <c r="BX2" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="BX2" s="6" t="s">
+      <c r="BY2" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="BY2" s="6" t="s">
+      <c r="BZ2" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="BZ2" s="6" t="s">
+      <c r="CA2" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="CA2" s="6" t="s">
+      <c r="CB2" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="CB2" s="6" t="s">
+      <c r="CC2" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="CC2" s="6" t="s">
+      <c r="CD2" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="CD2" s="6" t="s">
+      <c r="CE2" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="CE2" s="24" t="s">
+      <c r="CF2" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="CF2" s="24" t="s">
+      <c r="CG2" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="CG2" s="24" t="s">
+      <c r="CH2" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="CH2" s="24" t="s">
+      <c r="CI2" s="24" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:86" ht="139.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:87" ht="139.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="7" t="s">
         <v>82</v>
       </c>
@@ -1877,62 +1907,64 @@
       </c>
       <c r="E3" s="9"/>
       <c r="F3" s="10"/>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="49" t="s">
+        <v>278</v>
+      </c>
+      <c r="H3" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="H3" s="10"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11" t="s">
+      <c r="I3" s="10"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="K3" s="12"/>
       <c r="L3" s="12"/>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="12"/>
+      <c r="N3" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="O3" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="O3" s="13" t="s">
+      <c r="P3" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="P3" s="14"/>
       <c r="Q3" s="14"/>
-      <c r="R3" s="13" t="s">
+      <c r="R3" s="14"/>
+      <c r="S3" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="S3" s="13" t="s">
+      <c r="T3" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="T3" s="2"/>
-      <c r="U3" s="13" t="s">
+      <c r="U3" s="2"/>
+      <c r="V3" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="V3" s="13"/>
-      <c r="W3" s="2"/>
+      <c r="W3" s="13"/>
       <c r="X3" s="2"/>
-      <c r="Y3" s="15" t="s">
+      <c r="Y3" s="2"/>
+      <c r="Z3" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="Z3" s="15" t="s">
+      <c r="AA3" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="AA3" s="15" t="s">
+      <c r="AB3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="AB3" s="13" t="s">
+      <c r="AC3" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="AC3" s="13" t="s">
+      <c r="AD3" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="AD3" s="14"/>
-      <c r="AE3" s="2"/>
-      <c r="AF3" s="21"/>
+      <c r="AE3" s="14"/>
+      <c r="AF3" s="2"/>
       <c r="AG3" s="21"/>
       <c r="AH3" s="21"/>
       <c r="AI3" s="21"/>
-      <c r="AJ3" s="16"/>
+      <c r="AJ3" s="21"/>
       <c r="AK3" s="16"/>
       <c r="AL3" s="16"/>
       <c r="AM3" s="16"/>
@@ -1940,113 +1972,114 @@
       <c r="AO3" s="16"/>
       <c r="AP3" s="16"/>
       <c r="AQ3" s="16"/>
-      <c r="AR3" s="21" t="s">
+      <c r="AR3" s="16"/>
+      <c r="AS3" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="AS3" s="17"/>
       <c r="AT3" s="17"/>
       <c r="AU3" s="17"/>
-      <c r="AV3" s="6"/>
+      <c r="AV3" s="17"/>
       <c r="AW3" s="6"/>
-      <c r="AX3" s="18" t="s">
+      <c r="AX3" s="6"/>
+      <c r="AY3" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="AY3" s="18"/>
-      <c r="AZ3" s="19" t="s">
+      <c r="AZ3" s="18"/>
+      <c r="BA3" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="BA3" s="19" t="s">
+      <c r="BB3" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="BB3" s="19" t="s">
+      <c r="BC3" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="BC3" s="19" t="s">
+      <c r="BD3" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="BD3" s="19" t="s">
+      <c r="BE3" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="BE3" s="19" t="s">
+      <c r="BF3" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="BF3" s="19" t="s">
+      <c r="BG3" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="BG3" s="19" t="s">
+      <c r="BH3" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="BH3" s="19" t="s">
+      <c r="BI3" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="BI3" s="19" t="s">
+      <c r="BJ3" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="BJ3" s="19" t="s">
+      <c r="BK3" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="BK3" s="18" t="s">
+      <c r="BL3" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="BL3" s="18"/>
-      <c r="BM3" s="18" t="s">
+      <c r="BM3" s="18"/>
+      <c r="BN3" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="BN3" s="20" t="s">
+      <c r="BO3" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="BO3" s="20" t="s">
+      <c r="BP3" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="BP3" s="20" t="s">
+      <c r="BQ3" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="BQ3" s="20" t="s">
+      <c r="BR3" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="BR3" s="18" t="s">
+      <c r="BS3" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="BS3" s="18" t="s">
+      <c r="BT3" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="BT3" s="18" t="s">
+      <c r="BU3" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="BU3" s="18" t="s">
+      <c r="BV3" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="BV3" s="18" t="s">
+      <c r="BW3" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="BW3" s="18" t="s">
+      <c r="BX3" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="BX3" s="18" t="s">
+      <c r="BY3" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="BY3" s="19"/>
-      <c r="BZ3" s="18" t="s">
+      <c r="BZ3" s="19"/>
+      <c r="CA3" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="CA3" s="18" t="s">
+      <c r="CB3" s="18" t="s">
         <v>126</v>
-      </c>
-      <c r="CB3" s="18" t="s">
-        <v>127</v>
       </c>
       <c r="CC3" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="CD3" s="19" t="s">
+      <c r="CD3" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="CE3" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="CE3" s="24"/>
       <c r="CF3" s="24"/>
       <c r="CG3" s="24"/>
       <c r="CH3" s="24"/>
+      <c r="CI3" s="24"/>
     </row>
-    <row r="4" spans="1:86" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:87" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
         <v>129</v>
       </c>
@@ -2063,13 +2096,13 @@
       <c r="F4" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="G4" s="5"/>
+      <c r="G4" s="47" t="s">
+        <v>131</v>
+      </c>
       <c r="H4" s="5"/>
-      <c r="I4" s="12"/>
+      <c r="I4" s="5"/>
       <c r="J4" s="12"/>
-      <c r="K4" s="12" t="s">
-        <v>132</v>
-      </c>
+      <c r="K4" s="12"/>
       <c r="L4" s="12" t="s">
         <v>132</v>
       </c>
@@ -2079,32 +2112,34 @@
       <c r="N4" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="O4" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="P4" s="14"/>
+      <c r="P4" s="2" t="s">
+        <v>132</v>
+      </c>
       <c r="Q4" s="14"/>
-      <c r="R4" s="2"/>
+      <c r="R4" s="14"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
       <c r="V4" s="2"/>
       <c r="W4" s="2"/>
       <c r="X4" s="2"/>
-      <c r="Y4" s="2" t="s">
-        <v>133</v>
-      </c>
+      <c r="Y4" s="2"/>
       <c r="Z4" s="2" t="s">
         <v>133</v>
       </c>
       <c r="AA4" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="AB4" s="2"/>
+      <c r="AB4" s="2" t="s">
+        <v>133</v>
+      </c>
       <c r="AC4" s="2"/>
-      <c r="AD4" s="14"/>
-      <c r="AE4" s="2"/>
-      <c r="AF4" s="16"/>
+      <c r="AD4" s="2"/>
+      <c r="AE4" s="14"/>
+      <c r="AF4" s="2"/>
       <c r="AG4" s="16"/>
       <c r="AH4" s="16"/>
       <c r="AI4" s="16"/>
@@ -2117,10 +2152,10 @@
       <c r="AP4" s="16"/>
       <c r="AQ4" s="16"/>
       <c r="AR4" s="16"/>
-      <c r="AS4" s="17"/>
+      <c r="AS4" s="16"/>
       <c r="AT4" s="17"/>
       <c r="AU4" s="17"/>
-      <c r="AV4" s="6"/>
+      <c r="AV4" s="17"/>
       <c r="AW4" s="6"/>
       <c r="AX4" s="6"/>
       <c r="AY4" s="6"/>
@@ -2155,12 +2190,13 @@
       <c r="CB4" s="6"/>
       <c r="CC4" s="6"/>
       <c r="CD4" s="6"/>
-      <c r="CE4" s="24"/>
+      <c r="CE4" s="6"/>
       <c r="CF4" s="24"/>
       <c r="CG4" s="24"/>
       <c r="CH4" s="24"/>
+      <c r="CI4" s="24"/>
     </row>
-    <row r="5" spans="1:86" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:87" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
         <v>134</v>
       </c>
@@ -2179,13 +2215,13 @@
       <c r="F5" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>136</v>
+      <c r="G5" s="47" t="s">
+        <v>137</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="5" t="s">
         <v>136</v>
       </c>
       <c r="J5" s="12" t="s">
@@ -2203,18 +2239,18 @@
       <c r="N5" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="O5" s="12" t="s">
         <v>136</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>136</v>
       </c>
       <c r="Q5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="R5" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="R5" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="S5" s="2" t="s">
         <v>136</v>
       </c>
@@ -2228,13 +2264,13 @@
         <v>136</v>
       </c>
       <c r="W5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="X5" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="X5" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="Y5" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="Z5" s="2" t="s">
         <v>139</v>
@@ -2246,7 +2282,7 @@
         <v>139</v>
       </c>
       <c r="AC5" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AD5" s="2" t="s">
         <v>137</v>
@@ -2254,29 +2290,29 @@
       <c r="AE5" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="AF5" s="21" t="s">
-        <v>136</v>
+      <c r="AF5" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="AG5" s="21" t="s">
         <v>136</v>
       </c>
       <c r="AH5" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="AI5" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="AI5" s="21" t="s">
-        <v>136</v>
-      </c>
       <c r="AJ5" s="21" t="s">
         <v>136</v>
       </c>
       <c r="AK5" s="21" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="AL5" s="21" t="s">
         <v>139</v>
       </c>
       <c r="AM5" s="21" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AN5" s="21" t="s">
         <v>136</v>
@@ -2285,24 +2321,24 @@
         <v>136</v>
       </c>
       <c r="AP5" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="AQ5" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="AQ5" s="21" t="s">
+      <c r="AR5" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="AR5" s="21" t="s">
+      <c r="AS5" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="AS5" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="AT5" s="3" t="s">
         <v>136</v>
       </c>
       <c r="AU5" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="AV5" s="6" t="s">
+      <c r="AV5" s="3" t="s">
         <v>136</v>
       </c>
       <c r="AW5" s="6" t="s">
@@ -2314,11 +2350,11 @@
       <c r="AY5" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="AZ5" s="22" t="s">
+      <c r="AZ5" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BA5" s="22" t="s">
         <v>139</v>
-      </c>
-      <c r="BA5" s="22" t="s">
-        <v>140</v>
       </c>
       <c r="BB5" s="22" t="s">
         <v>140</v>
@@ -2327,10 +2363,10 @@
         <v>140</v>
       </c>
       <c r="BD5" s="22" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="BE5" s="22" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="BF5" s="22" t="s">
         <v>139</v>
@@ -2345,35 +2381,35 @@
         <v>139</v>
       </c>
       <c r="BJ5" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="BK5" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="BK5" s="22" t="s">
         <v>136</v>
       </c>
       <c r="BL5" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="BM5" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="BN5" s="23" t="s">
+      <c r="BN5" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="BO5" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="BO5" s="23" t="s">
+      <c r="BP5" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="BP5" s="23" t="s">
+      <c r="BQ5" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="BQ5" s="23" t="s">
+      <c r="BR5" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="BR5" s="6" t="s">
+      <c r="BS5" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="BS5" s="6" t="s">
-        <v>136</v>
-      </c>
       <c r="BT5" s="6" t="s">
         <v>136</v>
       </c>
@@ -2381,22 +2417,22 @@
         <v>136</v>
       </c>
       <c r="BV5" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="BW5" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="BW5" s="6" t="s">
-        <v>140</v>
       </c>
       <c r="BX5" s="6" t="s">
         <v>140</v>
       </c>
       <c r="BY5" s="6" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="BZ5" s="6" t="s">
         <v>137</v>
       </c>
       <c r="CA5" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="CB5" s="6" t="s">
         <v>136</v>
@@ -2405,22 +2441,25 @@
         <v>136</v>
       </c>
       <c r="CD5" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="CE5" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="CE5" s="24" t="s">
-        <v>136</v>
-      </c>
       <c r="CF5" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="CG5" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="CG5" s="24" t="s">
-        <v>136</v>
-      </c>
       <c r="CH5" s="24" t="s">
         <v>136</v>
       </c>
+      <c r="CI5" s="24" t="s">
+        <v>136</v>
+      </c>
     </row>
-    <row r="6" spans="1:86" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:87" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
         <v>142</v>
       </c>
@@ -2435,20 +2474,22 @@
       <c r="F6" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="G6" s="5"/>
+      <c r="G6" s="47" t="s">
+        <v>279</v>
+      </c>
       <c r="H6" s="5"/>
-      <c r="I6" s="12"/>
+      <c r="I6" s="5"/>
       <c r="J6" s="12"/>
       <c r="K6" s="12"/>
       <c r="L6" s="12"/>
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
-      <c r="O6" s="2"/>
+      <c r="O6" s="12"/>
       <c r="P6" s="2"/>
-      <c r="Q6" s="2" t="s">
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="R6" s="2"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
@@ -2459,16 +2500,16 @@
       <c r="Z6" s="2"/>
       <c r="AA6" s="2"/>
       <c r="AB6" s="2"/>
-      <c r="AC6" s="2" t="s">
+      <c r="AC6" s="2"/>
+      <c r="AD6" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="AD6" s="2" t="s">
+      <c r="AE6" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="AE6" s="2" t="s">
+      <c r="AF6" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="AF6" s="21"/>
       <c r="AG6" s="21"/>
       <c r="AH6" s="21"/>
       <c r="AI6" s="21"/>
@@ -2479,14 +2520,14 @@
       <c r="AN6" s="21"/>
       <c r="AO6" s="21"/>
       <c r="AP6" s="21"/>
-      <c r="AQ6" s="21" t="s">
+      <c r="AQ6" s="21"/>
+      <c r="AR6" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="AR6" s="21"/>
-      <c r="AS6" s="3"/>
+      <c r="AS6" s="21"/>
       <c r="AT6" s="3"/>
       <c r="AU6" s="3"/>
-      <c r="AV6" s="6"/>
+      <c r="AV6" s="3"/>
       <c r="AW6" s="6"/>
       <c r="AX6" s="6"/>
       <c r="AY6" s="6"/>
@@ -2502,43 +2543,44 @@
       <c r="BI6" s="6"/>
       <c r="BJ6" s="6"/>
       <c r="BK6" s="6"/>
-      <c r="BL6" s="6" t="s">
+      <c r="BL6" s="6"/>
+      <c r="BM6" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="BM6" s="6" t="s">
+      <c r="BN6" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="BN6" s="6"/>
       <c r="BO6" s="6"/>
       <c r="BP6" s="6"/>
       <c r="BQ6" s="6"/>
-      <c r="BR6" s="6" t="s">
+      <c r="BR6" s="6"/>
+      <c r="BS6" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="BS6" s="6"/>
       <c r="BT6" s="6"/>
       <c r="BU6" s="6"/>
       <c r="BV6" s="6"/>
       <c r="BW6" s="6"/>
       <c r="BX6" s="6"/>
-      <c r="BY6" s="6" t="s">
+      <c r="BY6" s="6"/>
+      <c r="BZ6" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="BZ6" s="6" t="s">
+      <c r="CA6" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="CA6" s="6"/>
       <c r="CB6" s="6"/>
       <c r="CC6" s="6"/>
-      <c r="CD6" s="6" t="s">
+      <c r="CD6" s="6"/>
+      <c r="CE6" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="CE6" s="24"/>
       <c r="CF6" s="24"/>
       <c r="CG6" s="24"/>
       <c r="CH6" s="24"/>
+      <c r="CI6" s="24"/>
     </row>
-    <row r="7" spans="1:86" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:87" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="44" t="s">
         <v>269</v>
       </c>
@@ -2557,248 +2599,251 @@
       <c r="F7" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="47" t="s">
+        <v>280</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="I7" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="I7" s="25" t="s">
+      <c r="J7" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="J7" s="12" t="s">
+      <c r="K7" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="L7" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="M7" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="M7" s="12" t="s">
+      <c r="N7" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="N7" s="12" t="s">
+      <c r="O7" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="O7" s="26" t="s">
+      <c r="P7" s="26" t="s">
         <v>169</v>
       </c>
-      <c r="P7" s="26" t="s">
+      <c r="Q7" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="Q7" s="26" t="s">
+      <c r="R7" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="U7" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="U7" s="2" t="s">
+      <c r="V7" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="W7" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="X7" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="X7" s="2" t="s">
+      <c r="Y7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="Y7" s="26" t="s">
+      <c r="Z7" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="Z7" s="26" t="s">
+      <c r="AA7" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="AA7" s="26" t="s">
+      <c r="AB7" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="AB7" s="2" t="s">
+      <c r="AC7" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="AC7" s="2" t="s">
+      <c r="AD7" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="AD7" s="26" t="s">
+      <c r="AE7" s="26" t="s">
         <v>184</v>
       </c>
-      <c r="AE7" s="2" t="s">
+      <c r="AF7" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="AF7" s="27" t="s">
+      <c r="AG7" s="27" t="s">
         <v>186</v>
       </c>
-      <c r="AG7" s="27" t="s">
+      <c r="AH7" s="27" t="s">
         <v>187</v>
       </c>
-      <c r="AH7" s="27" t="s">
+      <c r="AI7" s="27" t="s">
         <v>188</v>
       </c>
-      <c r="AI7" s="27" t="s">
+      <c r="AJ7" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="AJ7" s="27" t="s">
+      <c r="AK7" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="AK7" s="27" t="s">
+      <c r="AL7" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="AL7" s="27" t="s">
+      <c r="AM7" s="27" t="s">
         <v>192</v>
       </c>
-      <c r="AM7" s="27" t="s">
+      <c r="AN7" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="AN7" s="27" t="s">
+      <c r="AO7" s="27" t="s">
         <v>194</v>
       </c>
-      <c r="AO7" s="27" t="s">
+      <c r="AP7" s="27" t="s">
         <v>195</v>
       </c>
-      <c r="AP7" s="27" t="s">
+      <c r="AQ7" s="27" t="s">
         <v>196</v>
       </c>
-      <c r="AQ7" s="27" t="s">
+      <c r="AR7" s="27" t="s">
         <v>197</v>
       </c>
-      <c r="AR7" s="27" t="s">
+      <c r="AS7" s="27" t="s">
         <v>198</v>
       </c>
-      <c r="AS7" s="29" t="s">
+      <c r="AT7" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="AT7" s="29" t="s">
+      <c r="AU7" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="AU7" s="29" t="s">
+      <c r="AV7" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="AV7" s="29" t="s">
+      <c r="AW7" s="29" t="s">
         <v>202</v>
       </c>
-      <c r="AW7" s="29" t="s">
+      <c r="AX7" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="AX7" s="6" t="s">
+      <c r="AY7" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="AY7" s="6" t="s">
+      <c r="AZ7" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="AZ7" s="29" t="s">
+      <c r="BA7" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="BA7" s="29" t="s">
+      <c r="BB7" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="BB7" s="29" t="s">
+      <c r="BC7" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="BC7" s="29" t="s">
+      <c r="BD7" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="BD7" s="6" t="s">
+      <c r="BE7" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="BE7" s="29" t="s">
+      <c r="BF7" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="BF7" s="29" t="s">
+      <c r="BG7" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="BG7" s="29" t="s">
+      <c r="BH7" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="BH7" s="29" t="s">
+      <c r="BI7" s="29" t="s">
         <v>213</v>
       </c>
-      <c r="BI7" s="29" t="s">
+      <c r="BJ7" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="BJ7" s="29" t="s">
+      <c r="BK7" s="29" t="s">
         <v>215</v>
       </c>
-      <c r="BK7" s="6" t="s">
+      <c r="BL7" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="BL7" s="6" t="s">
+      <c r="BM7" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="BM7" s="6" t="s">
+      <c r="BN7" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="BN7" s="6" t="s">
+      <c r="BO7" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="BO7" s="6" t="s">
+      <c r="BP7" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="BP7" s="6" t="s">
+      <c r="BQ7" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="BQ7" s="6" t="s">
+      <c r="BR7" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="BR7" s="6" t="s">
+      <c r="BS7" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="BS7" s="6" t="s">
+      <c r="BT7" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="BT7" s="6" t="s">
+      <c r="BU7" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="BU7" s="6" t="s">
+      <c r="BV7" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="BV7" s="6" t="s">
+      <c r="BW7" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="BW7" s="6" t="s">
+      <c r="BX7" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="BX7" s="6" t="s">
+      <c r="BY7" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="BY7" s="28" t="s">
+      <c r="BZ7" s="28" t="s">
         <v>230</v>
       </c>
-      <c r="BZ7" s="6" t="s">
+      <c r="CA7" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="CA7" s="6" t="s">
+      <c r="CB7" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="CB7" s="6" t="s">
+      <c r="CC7" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="CC7" s="6" t="s">
+      <c r="CD7" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="CD7" s="6" t="s">
+      <c r="CE7" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="CE7" s="29" t="s">
+      <c r="CF7" s="29" t="s">
         <v>236</v>
       </c>
-      <c r="CF7" s="29" t="s">
+      <c r="CG7" s="29" t="s">
         <v>237</v>
       </c>
-      <c r="CG7" s="29" t="s">
+      <c r="CH7" s="29" t="s">
         <v>238</v>
       </c>
-      <c r="CH7" s="29" t="s">
+      <c r="CI7" s="29" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="8" spans="1:86" ht="17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:87" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="44" t="s">
         <v>271</v>
       </c>
@@ -2817,43 +2862,43 @@
       <c r="F8" s="29" t="s">
         <v>240</v>
       </c>
-      <c r="H8" s="43"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29" t="s">
+      <c r="G8" s="50" t="s">
+        <v>282</v>
+      </c>
+      <c r="I8" s="43"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="29" t="s">
         <v>273</v>
       </c>
-      <c r="L8" s="29"/>
-      <c r="M8" s="35" t="s">
+      <c r="M8" s="29"/>
+      <c r="N8" s="35" t="s">
         <v>274</v>
       </c>
-      <c r="N8" s="35" t="s">
+      <c r="O8" s="35" t="s">
         <v>275</v>
       </c>
-      <c r="O8" s="29" t="s">
+      <c r="P8" s="29" t="s">
         <v>241</v>
       </c>
-      <c r="P8" s="29" t="s">
+      <c r="Q8" s="29" t="s">
         <v>242</v>
       </c>
-      <c r="Q8" s="35" t="s">
+      <c r="R8" s="35" t="s">
         <v>250</v>
       </c>
-      <c r="R8" s="29" t="s">
+      <c r="S8" s="29" t="s">
         <v>243</v>
       </c>
-      <c r="S8" s="30"/>
       <c r="T8" s="30"/>
-      <c r="U8" s="31"/>
+      <c r="U8" s="30"/>
       <c r="V8" s="31"/>
-      <c r="W8" s="36">
+      <c r="W8" s="31"/>
+      <c r="X8" s="36">
         <v>44177</v>
       </c>
-      <c r="X8" s="42" t="s">
+      <c r="Y8" s="42" t="s">
         <v>265</v>
-      </c>
-      <c r="Y8" s="30">
-        <v>2.169024E-2</v>
       </c>
       <c r="Z8" s="30">
         <v>2.169024E-2</v>
@@ -2862,38 +2907,38 @@
         <v>2.169024E-2</v>
       </c>
       <c r="AB8" s="30">
+        <v>2.169024E-2</v>
+      </c>
+      <c r="AC8" s="30">
         <v>8</v>
       </c>
-      <c r="AC8" s="35" t="s">
+      <c r="AD8" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="AD8" s="29" t="s">
+      <c r="AE8" s="29" t="s">
         <v>244</v>
       </c>
-      <c r="AE8" s="35"/>
-      <c r="AF8" s="35" t="s">
+      <c r="AF8" s="35"/>
+      <c r="AG8" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="AG8" s="35" t="s">
+      <c r="AH8" s="35" t="s">
         <v>265</v>
       </c>
-      <c r="AH8" s="36">
+      <c r="AI8" s="36">
         <v>44177</v>
-      </c>
-      <c r="AI8" s="35" t="s">
-        <v>259</v>
       </c>
       <c r="AJ8" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="AK8" s="29">
-        <v>88</v>
+      <c r="AK8" s="35" t="s">
+        <v>259</v>
       </c>
       <c r="AL8" s="29">
         <v>88</v>
       </c>
-      <c r="AM8" s="35" t="s">
-        <v>259</v>
+      <c r="AM8" s="29">
+        <v>88</v>
       </c>
       <c r="AN8" s="35" t="s">
         <v>259</v>
@@ -2902,80 +2947,80 @@
         <v>259</v>
       </c>
       <c r="AP8" s="35" t="s">
+        <v>259</v>
+      </c>
+      <c r="AQ8" s="35" t="s">
         <v>245</v>
       </c>
-      <c r="AQ8" s="37" t="s">
+      <c r="AR8" s="37" t="s">
         <v>251</v>
       </c>
-      <c r="AR8" s="29" t="s">
+      <c r="AS8" s="29" t="s">
         <v>245</v>
       </c>
-      <c r="AS8" s="29" t="s">
+      <c r="AT8" s="29" t="s">
         <v>253</v>
       </c>
-      <c r="AT8" s="29" t="s">
+      <c r="AU8" s="29" t="s">
         <v>254</v>
       </c>
-      <c r="AU8" s="29"/>
-      <c r="AV8" s="35" t="s">
+      <c r="AV8" s="29"/>
+      <c r="AW8" s="35" t="s">
         <v>255</v>
       </c>
-      <c r="AW8" s="29" t="s">
+      <c r="AX8" s="29" t="s">
         <v>246</v>
       </c>
-      <c r="AX8" s="39" t="s">
+      <c r="AY8" s="39" t="s">
         <v>256</v>
       </c>
-      <c r="AY8" s="40">
+      <c r="AZ8" s="40">
         <v>44500</v>
       </c>
-      <c r="AZ8" s="30">
+      <c r="BA8" s="30">
         <v>0.200098</v>
-      </c>
-      <c r="BA8" s="29" t="s">
-        <v>247</v>
       </c>
       <c r="BB8" s="29" t="s">
         <v>247</v>
       </c>
       <c r="BC8" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="BD8" s="29" t="s">
         <v>245</v>
       </c>
-      <c r="BD8">
+      <c r="BE8">
         <v>888</v>
       </c>
-      <c r="BE8" s="30">
+      <c r="BF8" s="30">
         <v>3</v>
       </c>
-      <c r="BF8" s="30">
+      <c r="BG8" s="30">
         <v>1680</v>
       </c>
-      <c r="BG8" s="30">
+      <c r="BH8" s="30">
         <v>70</v>
       </c>
-      <c r="BH8" s="30">
+      <c r="BI8" s="30">
         <v>1.4E-2</v>
       </c>
-      <c r="BI8" s="30">
+      <c r="BJ8" s="30">
         <v>200</v>
-      </c>
-      <c r="BJ8" s="35" t="s">
-        <v>259</v>
       </c>
       <c r="BK8" s="35" t="s">
         <v>259</v>
       </c>
       <c r="BL8" s="35" t="s">
+        <v>259</v>
+      </c>
+      <c r="BM8" s="35" t="s">
         <v>257</v>
       </c>
-      <c r="BM8" s="29" t="s">
+      <c r="BN8" s="29" t="s">
         <v>258</v>
       </c>
-      <c r="BN8" s="29">
+      <c r="BO8" s="29">
         <v>88</v>
-      </c>
-      <c r="BO8">
-        <v>1</v>
       </c>
       <c r="BP8">
         <v>1</v>
@@ -2983,11 +3028,11 @@
       <c r="BQ8">
         <v>1</v>
       </c>
-      <c r="BR8" t="s">
+      <c r="BR8">
+        <v>1</v>
+      </c>
+      <c r="BS8" t="s">
         <v>260</v>
-      </c>
-      <c r="BS8" t="s">
-        <v>259</v>
       </c>
       <c r="BT8" t="s">
         <v>259</v>
@@ -2995,37 +3040,40 @@
       <c r="BU8" t="s">
         <v>259</v>
       </c>
-      <c r="BV8">
+      <c r="BV8" t="s">
+        <v>259</v>
+      </c>
+      <c r="BW8">
         <v>88</v>
-      </c>
-      <c r="BW8" t="s">
-        <v>245</v>
       </c>
       <c r="BX8" t="s">
         <v>245</v>
       </c>
-      <c r="BY8" s="29" t="s">
+      <c r="BY8" t="s">
+        <v>245</v>
+      </c>
+      <c r="BZ8" s="29" t="s">
         <v>261</v>
       </c>
-      <c r="BZ8" s="35"/>
       <c r="CA8" s="35"/>
       <c r="CB8" s="35"/>
       <c r="CC8" s="35"/>
       <c r="CD8" s="35"/>
-      <c r="CE8" s="29" t="s">
+      <c r="CE8" s="35"/>
+      <c r="CF8" s="29" t="s">
         <v>246</v>
       </c>
-      <c r="CF8" s="36">
+      <c r="CG8" s="36">
         <v>44500</v>
       </c>
-      <c r="CG8" s="35" t="s">
+      <c r="CH8" s="35" t="s">
         <v>262</v>
       </c>
-      <c r="CH8" s="35" t="s">
+      <c r="CI8" s="35" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="9" spans="1:86" ht="17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:87" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="33"/>
       <c r="B9" s="38"/>
       <c r="C9" s="35" t="s">
@@ -3040,43 +3088,43 @@
       <c r="F9" s="29" t="s">
         <v>240</v>
       </c>
-      <c r="G9" s="29" t="s">
+      <c r="G9" s="50" t="s">
+        <v>281</v>
+      </c>
+      <c r="H9" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="H9" s="43"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="29"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="34"/>
       <c r="K9" s="29"/>
       <c r="L9" s="29"/>
-      <c r="M9" s="35" t="s">
+      <c r="M9" s="29"/>
+      <c r="N9" s="35" t="s">
         <v>274</v>
       </c>
-      <c r="N9" s="35" t="s">
+      <c r="O9" s="35" t="s">
         <v>275</v>
       </c>
-      <c r="O9" s="29" t="s">
+      <c r="P9" s="29" t="s">
         <v>241</v>
       </c>
-      <c r="P9" s="29" t="s">
+      <c r="Q9" s="29" t="s">
         <v>242</v>
       </c>
-      <c r="Q9" s="35" t="s">
+      <c r="R9" s="35" t="s">
         <v>250</v>
       </c>
-      <c r="R9" s="29" t="s">
+      <c r="S9" s="29" t="s">
         <v>243</v>
       </c>
-      <c r="S9" s="30"/>
       <c r="T9" s="30"/>
-      <c r="U9" s="32"/>
+      <c r="U9" s="30"/>
       <c r="V9" s="32"/>
-      <c r="W9" s="36">
+      <c r="W9" s="32"/>
+      <c r="X9" s="36">
         <v>44177</v>
       </c>
-      <c r="X9" s="32"/>
-      <c r="Y9" s="30">
-        <v>2.725352E-2</v>
-      </c>
+      <c r="Y9" s="32"/>
       <c r="Z9" s="30">
         <v>2.725352E-2</v>
       </c>
@@ -3084,16 +3132,18 @@
         <v>2.725352E-2</v>
       </c>
       <c r="AB9" s="30">
+        <v>2.725352E-2</v>
+      </c>
+      <c r="AC9" s="30">
         <v>8</v>
       </c>
-      <c r="AC9" s="35" t="s">
+      <c r="AD9" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="AD9" s="29" t="s">
+      <c r="AE9" s="29" t="s">
         <v>244</v>
       </c>
-      <c r="AE9" s="35"/>
-      <c r="AF9" s="29"/>
+      <c r="AF9" s="35"/>
       <c r="AG9" s="29"/>
       <c r="AH9" s="29"/>
       <c r="AI9" s="29"/>
@@ -3103,84 +3153,82 @@
       <c r="AM9" s="29"/>
       <c r="AN9" s="29"/>
       <c r="AO9" s="29"/>
-      <c r="AP9" s="35" t="s">
+      <c r="AP9" s="29"/>
+      <c r="AQ9" s="35" t="s">
         <v>245</v>
       </c>
-      <c r="AQ9" s="37" t="s">
+      <c r="AR9" s="37" t="s">
         <v>251</v>
       </c>
-      <c r="AR9" s="29" t="s">
+      <c r="AS9" s="29" t="s">
         <v>245</v>
       </c>
-      <c r="AS9" s="29" t="s">
+      <c r="AT9" s="29" t="s">
         <v>253</v>
       </c>
-      <c r="AT9" s="29" t="s">
+      <c r="AU9" s="29" t="s">
         <v>254</v>
       </c>
-      <c r="AU9" s="29"/>
-      <c r="AV9" s="35" t="s">
+      <c r="AV9" s="29"/>
+      <c r="AW9" s="35" t="s">
         <v>255</v>
       </c>
-      <c r="AW9" s="29" t="s">
+      <c r="AX9" s="29" t="s">
         <v>246</v>
       </c>
-      <c r="AX9" s="39" t="s">
+      <c r="AY9" s="39" t="s">
         <v>256</v>
       </c>
-      <c r="AY9" s="40">
+      <c r="AZ9" s="40">
         <v>44501</v>
       </c>
-      <c r="AZ9" s="30">
+      <c r="BA9" s="30">
         <v>0.200098</v>
-      </c>
-      <c r="BA9" s="29" t="s">
-        <v>247</v>
       </c>
       <c r="BB9" s="29" t="s">
         <v>247</v>
       </c>
       <c r="BC9" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="BD9" s="29" t="s">
         <v>245</v>
       </c>
-      <c r="BD9">
+      <c r="BE9">
         <v>888</v>
       </c>
-      <c r="BE9" s="30">
+      <c r="BF9" s="30">
         <v>3</v>
       </c>
-      <c r="BF9" s="30">
+      <c r="BG9" s="30">
         <v>1680</v>
       </c>
-      <c r="BG9" s="30">
+      <c r="BH9" s="30">
         <v>70</v>
       </c>
-      <c r="BH9" s="30">
+      <c r="BI9" s="30">
         <v>1.54E-2</v>
       </c>
-      <c r="BI9" s="30">
+      <c r="BJ9" s="30">
         <v>220</v>
-      </c>
-      <c r="BJ9" s="35" t="s">
-        <v>259</v>
       </c>
       <c r="BK9" s="35" t="s">
         <v>259</v>
       </c>
       <c r="BL9" s="35" t="s">
+        <v>259</v>
+      </c>
+      <c r="BM9" s="35" t="s">
         <v>257</v>
       </c>
-      <c r="BM9" s="29" t="s">
+      <c r="BN9" s="29" t="s">
         <v>258</v>
       </c>
-      <c r="BN9" s="29">
+      <c r="BO9" s="29">
         <v>89</v>
       </c>
-      <c r="BR9" t="s">
+      <c r="BS9" t="s">
         <v>260</v>
-      </c>
-      <c r="BS9" t="s">
-        <v>259</v>
       </c>
       <c r="BT9" t="s">
         <v>259</v>
@@ -3188,37 +3236,40 @@
       <c r="BU9" t="s">
         <v>259</v>
       </c>
-      <c r="BV9">
+      <c r="BV9" t="s">
+        <v>259</v>
+      </c>
+      <c r="BW9">
         <v>89</v>
-      </c>
-      <c r="BW9" t="s">
-        <v>245</v>
       </c>
       <c r="BX9" t="s">
         <v>245</v>
       </c>
-      <c r="BY9" s="29" t="s">
+      <c r="BY9" t="s">
+        <v>245</v>
+      </c>
+      <c r="BZ9" s="29" t="s">
         <v>261</v>
       </c>
-      <c r="BZ9" s="35"/>
       <c r="CA9" s="35"/>
       <c r="CB9" s="35"/>
       <c r="CC9" s="35"/>
       <c r="CD9" s="35"/>
-      <c r="CE9" s="29" t="s">
+      <c r="CE9" s="35"/>
+      <c r="CF9" s="29" t="s">
         <v>246</v>
       </c>
-      <c r="CF9" s="36">
+      <c r="CG9" s="36">
         <v>44501</v>
       </c>
-      <c r="CG9" s="35" t="s">
+      <c r="CH9" s="35" t="s">
         <v>262</v>
       </c>
-      <c r="CH9" s="35" t="s">
+      <c r="CI9" s="35" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="10" spans="1:86" ht="17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:87" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="33"/>
       <c r="B10" s="33"/>
       <c r="C10" s="29" t="s">
@@ -3233,41 +3284,41 @@
       <c r="F10" s="29" t="s">
         <v>240</v>
       </c>
-      <c r="H10" s="43"/>
-      <c r="I10" s="34" t="s">
+      <c r="G10" s="50" t="s">
+        <v>281</v>
+      </c>
+      <c r="I10" s="43"/>
+      <c r="J10" s="34" t="s">
         <v>268</v>
       </c>
-      <c r="K10" s="29"/>
       <c r="L10" s="29"/>
-      <c r="M10" s="35" t="s">
+      <c r="M10" s="29"/>
+      <c r="N10" s="35" t="s">
         <v>274</v>
       </c>
-      <c r="N10" s="35" t="s">
+      <c r="O10" s="35" t="s">
         <v>275</v>
       </c>
-      <c r="O10" s="29" t="s">
+      <c r="P10" s="29" t="s">
         <v>241</v>
       </c>
-      <c r="P10" s="29" t="s">
+      <c r="Q10" s="29" t="s">
         <v>242</v>
       </c>
-      <c r="Q10" s="35" t="s">
+      <c r="R10" s="35" t="s">
         <v>250</v>
       </c>
-      <c r="R10" s="29" t="s">
+      <c r="S10" s="29" t="s">
         <v>243</v>
       </c>
-      <c r="S10" s="30"/>
       <c r="T10" s="30"/>
-      <c r="U10" s="31"/>
+      <c r="U10" s="30"/>
       <c r="V10" s="31"/>
-      <c r="W10" s="36">
+      <c r="W10" s="31"/>
+      <c r="X10" s="36">
         <v>44177</v>
       </c>
-      <c r="X10" s="31"/>
-      <c r="Y10" s="30">
-        <v>2.169024E-2</v>
-      </c>
+      <c r="Y10" s="31"/>
       <c r="Z10" s="30">
         <v>2.169024E-2</v>
       </c>
@@ -3275,102 +3326,102 @@
         <v>2.169024E-2</v>
       </c>
       <c r="AB10" s="30">
+        <v>2.169024E-2</v>
+      </c>
+      <c r="AC10" s="30">
         <v>8</v>
       </c>
-      <c r="AC10" s="35" t="s">
+      <c r="AD10" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="AD10" s="29" t="s">
+      <c r="AE10" s="29" t="s">
         <v>244</v>
       </c>
-      <c r="AE10" s="35"/>
-      <c r="AF10" s="29"/>
+      <c r="AF10" s="35"/>
       <c r="AG10" s="29"/>
-      <c r="AH10" s="36">
+      <c r="AH10" s="29"/>
+      <c r="AI10" s="36">
         <v>44177</v>
       </c>
-      <c r="AI10" s="29"/>
       <c r="AJ10" s="29"/>
       <c r="AK10" s="29"/>
       <c r="AL10" s="29"/>
       <c r="AM10" s="29"/>
       <c r="AN10" s="29"/>
       <c r="AO10" s="29"/>
-      <c r="AP10" s="35" t="s">
+      <c r="AP10" s="29"/>
+      <c r="AQ10" s="35" t="s">
         <v>245</v>
       </c>
-      <c r="AQ10" s="37" t="s">
+      <c r="AR10" s="37" t="s">
         <v>251</v>
       </c>
-      <c r="AR10" s="29" t="s">
+      <c r="AS10" s="29" t="s">
         <v>245</v>
       </c>
-      <c r="AS10" s="29" t="s">
+      <c r="AT10" s="29" t="s">
         <v>266</v>
       </c>
-      <c r="AT10" s="29" t="s">
+      <c r="AU10" s="29" t="s">
         <v>267</v>
       </c>
-      <c r="AU10" s="29"/>
-      <c r="AV10" s="35" t="s">
+      <c r="AV10" s="29"/>
+      <c r="AW10" s="35" t="s">
         <v>255</v>
       </c>
-      <c r="AW10" s="29" t="s">
+      <c r="AX10" s="29" t="s">
         <v>246</v>
       </c>
-      <c r="AX10" s="39" t="s">
+      <c r="AY10" s="39" t="s">
         <v>256</v>
       </c>
-      <c r="AY10" s="40">
+      <c r="AZ10" s="40">
         <v>44502</v>
       </c>
-      <c r="AZ10" s="30">
+      <c r="BA10" s="30">
         <v>0.200098</v>
-      </c>
-      <c r="BA10" s="29" t="s">
-        <v>247</v>
       </c>
       <c r="BB10" s="29" t="s">
         <v>247</v>
       </c>
       <c r="BC10" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="BD10" s="29" t="s">
         <v>245</v>
       </c>
-      <c r="BD10">
+      <c r="BE10">
         <v>888</v>
       </c>
-      <c r="BE10" s="30">
+      <c r="BF10" s="30">
         <v>3</v>
       </c>
-      <c r="BF10" s="30">
+      <c r="BG10" s="30">
         <v>1680</v>
       </c>
-      <c r="BG10" s="30">
+      <c r="BH10" s="30">
         <v>70</v>
       </c>
-      <c r="BH10" s="30">
+      <c r="BI10" s="30">
         <v>1.4E-2</v>
       </c>
-      <c r="BI10" s="30">
+      <c r="BJ10" s="30">
         <v>200</v>
-      </c>
-      <c r="BJ10" s="35" t="s">
-        <v>259</v>
       </c>
       <c r="BK10" s="35" t="s">
         <v>259</v>
       </c>
       <c r="BL10" s="35" t="s">
+        <v>259</v>
+      </c>
+      <c r="BM10" s="35" t="s">
         <v>257</v>
       </c>
-      <c r="BM10" s="29" t="s">
+      <c r="BN10" s="29" t="s">
         <v>258</v>
       </c>
-      <c r="BN10" s="29">
+      <c r="BO10" s="29">
         <v>90</v>
-      </c>
-      <c r="BO10">
-        <v>1</v>
       </c>
       <c r="BP10">
         <v>1</v>
@@ -3378,11 +3429,11 @@
       <c r="BQ10">
         <v>1</v>
       </c>
-      <c r="BR10" t="s">
+      <c r="BR10">
+        <v>1</v>
+      </c>
+      <c r="BS10" t="s">
         <v>260</v>
-      </c>
-      <c r="BS10" t="s">
-        <v>259</v>
       </c>
       <c r="BT10" t="s">
         <v>259</v>
@@ -3390,33 +3441,36 @@
       <c r="BU10" t="s">
         <v>259</v>
       </c>
-      <c r="BV10">
+      <c r="BV10" t="s">
+        <v>259</v>
+      </c>
+      <c r="BW10">
         <v>90</v>
-      </c>
-      <c r="BW10" t="s">
-        <v>245</v>
       </c>
       <c r="BX10" t="s">
         <v>245</v>
       </c>
-      <c r="BY10" s="29" t="s">
+      <c r="BY10" t="s">
+        <v>245</v>
+      </c>
+      <c r="BZ10" s="29" t="s">
         <v>261</v>
       </c>
-      <c r="BZ10" s="35"/>
       <c r="CA10" s="35"/>
       <c r="CB10" s="35"/>
       <c r="CC10" s="35"/>
       <c r="CD10" s="35"/>
-      <c r="CE10" s="29" t="s">
+      <c r="CE10" s="35"/>
+      <c r="CF10" s="29" t="s">
         <v>246</v>
       </c>
-      <c r="CF10" s="36">
+      <c r="CG10" s="36">
         <v>44502</v>
       </c>
-      <c r="CG10" s="35" t="s">
+      <c r="CH10" s="35" t="s">
         <v>262</v>
       </c>
-      <c r="CH10" s="35" t="s">
+      <c r="CI10" s="35" t="s">
         <v>263</v>
       </c>
     </row>

--- a/spec/fixtures/batch_submission_manifest_object_test.xlsx
+++ b/spec/fixtures/batch_submission_manifest_object_test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10111"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/smc101/vagrant/morphosource-vagrant/MorphoSource_SF/spec/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D2DB81-763A-6C40-BF19-8DC1348CA67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9950B873-716C-E940-AFE7-42A9B2A8FA07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -826,9 +826,6 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>Zach Randall</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
@@ -936,6 +933,9 @@
   </si>
   <si>
     <t>Raw</t>
+  </si>
+  <si>
+    <t>John Doe</t>
   </si>
 </sst>
 </file>
@@ -1799,7 +1799,7 @@
         <v>55</v>
       </c>
       <c r="BE2" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="BF2" s="6" t="s">
         <v>56</v>
@@ -1908,7 +1908,7 @@
       <c r="E3" s="9"/>
       <c r="F3" s="10"/>
       <c r="G3" s="49" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H3" s="10" t="s">
         <v>86</v>
@@ -2475,7 +2475,7 @@
         <v>145</v>
       </c>
       <c r="G6" s="47" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -2582,10 +2582,10 @@
     </row>
     <row r="7" spans="1:87" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="44" t="s">
+        <v>268</v>
+      </c>
+      <c r="B7" s="45" t="s">
         <v>269</v>
-      </c>
-      <c r="B7" s="45" t="s">
-        <v>270</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>157</v>
@@ -2600,7 +2600,7 @@
         <v>160</v>
       </c>
       <c r="G7" s="47" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>161</v>
@@ -2750,7 +2750,7 @@
         <v>209</v>
       </c>
       <c r="BE7" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="BF7" s="29" t="s">
         <v>210</v>
@@ -2845,38 +2845,38 @@
     </row>
     <row r="8" spans="1:87" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="44" t="s">
+        <v>270</v>
+      </c>
+      <c r="B8" s="46" t="s">
         <v>271</v>
       </c>
-      <c r="B8" s="46" t="s">
-        <v>272</v>
-      </c>
       <c r="C8" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>263</v>
+      </c>
+      <c r="E8" s="29" t="s">
         <v>248</v>
-      </c>
-      <c r="D8" s="41" t="s">
-        <v>264</v>
-      </c>
-      <c r="E8" s="29" t="s">
-        <v>249</v>
       </c>
       <c r="F8" s="29" t="s">
         <v>240</v>
       </c>
       <c r="G8" s="50" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I8" s="43"/>
       <c r="J8" s="34"/>
       <c r="K8" s="29"/>
       <c r="L8" s="29" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M8" s="29"/>
       <c r="N8" s="35" t="s">
+        <v>273</v>
+      </c>
+      <c r="O8" s="35" t="s">
         <v>274</v>
-      </c>
-      <c r="O8" s="35" t="s">
-        <v>275</v>
       </c>
       <c r="P8" s="29" t="s">
         <v>241</v>
@@ -2885,7 +2885,7 @@
         <v>242</v>
       </c>
       <c r="R8" s="35" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="S8" s="29" t="s">
         <v>243</v>
@@ -2898,7 +2898,7 @@
         <v>44177</v>
       </c>
       <c r="Y8" s="42" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Z8" s="30">
         <v>2.169024E-2</v>
@@ -2920,19 +2920,19 @@
       </c>
       <c r="AF8" s="35"/>
       <c r="AG8" s="35" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AH8" s="35" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AI8" s="36">
         <v>44177</v>
       </c>
       <c r="AJ8" s="35" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AK8" s="35" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AL8" s="29">
         <v>88</v>
@@ -2941,38 +2941,38 @@
         <v>88</v>
       </c>
       <c r="AN8" s="35" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AO8" s="35" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AP8" s="35" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AQ8" s="35" t="s">
         <v>245</v>
       </c>
       <c r="AR8" s="37" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AS8" s="29" t="s">
         <v>245</v>
       </c>
       <c r="AT8" s="29" t="s">
+        <v>252</v>
+      </c>
+      <c r="AU8" s="29" t="s">
         <v>253</v>
-      </c>
-      <c r="AU8" s="29" t="s">
-        <v>254</v>
       </c>
       <c r="AV8" s="29"/>
       <c r="AW8" s="35" t="s">
+        <v>254</v>
+      </c>
+      <c r="AX8" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="AY8" s="39" t="s">
         <v>255</v>
-      </c>
-      <c r="AX8" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="AY8" s="39" t="s">
-        <v>256</v>
       </c>
       <c r="AZ8" s="40">
         <v>44500</v>
@@ -2981,10 +2981,10 @@
         <v>0.200098</v>
       </c>
       <c r="BB8" s="29" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="BC8" s="29" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="BD8" s="29" t="s">
         <v>245</v>
@@ -3008,16 +3008,16 @@
         <v>200</v>
       </c>
       <c r="BK8" s="35" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BL8" s="35" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BM8" s="35" t="s">
+        <v>256</v>
+      </c>
+      <c r="BN8" s="29" t="s">
         <v>257</v>
-      </c>
-      <c r="BN8" s="29" t="s">
-        <v>258</v>
       </c>
       <c r="BO8" s="29">
         <v>88</v>
@@ -3032,16 +3032,16 @@
         <v>1</v>
       </c>
       <c r="BS8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BT8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BU8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BV8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BW8">
         <v>88</v>
@@ -3053,7 +3053,7 @@
         <v>245</v>
       </c>
       <c r="BZ8" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="CA8" s="35"/>
       <c r="CB8" s="35"/>
@@ -3061,38 +3061,38 @@
       <c r="CD8" s="35"/>
       <c r="CE8" s="35"/>
       <c r="CF8" s="29" t="s">
-        <v>246</v>
+        <v>282</v>
       </c>
       <c r="CG8" s="36">
         <v>44500</v>
       </c>
       <c r="CH8" s="35" t="s">
+        <v>261</v>
+      </c>
+      <c r="CI8" s="35" t="s">
         <v>262</v>
-      </c>
-      <c r="CI8" s="35" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:87" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="33"/>
       <c r="B9" s="38"/>
       <c r="C9" s="35" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D9" s="41" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F9" s="29" t="s">
         <v>240</v>
       </c>
       <c r="G9" s="50" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I9" s="43"/>
       <c r="J9" s="34"/>
@@ -3100,10 +3100,10 @@
       <c r="L9" s="29"/>
       <c r="M9" s="29"/>
       <c r="N9" s="35" t="s">
+        <v>273</v>
+      </c>
+      <c r="O9" s="35" t="s">
         <v>274</v>
-      </c>
-      <c r="O9" s="35" t="s">
-        <v>275</v>
       </c>
       <c r="P9" s="29" t="s">
         <v>241</v>
@@ -3112,7 +3112,7 @@
         <v>242</v>
       </c>
       <c r="R9" s="35" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="S9" s="29" t="s">
         <v>243</v>
@@ -3158,26 +3158,26 @@
         <v>245</v>
       </c>
       <c r="AR9" s="37" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AS9" s="29" t="s">
         <v>245</v>
       </c>
       <c r="AT9" s="29" t="s">
+        <v>252</v>
+      </c>
+      <c r="AU9" s="29" t="s">
         <v>253</v>
-      </c>
-      <c r="AU9" s="29" t="s">
-        <v>254</v>
       </c>
       <c r="AV9" s="29"/>
       <c r="AW9" s="35" t="s">
+        <v>254</v>
+      </c>
+      <c r="AX9" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="AY9" s="39" t="s">
         <v>255</v>
-      </c>
-      <c r="AX9" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="AY9" s="39" t="s">
-        <v>256</v>
       </c>
       <c r="AZ9" s="40">
         <v>44501</v>
@@ -3186,10 +3186,10 @@
         <v>0.200098</v>
       </c>
       <c r="BB9" s="29" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="BC9" s="29" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="BD9" s="29" t="s">
         <v>245</v>
@@ -3213,31 +3213,31 @@
         <v>220</v>
       </c>
       <c r="BK9" s="35" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BL9" s="35" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BM9" s="35" t="s">
+        <v>256</v>
+      </c>
+      <c r="BN9" s="29" t="s">
         <v>257</v>
-      </c>
-      <c r="BN9" s="29" t="s">
-        <v>258</v>
       </c>
       <c r="BO9" s="29">
         <v>89</v>
       </c>
       <c r="BS9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BT9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BU9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BV9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BW9">
         <v>89</v>
@@ -3249,7 +3249,7 @@
         <v>245</v>
       </c>
       <c r="BZ9" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="CA9" s="35"/>
       <c r="CB9" s="35"/>
@@ -3257,47 +3257,47 @@
       <c r="CD9" s="35"/>
       <c r="CE9" s="35"/>
       <c r="CF9" s="29" t="s">
-        <v>246</v>
+        <v>282</v>
       </c>
       <c r="CG9" s="36">
         <v>44501</v>
       </c>
       <c r="CH9" s="35" t="s">
+        <v>261</v>
+      </c>
+      <c r="CI9" s="35" t="s">
         <v>262</v>
-      </c>
-      <c r="CI9" s="35" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:87" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="33"/>
       <c r="B10" s="33"/>
       <c r="C10" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="D10" s="41" t="s">
+        <v>263</v>
+      </c>
+      <c r="E10" s="29" t="s">
         <v>248</v>
-      </c>
-      <c r="D10" s="41" t="s">
-        <v>264</v>
-      </c>
-      <c r="E10" s="29" t="s">
-        <v>249</v>
       </c>
       <c r="F10" s="29" t="s">
         <v>240</v>
       </c>
       <c r="G10" s="50" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I10" s="43"/>
       <c r="J10" s="34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L10" s="29"/>
       <c r="M10" s="29"/>
       <c r="N10" s="35" t="s">
+        <v>273</v>
+      </c>
+      <c r="O10" s="35" t="s">
         <v>274</v>
-      </c>
-      <c r="O10" s="35" t="s">
-        <v>275</v>
       </c>
       <c r="P10" s="29" t="s">
         <v>241</v>
@@ -3306,7 +3306,7 @@
         <v>242</v>
       </c>
       <c r="R10" s="35" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="S10" s="29" t="s">
         <v>243</v>
@@ -3354,26 +3354,26 @@
         <v>245</v>
       </c>
       <c r="AR10" s="37" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AS10" s="29" t="s">
         <v>245</v>
       </c>
       <c r="AT10" s="29" t="s">
+        <v>265</v>
+      </c>
+      <c r="AU10" s="29" t="s">
         <v>266</v>
-      </c>
-      <c r="AU10" s="29" t="s">
-        <v>267</v>
       </c>
       <c r="AV10" s="29"/>
       <c r="AW10" s="35" t="s">
+        <v>254</v>
+      </c>
+      <c r="AX10" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="AY10" s="39" t="s">
         <v>255</v>
-      </c>
-      <c r="AX10" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="AY10" s="39" t="s">
-        <v>256</v>
       </c>
       <c r="AZ10" s="40">
         <v>44502</v>
@@ -3382,10 +3382,10 @@
         <v>0.200098</v>
       </c>
       <c r="BB10" s="29" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="BC10" s="29" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="BD10" s="29" t="s">
         <v>245</v>
@@ -3409,16 +3409,16 @@
         <v>200</v>
       </c>
       <c r="BK10" s="35" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BL10" s="35" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BM10" s="35" t="s">
+        <v>256</v>
+      </c>
+      <c r="BN10" s="29" t="s">
         <v>257</v>
-      </c>
-      <c r="BN10" s="29" t="s">
-        <v>258</v>
       </c>
       <c r="BO10" s="29">
         <v>90</v>
@@ -3433,16 +3433,16 @@
         <v>1</v>
       </c>
       <c r="BS10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="BT10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BU10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BV10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BW10">
         <v>90</v>
@@ -3454,7 +3454,7 @@
         <v>245</v>
       </c>
       <c r="BZ10" s="29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="CA10" s="35"/>
       <c r="CB10" s="35"/>
@@ -3462,16 +3462,16 @@
       <c r="CD10" s="35"/>
       <c r="CE10" s="35"/>
       <c r="CF10" s="29" t="s">
-        <v>246</v>
+        <v>282</v>
       </c>
       <c r="CG10" s="36">
         <v>44502</v>
       </c>
       <c r="CH10" s="35" t="s">
+        <v>261</v>
+      </c>
+      <c r="CI10" s="35" t="s">
         <v>262</v>
-      </c>
-      <c r="CI10" s="35" t="s">
-        <v>263</v>
       </c>
     </row>
   </sheetData>

--- a/spec/fixtures/batch_submission_manifest_object_test.xlsx
+++ b/spec/fixtures/batch_submission_manifest_object_test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10410"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/smc101/vagrant/morphosource-vagrant/MorphoSource_SF/spec/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9950B873-716C-E940-AFE7-42A9B2A8FA07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD5B255-E61E-B24B-81A4-26CB38D4F15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="284">
   <si>
     <t>Field Section</t>
   </si>
@@ -184,9 +184,6 @@
     <t>Flux normalization</t>
   </si>
   <si>
-    <t>Geometric calibration</t>
-  </si>
-  <si>
     <t>Shading correction</t>
   </si>
   <si>
@@ -329,9 +326,6 @@
   </si>
   <si>
     <t>Only takes yes/no values. Flux Normalization Calibration</t>
-  </si>
-  <si>
-    <t>Only takes yes/no values. Geometric Calibration</t>
   </si>
   <si>
     <t>Only takes yes/no values. Shading Correction Calibration</t>
@@ -712,9 +706,6 @@
     <t>imaging_event.ct.flux_normalization</t>
   </si>
   <si>
-    <t>imaging_event.ct.geometric_calibration</t>
-  </si>
-  <si>
     <t>imaging_event.ct.shading_correction</t>
   </si>
   <si>
@@ -936,6 +927,19 @@
   </si>
   <si>
     <t>John Doe</t>
+  </si>
+  <si>
+    <t>Pixel spacing calibration</t>
+  </si>
+  <si>
+    <t>Geometry: Geometry
+Fiducial: Fiducial</t>
+  </si>
+  <si>
+    <t>imaging_event.ct.pixel_spacing_calibration</t>
+  </si>
+  <si>
+    <t>Geometry</t>
   </si>
 </sst>
 </file>
@@ -1087,7 +1091,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1169,6 +1173,8 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1553,7 +1559,7 @@
       <c r="BB1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="BC1" s="6" t="s">
+      <c r="BC1" s="51" t="s">
         <v>11</v>
       </c>
       <c r="BD1" s="6" t="s">
@@ -1792,92 +1798,92 @@
       <c r="BB2" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="BC2" s="6" t="s">
+      <c r="BC2" s="51" t="s">
+        <v>280</v>
+      </c>
+      <c r="BD2" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="BD2" s="6" t="s">
+      <c r="BE2" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="BF2" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="BE2" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="BF2" s="6" t="s">
+      <c r="BG2" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="BG2" s="6" t="s">
+      <c r="BH2" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="BH2" s="6" t="s">
+      <c r="BI2" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="BI2" s="6" t="s">
+      <c r="BJ2" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="BJ2" s="6" t="s">
+      <c r="BK2" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="BK2" s="6" t="s">
+      <c r="BL2" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="BL2" s="6" t="s">
+      <c r="BM2" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="BM2" s="6" t="s">
+      <c r="BN2" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="BN2" s="6" t="s">
+      <c r="BO2" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="BO2" s="6" t="s">
+      <c r="BP2" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="BP2" s="6" t="s">
+      <c r="BQ2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="BQ2" s="6" t="s">
+      <c r="BR2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="BR2" s="6" t="s">
+      <c r="BS2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="BS2" s="6" t="s">
+      <c r="BT2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="BT2" s="6" t="s">
+      <c r="BU2" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="BU2" s="6" t="s">
+      <c r="BV2" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="BV2" s="6" t="s">
+      <c r="BW2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="BW2" s="6" t="s">
+      <c r="BX2" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="BX2" s="6" t="s">
+      <c r="BY2" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="BY2" s="6" t="s">
+      <c r="BZ2" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="BZ2" s="6" t="s">
+      <c r="CA2" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="CA2" s="6" t="s">
+      <c r="CB2" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="CB2" s="6" t="s">
+      <c r="CC2" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="CC2" s="6" t="s">
+      <c r="CD2" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="CD2" s="6" t="s">
+      <c r="CE2" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="CE2" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="CF2" s="24" t="s">
         <v>22</v>
@@ -1894,70 +1900,70 @@
     </row>
     <row r="3" spans="1:87" ht="139.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="D3" s="10" t="s">
         <v>84</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>85</v>
       </c>
       <c r="E3" s="9"/>
       <c r="F3" s="10"/>
       <c r="G3" s="49" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I3" s="10"/>
       <c r="J3" s="11"/>
       <c r="K3" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L3" s="12"/>
       <c r="M3" s="12"/>
       <c r="N3" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="O3" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="P3" s="13" t="s">
         <v>89</v>
-      </c>
-      <c r="P3" s="13" t="s">
-        <v>90</v>
       </c>
       <c r="Q3" s="14"/>
       <c r="R3" s="14"/>
       <c r="S3" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="T3" s="13" t="s">
         <v>91</v>
-      </c>
-      <c r="T3" s="13" t="s">
-        <v>92</v>
       </c>
       <c r="U3" s="2"/>
       <c r="V3" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W3" s="13"/>
       <c r="X3" s="2"/>
       <c r="Y3" s="2"/>
       <c r="Z3" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA3" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="AA3" s="15" t="s">
+      <c r="AB3" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="AB3" s="15" t="s">
+      <c r="AC3" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="AC3" s="13" t="s">
+      <c r="AD3" s="13" t="s">
         <v>97</v>
-      </c>
-      <c r="AD3" s="13" t="s">
-        <v>98</v>
       </c>
       <c r="AE3" s="14"/>
       <c r="AF3" s="2"/>
@@ -1974,7 +1980,7 @@
       <c r="AQ3" s="16"/>
       <c r="AR3" s="16"/>
       <c r="AS3" s="21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AT3" s="17"/>
       <c r="AU3" s="17"/>
@@ -1982,97 +1988,95 @@
       <c r="AW3" s="6"/>
       <c r="AX3" s="6"/>
       <c r="AY3" s="18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AZ3" s="18"/>
       <c r="BA3" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="BB3" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="BB3" s="19" t="s">
+      <c r="BC3" s="19"/>
+      <c r="BD3" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="BC3" s="19" t="s">
+      <c r="BE3" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="BD3" s="19" t="s">
+      <c r="BF3" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="BE3" s="19" t="s">
+      <c r="BG3" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="BF3" s="19" t="s">
+      <c r="BH3" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="BG3" s="19" t="s">
+      <c r="BI3" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="BH3" s="19" t="s">
+      <c r="BJ3" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="BI3" s="19" t="s">
+      <c r="BK3" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="BJ3" s="19" t="s">
+      <c r="BL3" s="18" t="s">
         <v>110</v>
-      </c>
-      <c r="BK3" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="BL3" s="18" t="s">
-        <v>112</v>
       </c>
       <c r="BM3" s="18"/>
       <c r="BN3" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="BO3" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="BP3" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="BO3" s="20" t="s">
+      <c r="BQ3" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="BP3" s="20" t="s">
+      <c r="BR3" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="BQ3" s="20" t="s">
+      <c r="BS3" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="BR3" s="20" t="s">
+      <c r="BT3" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="BS3" s="18" t="s">
+      <c r="BU3" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="BT3" s="18" t="s">
+      <c r="BV3" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="BU3" s="18" t="s">
+      <c r="BW3" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="BV3" s="18" t="s">
+      <c r="BX3" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="BW3" s="18" t="s">
+      <c r="BY3" s="18" t="s">
         <v>122</v>
-      </c>
-      <c r="BX3" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="BY3" s="18" t="s">
-        <v>124</v>
       </c>
       <c r="BZ3" s="19"/>
       <c r="CA3" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="CB3" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="CC3" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="CB3" s="18" t="s">
+      <c r="CD3" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="CE3" s="19" t="s">
         <v>126</v>
-      </c>
-      <c r="CC3" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="CD3" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="CE3" s="19" t="s">
-        <v>128</v>
       </c>
       <c r="CF3" s="24"/>
       <c r="CG3" s="24"/>
@@ -2081,42 +2085,42 @@
     </row>
     <row r="4" spans="1:87" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>129</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>131</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G4" s="47" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="12"/>
       <c r="K4" s="12"/>
       <c r="L4" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="Q4" s="14"/>
       <c r="R4" s="14"/>
@@ -2128,13 +2132,13 @@
       <c r="X4" s="2"/>
       <c r="Y4" s="2"/>
       <c r="Z4" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AA4" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AB4" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AC4" s="2"/>
       <c r="AD4" s="2"/>
@@ -2162,7 +2166,7 @@
       <c r="AZ4" s="6"/>
       <c r="BA4" s="6"/>
       <c r="BB4" s="6"/>
-      <c r="BC4" s="6"/>
+      <c r="BC4" s="51"/>
       <c r="BD4" s="6"/>
       <c r="BE4" s="6"/>
       <c r="BF4" s="6"/>
@@ -2198,284 +2202,284 @@
     </row>
     <row r="5" spans="1:87" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="F5" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="G5" s="47" t="s">
+        <v>135</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="M5" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="N5" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="O5" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="X5" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="Y5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AB5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AC5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AD5" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AE5" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AF5" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG5" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="AH5" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="AI5" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="AJ5" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="AK5" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="AL5" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="AM5" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="G5" s="47" t="s">
+      <c r="AN5" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="AO5" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="AP5" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="AQ5" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR5" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS5" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="AT5" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="AU5" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="AV5" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="AW5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="AX5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="AY5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="AZ5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="BA5" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="BB5" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="BC5" s="52" t="s">
+        <v>135</v>
+      </c>
+      <c r="BD5" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="BE5" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="BF5" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="BG5" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="BH5" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="BI5" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="BJ5" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="BK5" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="BL5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="BM5" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="BN5" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO5" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="BP5" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="BQ5" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="BR5" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="BS5" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="BT5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="BU5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="BV5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="BW5" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="BX5" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="BY5" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="BZ5" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="CA5" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="CB5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="CC5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="CD5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="CE5" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="CF5" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="CG5" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="K5" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="L5" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="M5" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="N5" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="O5" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="W5" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="X5" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y5" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="Z5" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AA5" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AB5" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AC5" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AD5" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="AE5" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="AF5" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="AG5" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="AH5" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="AI5" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="AJ5" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="AK5" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="AL5" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="AM5" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="AN5" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="AO5" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="AP5" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="AQ5" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="AR5" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="AS5" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="AT5" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="AU5" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="AV5" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="AW5" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="AX5" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="AY5" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="AZ5" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="BA5" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="BB5" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="BC5" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="BD5" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="BE5" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="BF5" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="BG5" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="BH5" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="BI5" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="BJ5" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="BK5" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="BL5" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="BM5" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="BN5" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="BO5" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="BP5" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="BQ5" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="BR5" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="BS5" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="BT5" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="BU5" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="BV5" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="BW5" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="BX5" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="BY5" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="BZ5" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="CA5" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="CB5" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="CC5" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="CD5" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="CE5" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="CF5" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="CG5" s="24" t="s">
-        <v>138</v>
-      </c>
       <c r="CH5" s="24" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="CI5" s="24" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:87" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G6" s="47" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -2488,7 +2492,7 @@
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
@@ -2502,13 +2506,13 @@
       <c r="AB6" s="2"/>
       <c r="AC6" s="2"/>
       <c r="AD6" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="AE6" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="AF6" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="AE6" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="AF6" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="AG6" s="21"/>
       <c r="AH6" s="21"/>
@@ -2522,7 +2526,7 @@
       <c r="AP6" s="21"/>
       <c r="AQ6" s="21"/>
       <c r="AR6" s="21" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AS6" s="21"/>
       <c r="AT6" s="3"/>
@@ -2534,7 +2538,9 @@
       <c r="AZ6" s="6"/>
       <c r="BA6" s="6"/>
       <c r="BB6" s="6"/>
-      <c r="BC6" s="6"/>
+      <c r="BC6" s="52" t="s">
+        <v>281</v>
+      </c>
       <c r="BD6" s="6"/>
       <c r="BE6" s="6"/>
       <c r="BF6" s="6"/>
@@ -2545,17 +2551,17 @@
       <c r="BK6" s="6"/>
       <c r="BL6" s="6"/>
       <c r="BM6" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="BN6" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="BO6" s="6"/>
       <c r="BP6" s="6"/>
       <c r="BQ6" s="6"/>
       <c r="BR6" s="6"/>
       <c r="BS6" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="BT6" s="6"/>
       <c r="BU6" s="6"/>
@@ -2564,16 +2570,16 @@
       <c r="BX6" s="6"/>
       <c r="BY6" s="6"/>
       <c r="BZ6" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="CA6" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="CB6" s="6"/>
       <c r="CC6" s="6"/>
       <c r="CD6" s="6"/>
       <c r="CE6" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="CF6" s="24"/>
       <c r="CG6" s="24"/>
@@ -2582,313 +2588,313 @@
     </row>
     <row r="7" spans="1:87" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="44" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B7" s="45" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="G7" s="47" t="s">
+        <v>276</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="I7" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="G7" s="47" t="s">
-        <v>279</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="J7" s="25" t="s">
         <v>161</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="K7" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="L7" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="M7" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="N7" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="M7" s="12" t="s">
+      <c r="O7" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="N7" s="12" t="s">
+      <c r="P7" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="O7" s="12" t="s">
+      <c r="Q7" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="P7" s="26" t="s">
+      <c r="R7" s="26" t="s">
         <v>169</v>
       </c>
-      <c r="Q7" s="26" t="s">
+      <c r="S7" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="R7" s="26" t="s">
+      <c r="T7" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="U7" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="V7" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="U7" s="2" t="s">
+      <c r="W7" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="X7" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="Y7" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="X7" s="2" t="s">
+      <c r="Z7" s="26" t="s">
         <v>177</v>
       </c>
-      <c r="Y7" s="2" t="s">
+      <c r="AA7" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="Z7" s="26" t="s">
+      <c r="AB7" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="AA7" s="26" t="s">
+      <c r="AC7" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="AB7" s="26" t="s">
+      <c r="AD7" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="AC7" s="2" t="s">
+      <c r="AE7" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="AD7" s="2" t="s">
+      <c r="AF7" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="AE7" s="26" t="s">
+      <c r="AG7" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="AF7" s="2" t="s">
+      <c r="AH7" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="AG7" s="27" t="s">
+      <c r="AI7" s="27" t="s">
         <v>186</v>
       </c>
-      <c r="AH7" s="27" t="s">
+      <c r="AJ7" s="27" t="s">
         <v>187</v>
       </c>
-      <c r="AI7" s="27" t="s">
+      <c r="AK7" s="27" t="s">
         <v>188</v>
       </c>
-      <c r="AJ7" s="27" t="s">
+      <c r="AL7" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="AK7" s="27" t="s">
+      <c r="AM7" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="AL7" s="27" t="s">
+      <c r="AN7" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="AM7" s="27" t="s">
+      <c r="AO7" s="27" t="s">
         <v>192</v>
       </c>
-      <c r="AN7" s="27" t="s">
+      <c r="AP7" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="AO7" s="27" t="s">
+      <c r="AQ7" s="27" t="s">
         <v>194</v>
       </c>
-      <c r="AP7" s="27" t="s">
+      <c r="AR7" s="27" t="s">
         <v>195</v>
       </c>
-      <c r="AQ7" s="27" t="s">
+      <c r="AS7" s="27" t="s">
         <v>196</v>
       </c>
-      <c r="AR7" s="27" t="s">
+      <c r="AT7" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="AS7" s="27" t="s">
+      <c r="AU7" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="AT7" s="29" t="s">
+      <c r="AV7" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="AU7" s="29" t="s">
+      <c r="AW7" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="AV7" s="29" t="s">
+      <c r="AX7" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="AW7" s="29" t="s">
+      <c r="AY7" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="AX7" s="29" t="s">
+      <c r="AZ7" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="AY7" s="6" t="s">
+      <c r="BA7" s="29" t="s">
         <v>204</v>
       </c>
-      <c r="AZ7" s="6" t="s">
+      <c r="BB7" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="BA7" s="29" t="s">
+      <c r="BC7" s="50" t="s">
+        <v>282</v>
+      </c>
+      <c r="BD7" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="BB7" s="29" t="s">
+      <c r="BE7" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="BF7" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="BC7" s="29" t="s">
+      <c r="BG7" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="BD7" s="29" t="s">
+      <c r="BH7" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="BE7" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="BF7" s="29" t="s">
+      <c r="BI7" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="BG7" s="29" t="s">
+      <c r="BJ7" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="BH7" s="29" t="s">
+      <c r="BK7" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="BI7" s="29" t="s">
+      <c r="BL7" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="BJ7" s="29" t="s">
+      <c r="BM7" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="BK7" s="29" t="s">
+      <c r="BN7" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="BL7" s="6" t="s">
+      <c r="BO7" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="BM7" s="6" t="s">
+      <c r="BP7" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="BN7" s="6" t="s">
+      <c r="BQ7" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="BO7" s="6" t="s">
+      <c r="BR7" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="BP7" s="6" t="s">
+      <c r="BS7" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="BQ7" s="6" t="s">
+      <c r="BT7" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="BR7" s="6" t="s">
+      <c r="BU7" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="BS7" s="6" t="s">
+      <c r="BV7" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="BT7" s="6" t="s">
+      <c r="BW7" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="BU7" s="6" t="s">
+      <c r="BX7" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="BV7" s="6" t="s">
+      <c r="BY7" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="BW7" s="6" t="s">
+      <c r="BZ7" s="28" t="s">
         <v>227</v>
       </c>
-      <c r="BX7" s="6" t="s">
+      <c r="CA7" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="BY7" s="6" t="s">
+      <c r="CB7" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="BZ7" s="28" t="s">
+      <c r="CC7" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="CA7" s="6" t="s">
+      <c r="CD7" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="CB7" s="6" t="s">
+      <c r="CE7" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="CC7" s="6" t="s">
+      <c r="CF7" s="29" t="s">
         <v>233</v>
       </c>
-      <c r="CD7" s="6" t="s">
+      <c r="CG7" s="29" t="s">
         <v>234</v>
       </c>
-      <c r="CE7" s="6" t="s">
+      <c r="CH7" s="29" t="s">
         <v>235</v>
       </c>
-      <c r="CF7" s="29" t="s">
+      <c r="CI7" s="29" t="s">
         <v>236</v>
-      </c>
-      <c r="CG7" s="29" t="s">
-        <v>237</v>
-      </c>
-      <c r="CH7" s="29" t="s">
-        <v>238</v>
-      </c>
-      <c r="CI7" s="29" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:87" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="44" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B8" s="46" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D8" s="41" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G8" s="50" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="I8" s="43"/>
       <c r="J8" s="34"/>
       <c r="K8" s="29"/>
       <c r="L8" s="29" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="M8" s="29"/>
       <c r="N8" s="35" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="O8" s="35" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="P8" s="29" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="Q8" s="29" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="R8" s="35" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="S8" s="29" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="T8" s="30"/>
       <c r="U8" s="30"/>
@@ -2898,7 +2904,7 @@
         <v>44177</v>
       </c>
       <c r="Y8" s="42" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="Z8" s="30">
         <v>2.169024E-2</v>
@@ -2913,26 +2919,26 @@
         <v>8</v>
       </c>
       <c r="AD8" s="35" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AE8" s="29" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AF8" s="35"/>
       <c r="AG8" s="35" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="AH8" s="35" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="AI8" s="36">
         <v>44177</v>
       </c>
       <c r="AJ8" s="35" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="AK8" s="35" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="AL8" s="29">
         <v>88</v>
@@ -2941,38 +2947,38 @@
         <v>88</v>
       </c>
       <c r="AN8" s="35" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="AO8" s="35" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="AP8" s="35" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="AQ8" s="35" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AR8" s="37" t="s">
+        <v>247</v>
+      </c>
+      <c r="AS8" s="29" t="s">
+        <v>242</v>
+      </c>
+      <c r="AT8" s="29" t="s">
+        <v>249</v>
+      </c>
+      <c r="AU8" s="29" t="s">
         <v>250</v>
-      </c>
-      <c r="AS8" s="29" t="s">
-        <v>245</v>
-      </c>
-      <c r="AT8" s="29" t="s">
-        <v>252</v>
-      </c>
-      <c r="AU8" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="AV8" s="29"/>
       <c r="AW8" s="35" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="AX8" s="29" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="AY8" s="39" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AZ8" s="40">
         <v>44500</v>
@@ -2981,13 +2987,13 @@
         <v>0.200098</v>
       </c>
       <c r="BB8" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="BC8" s="29" t="s">
-        <v>246</v>
+        <v>243</v>
+      </c>
+      <c r="BC8" s="50" t="s">
+        <v>283</v>
       </c>
       <c r="BD8" s="29" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="BE8">
         <v>888</v>
@@ -3008,16 +3014,16 @@
         <v>200</v>
       </c>
       <c r="BK8" s="35" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="BL8" s="35" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="BM8" s="35" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="BN8" s="29" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="BO8" s="29">
         <v>88</v>
@@ -3032,28 +3038,28 @@
         <v>1</v>
       </c>
       <c r="BS8" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="BT8" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="BU8" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="BV8" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="BW8">
         <v>88</v>
       </c>
       <c r="BX8" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="BY8" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="BZ8" s="29" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="CA8" s="35"/>
       <c r="CB8" s="35"/>
@@ -3061,38 +3067,38 @@
       <c r="CD8" s="35"/>
       <c r="CE8" s="35"/>
       <c r="CF8" s="29" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="CG8" s="36">
         <v>44500</v>
       </c>
       <c r="CH8" s="35" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="CI8" s="35" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:87" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="33"/>
       <c r="B9" s="38"/>
       <c r="C9" s="35" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D9" s="41" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G9" s="50" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="I9" s="43"/>
       <c r="J9" s="34"/>
@@ -3100,22 +3106,22 @@
       <c r="L9" s="29"/>
       <c r="M9" s="29"/>
       <c r="N9" s="35" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="O9" s="35" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="P9" s="29" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="Q9" s="29" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="R9" s="35" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="S9" s="29" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="T9" s="30"/>
       <c r="U9" s="30"/>
@@ -3138,10 +3144,10 @@
         <v>8</v>
       </c>
       <c r="AD9" s="35" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AE9" s="29" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AF9" s="35"/>
       <c r="AG9" s="29"/>
@@ -3155,29 +3161,29 @@
       <c r="AO9" s="29"/>
       <c r="AP9" s="29"/>
       <c r="AQ9" s="35" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AR9" s="37" t="s">
+        <v>247</v>
+      </c>
+      <c r="AS9" s="29" t="s">
+        <v>242</v>
+      </c>
+      <c r="AT9" s="29" t="s">
+        <v>249</v>
+      </c>
+      <c r="AU9" s="29" t="s">
         <v>250</v>
-      </c>
-      <c r="AS9" s="29" t="s">
-        <v>245</v>
-      </c>
-      <c r="AT9" s="29" t="s">
-        <v>252</v>
-      </c>
-      <c r="AU9" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="AV9" s="29"/>
       <c r="AW9" s="35" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="AX9" s="29" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="AY9" s="39" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AZ9" s="40">
         <v>44501</v>
@@ -3186,13 +3192,13 @@
         <v>0.200098</v>
       </c>
       <c r="BB9" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="BC9" s="29" t="s">
-        <v>246</v>
+        <v>243</v>
+      </c>
+      <c r="BC9" s="50" t="s">
+        <v>283</v>
       </c>
       <c r="BD9" s="29" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="BE9">
         <v>888</v>
@@ -3213,43 +3219,43 @@
         <v>220</v>
       </c>
       <c r="BK9" s="35" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="BL9" s="35" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="BM9" s="35" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="BN9" s="29" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="BO9" s="29">
         <v>89</v>
       </c>
       <c r="BS9" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="BT9" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="BU9" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="BV9" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="BW9">
         <v>89</v>
       </c>
       <c r="BX9" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="BY9" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="BZ9" s="29" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="CA9" s="35"/>
       <c r="CB9" s="35"/>
@@ -3257,59 +3263,59 @@
       <c r="CD9" s="35"/>
       <c r="CE9" s="35"/>
       <c r="CF9" s="29" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="CG9" s="36">
         <v>44501</v>
       </c>
       <c r="CH9" s="35" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="CI9" s="35" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10" spans="1:87" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="33"/>
       <c r="B10" s="33"/>
       <c r="C10" s="29" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D10" s="41" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F10" s="29" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G10" s="50" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="I10" s="43"/>
       <c r="J10" s="34" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="L10" s="29"/>
       <c r="M10" s="29"/>
       <c r="N10" s="35" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="O10" s="35" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="P10" s="29" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="Q10" s="29" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="R10" s="35" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="S10" s="29" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="T10" s="30"/>
       <c r="U10" s="30"/>
@@ -3332,10 +3338,10 @@
         <v>8</v>
       </c>
       <c r="AD10" s="35" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AE10" s="29" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AF10" s="35"/>
       <c r="AG10" s="29"/>
@@ -3351,29 +3357,29 @@
       <c r="AO10" s="29"/>
       <c r="AP10" s="29"/>
       <c r="AQ10" s="35" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AR10" s="37" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AS10" s="29" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AT10" s="29" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="AU10" s="29" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="AV10" s="29"/>
       <c r="AW10" s="35" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="AX10" s="29" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="AY10" s="39" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AZ10" s="40">
         <v>44502</v>
@@ -3382,13 +3388,13 @@
         <v>0.200098</v>
       </c>
       <c r="BB10" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="BC10" s="29" t="s">
-        <v>246</v>
+        <v>243</v>
+      </c>
+      <c r="BC10" s="50" t="s">
+        <v>283</v>
       </c>
       <c r="BD10" s="29" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="BE10">
         <v>888</v>
@@ -3409,16 +3415,16 @@
         <v>200</v>
       </c>
       <c r="BK10" s="35" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="BL10" s="35" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="BM10" s="35" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="BN10" s="29" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="BO10" s="29">
         <v>90</v>
@@ -3433,28 +3439,28 @@
         <v>1</v>
       </c>
       <c r="BS10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="BT10" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="BU10" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="BV10" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="BW10">
         <v>90</v>
       </c>
       <c r="BX10" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="BY10" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="BZ10" s="29" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="CA10" s="35"/>
       <c r="CB10" s="35"/>
@@ -3462,16 +3468,16 @@
       <c r="CD10" s="35"/>
       <c r="CE10" s="35"/>
       <c r="CF10" s="29" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="CG10" s="36">
         <v>44502</v>
       </c>
       <c r="CH10" s="35" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="CI10" s="35" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>

--- a/spec/fixtures/batch_submission_manifest_object_test.xlsx
+++ b/spec/fixtures/batch_submission_manifest_object_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/smc101/vagrant/morphosource-vagrant/MorphoSource_SF/spec/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD5B255-E61E-B24B-81A4-26CB38D4F15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B671E6-D420-0C44-B9DC-22AC65869CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="281">
   <si>
     <t>Field Section</t>
   </si>
@@ -476,11 +476,6 @@
     </r>
   </si>
   <si>
-    <t>Open: Published with Open Download
-RestrictedDownload: Published with Restricted Download
-Private: Private</t>
-  </si>
-  <si>
     <t>CTImageSeries: CT/MRI image series (multiple files of type *.tiff, *.png, *.dcm, *.zip, etc.)
 Image: Image (*.tiff, *.png, *.dcm, etc.)
 Mesh: Mesh or point cloud (*.stl, *.ply, .etc, with optional associated texture or color file)
@@ -559,9 +554,6 @@
     <t>media.preview_file</t>
   </si>
   <si>
-    <t>media.publication_status</t>
-  </si>
-  <si>
     <t>media.media_type</t>
   </si>
   <si>
@@ -821,9 +813,6 @@
   </si>
   <si>
     <t>ANSP_Fish_181150.zip</t>
-  </si>
-  <si>
-    <t>Open</t>
   </si>
   <si>
     <t>Left</t>
@@ -1091,7 +1080,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1103,9 +1092,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1390,15 +1376,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06ED7EC9-286B-1D49-A57D-A989376D77CC}">
-  <dimension ref="A1:CI10"/>
+  <dimension ref="A1:CH10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="28.6640625" customWidth="1"/>
-    <col min="6" max="7" width="13.83203125" customWidth="1"/>
-    <col min="8" max="8" width="21.33203125" customWidth="1"/>
+    <col min="5" max="6" width="13.83203125" customWidth="1"/>
+    <col min="7" max="7" width="21.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:87" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:86" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1414,33 +1400,33 @@
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="47" t="s">
+      <c r="G1" s="5" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12" t="s">
+      <c r="I1" s="11"/>
+      <c r="J1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="K1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="L1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="M1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="N1" s="11" t="s">
         <v>3</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="P1" s="2" t="s">
         <v>4</v>
@@ -1470,7 +1456,7 @@
         <v>4</v>
       </c>
       <c r="Y1" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z1" s="2" t="s">
         <v>5</v>
@@ -1485,52 +1471,52 @@
         <v>5</v>
       </c>
       <c r="AD1" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AG1" s="21" t="s">
+      <c r="AF1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="AH1" s="21" t="s">
+      <c r="AG1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="AI1" s="21" t="s">
+      <c r="AH1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="AJ1" s="21" t="s">
+      <c r="AI1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="AK1" s="21" t="s">
+      <c r="AJ1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="21" t="s">
+      <c r="AK1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="AM1" s="21" t="s">
+      <c r="AL1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="AN1" s="21" t="s">
+      <c r="AM1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="AO1" s="21" t="s">
+      <c r="AN1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="AP1" s="21" t="s">
+      <c r="AO1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="AQ1" s="21" t="s">
+      <c r="AP1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="AR1" s="21" t="s">
+      <c r="AQ1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="AS1" s="21" t="s">
+      <c r="AR1" s="20" t="s">
         <v>8</v>
+      </c>
+      <c r="AS1" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="AT1" s="3" t="s">
         <v>9</v>
@@ -1538,8 +1524,8 @@
       <c r="AU1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="AV1" s="3" t="s">
-        <v>9</v>
+      <c r="AV1" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="AW1" s="6" t="s">
         <v>10</v>
@@ -1551,15 +1537,15 @@
         <v>10</v>
       </c>
       <c r="AZ1" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="BB1" s="6" t="s">
+      <c r="BB1" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="BC1" s="51" t="s">
+      <c r="BC1" s="6" t="s">
         <v>11</v>
       </c>
       <c r="BD1" s="6" t="s">
@@ -1629,13 +1615,13 @@
         <v>11</v>
       </c>
       <c r="BZ1" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CA1" s="6" t="s">
         <v>12</v>
       </c>
       <c r="CB1" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CC1" s="6" t="s">
         <v>13</v>
@@ -1643,23 +1629,20 @@
       <c r="CD1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="CE1" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="CF1" s="24" t="s">
+      <c r="CE1" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="CG1" s="24" t="s">
+      <c r="CF1" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="CH1" s="24" t="s">
+      <c r="CG1" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="CI1" s="24" t="s">
+      <c r="CH1" s="23" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:87" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:86" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>15</v>
       </c>
@@ -1669,421 +1652,419 @@
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="48"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="5"/>
       <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="12" t="s">
+      <c r="I2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="P2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF2" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="AG2" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH2" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="AI2" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ2" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="AK2" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="AL2" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="AM2" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="AN2" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="AO2" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="AP2" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="AQ2" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="AR2" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="AS2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AT2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AU2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AV2" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AW2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="U2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X2" s="2" t="s">
+      <c r="AX2" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AY2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="Y2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG2" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="AH2" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI2" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="AJ2" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="AK2" s="21" t="s">
+      <c r="AZ2" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="BA2" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="BB2" s="50" t="s">
+        <v>277</v>
+      </c>
+      <c r="BC2" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD2" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="BE2" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="BF2" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="BG2" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="BH2" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="BI2" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="BJ2" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="BK2" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="BL2" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="BM2" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="BN2" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="BO2" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="BP2" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="BQ2" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="BR2" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="BS2" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="BT2" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="BU2" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="BV2" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="BW2" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="BX2" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="BY2" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="BZ2" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="CA2" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="CB2" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="CC2" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="CD2" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="CE2" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="CF2" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="CG2" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="CH2" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="AL2" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="AM2" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="AN2" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="AO2" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="AP2" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="AQ2" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="AR2" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="AS2" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="AT2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AU2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="AV2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="AW2" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="AX2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="AY2" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="AZ2" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="BA2" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB2" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC2" s="51" t="s">
-        <v>280</v>
-      </c>
-      <c r="BD2" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="BE2" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="BF2" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="BG2" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="BH2" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="BI2" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="BJ2" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="BK2" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="BL2" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="BM2" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="BN2" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="BO2" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="BP2" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="BQ2" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="BR2" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="BS2" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="BT2" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="BU2" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="BV2" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="BW2" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="BX2" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="BY2" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="BZ2" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="CA2" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="CB2" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="CC2" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="CD2" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="CE2" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="CF2" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="CG2" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="CH2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="CI2" s="24" t="s">
-        <v>39</v>
-      </c>
     </row>
-    <row r="3" spans="1:87" ht="139.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:86" ht="139.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="7" t="s">
         <v>81</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>84</v>
       </c>
       <c r="E3" s="9"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="49" t="s">
-        <v>274</v>
-      </c>
-      <c r="H3" s="10" t="s">
+      <c r="F3" s="48" t="s">
+        <v>271</v>
+      </c>
+      <c r="G3" s="9" t="s">
         <v>85</v>
       </c>
+      <c r="H3" s="9"/>
       <c r="I3" s="10"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11" t="s">
+      <c r="J3" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="11" t="s">
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="N3" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="P3" s="13" t="s">
+      <c r="O3" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="13" t="s">
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="T3" s="13" t="s">
+      <c r="S3" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="U3" s="2"/>
-      <c r="V3" s="13" t="s">
+      <c r="T3" s="2"/>
+      <c r="U3" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="W3" s="13"/>
+      <c r="V3" s="12"/>
+      <c r="W3" s="2"/>
       <c r="X3" s="2"/>
-      <c r="Y3" s="2"/>
-      <c r="Z3" s="15" t="s">
+      <c r="Y3" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="AA3" s="15" t="s">
+      <c r="Z3" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="AB3" s="15" t="s">
+      <c r="AA3" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="AC3" s="13" t="s">
+      <c r="AB3" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="AD3" s="13" t="s">
+      <c r="AC3" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="AE3" s="14"/>
-      <c r="AF3" s="2"/>
-      <c r="AG3" s="21"/>
-      <c r="AH3" s="21"/>
-      <c r="AI3" s="21"/>
-      <c r="AJ3" s="21"/>
-      <c r="AK3" s="16"/>
-      <c r="AL3" s="16"/>
-      <c r="AM3" s="16"/>
-      <c r="AN3" s="16"/>
-      <c r="AO3" s="16"/>
-      <c r="AP3" s="16"/>
-      <c r="AQ3" s="16"/>
-      <c r="AR3" s="16"/>
-      <c r="AS3" s="21" t="s">
+      <c r="AD3" s="13"/>
+      <c r="AE3" s="2"/>
+      <c r="AF3" s="20"/>
+      <c r="AG3" s="20"/>
+      <c r="AH3" s="20"/>
+      <c r="AI3" s="20"/>
+      <c r="AJ3" s="15"/>
+      <c r="AK3" s="15"/>
+      <c r="AL3" s="15"/>
+      <c r="AM3" s="15"/>
+      <c r="AN3" s="15"/>
+      <c r="AO3" s="15"/>
+      <c r="AP3" s="15"/>
+      <c r="AQ3" s="15"/>
+      <c r="AR3" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="AT3" s="17"/>
-      <c r="AU3" s="17"/>
-      <c r="AV3" s="17"/>
+      <c r="AS3" s="16"/>
+      <c r="AT3" s="16"/>
+      <c r="AU3" s="16"/>
+      <c r="AV3" s="6"/>
       <c r="AW3" s="6"/>
-      <c r="AX3" s="6"/>
-      <c r="AY3" s="18" t="s">
+      <c r="AX3" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="AZ3" s="18"/>
-      <c r="BA3" s="19" t="s">
+      <c r="AY3" s="17"/>
+      <c r="AZ3" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="BB3" s="19" t="s">
+      <c r="BA3" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="BC3" s="19"/>
-      <c r="BD3" s="19" t="s">
+      <c r="BB3" s="18"/>
+      <c r="BC3" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="BE3" s="19" t="s">
+      <c r="BD3" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="BF3" s="19" t="s">
+      <c r="BE3" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="BG3" s="19" t="s">
+      <c r="BF3" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="BH3" s="19" t="s">
+      <c r="BG3" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="BI3" s="19" t="s">
+      <c r="BH3" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="BJ3" s="19" t="s">
+      <c r="BI3" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="BK3" s="19" t="s">
+      <c r="BJ3" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="BL3" s="18" t="s">
+      <c r="BK3" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="BM3" s="18"/>
-      <c r="BN3" s="18" t="s">
+      <c r="BL3" s="17"/>
+      <c r="BM3" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="BO3" s="20" t="s">
+      <c r="BN3" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="BP3" s="20" t="s">
+      <c r="BO3" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="BQ3" s="20" t="s">
+      <c r="BP3" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="BR3" s="20" t="s">
+      <c r="BQ3" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="BS3" s="18" t="s">
+      <c r="BR3" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="BT3" s="18" t="s">
+      <c r="BS3" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="BU3" s="18" t="s">
+      <c r="BT3" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="BV3" s="18" t="s">
+      <c r="BU3" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="BW3" s="18" t="s">
+      <c r="BV3" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="BX3" s="18" t="s">
+      <c r="BW3" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="BY3" s="18" t="s">
+      <c r="BX3" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="BZ3" s="19"/>
-      <c r="CA3" s="18" t="s">
+      <c r="BY3" s="18"/>
+      <c r="BZ3" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="CB3" s="18" t="s">
+      <c r="CA3" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="CC3" s="18" t="s">
+      <c r="CB3" s="17" t="s">
         <v>125</v>
       </c>
+      <c r="CC3" s="17" t="s">
+        <v>125</v>
+      </c>
       <c r="CD3" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="CE3" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="CF3" s="24"/>
-      <c r="CG3" s="24"/>
-      <c r="CH3" s="24"/>
-      <c r="CI3" s="24"/>
+      <c r="CE3" s="23"/>
+      <c r="CF3" s="23"/>
+      <c r="CG3" s="23"/>
+      <c r="CH3" s="23"/>
     </row>
-    <row r="4" spans="1:87" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:86" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
         <v>127</v>
       </c>
@@ -2097,76 +2078,74 @@
       <c r="E4" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="G4" s="47" t="s">
-        <v>129</v>
-      </c>
+      <c r="G4" s="5"/>
       <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12" t="s">
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="L4" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="N4" s="12" t="s">
+      <c r="M4" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="O4" s="12" t="s">
+      <c r="N4" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="14"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="2"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
       <c r="V4" s="2"/>
       <c r="W4" s="2"/>
       <c r="X4" s="2"/>
-      <c r="Y4" s="2"/>
+      <c r="Y4" s="2" t="s">
+        <v>131</v>
+      </c>
       <c r="Z4" s="2" t="s">
         <v>131</v>
       </c>
       <c r="AA4" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="AB4" s="2" t="s">
-        <v>131</v>
-      </c>
+      <c r="AB4" s="2"/>
       <c r="AC4" s="2"/>
-      <c r="AD4" s="2"/>
-      <c r="AE4" s="14"/>
-      <c r="AF4" s="2"/>
-      <c r="AG4" s="16"/>
-      <c r="AH4" s="16"/>
-      <c r="AI4" s="16"/>
-      <c r="AJ4" s="16"/>
-      <c r="AK4" s="16"/>
-      <c r="AL4" s="16"/>
-      <c r="AM4" s="16"/>
-      <c r="AN4" s="16"/>
-      <c r="AO4" s="16"/>
-      <c r="AP4" s="16"/>
-      <c r="AQ4" s="16"/>
-      <c r="AR4" s="16"/>
+      <c r="AD4" s="13"/>
+      <c r="AE4" s="2"/>
+      <c r="AF4" s="15"/>
+      <c r="AG4" s="15"/>
+      <c r="AH4" s="15"/>
+      <c r="AI4" s="15"/>
+      <c r="AJ4" s="15"/>
+      <c r="AK4" s="15"/>
+      <c r="AL4" s="15"/>
+      <c r="AM4" s="15"/>
+      <c r="AN4" s="15"/>
+      <c r="AO4" s="15"/>
+      <c r="AP4" s="15"/>
+      <c r="AQ4" s="15"/>
+      <c r="AR4" s="15"/>
       <c r="AS4" s="16"/>
-      <c r="AT4" s="17"/>
-      <c r="AU4" s="17"/>
-      <c r="AV4" s="17"/>
+      <c r="AT4" s="16"/>
+      <c r="AU4" s="16"/>
+      <c r="AV4" s="6"/>
       <c r="AW4" s="6"/>
       <c r="AX4" s="6"/>
       <c r="AY4" s="6"/>
       <c r="AZ4" s="6"/>
       <c r="BA4" s="6"/>
-      <c r="BB4" s="6"/>
-      <c r="BC4" s="51"/>
+      <c r="BB4" s="50"/>
+      <c r="BC4" s="6"/>
       <c r="BD4" s="6"/>
       <c r="BE4" s="6"/>
       <c r="BF4" s="6"/>
@@ -2194,13 +2173,12 @@
       <c r="CB4" s="6"/>
       <c r="CC4" s="6"/>
       <c r="CD4" s="6"/>
-      <c r="CE4" s="6"/>
-      <c r="CF4" s="24"/>
-      <c r="CG4" s="24"/>
-      <c r="CH4" s="24"/>
-      <c r="CI4" s="24"/>
+      <c r="CE4" s="23"/>
+      <c r="CF4" s="23"/>
+      <c r="CG4" s="23"/>
+      <c r="CH4" s="23"/>
     </row>
-    <row r="5" spans="1:87" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:86" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
         <v>132</v>
       </c>
@@ -2216,44 +2194,44 @@
       <c r="E5" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="46" t="s">
         <v>135</v>
       </c>
-      <c r="G5" s="47" t="s">
+      <c r="G5" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q5" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="K5" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="L5" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="M5" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="N5" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="O5" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>134</v>
-      </c>
       <c r="R5" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S5" s="2" t="s">
         <v>134</v>
@@ -2268,13 +2246,13 @@
         <v>134</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="Z5" s="2" t="s">
         <v>137</v>
@@ -2286,7 +2264,7 @@
         <v>137</v>
       </c>
       <c r="AC5" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AD5" s="2" t="s">
         <v>135</v>
@@ -2294,176 +2272,173 @@
       <c r="AE5" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="AF5" s="2" t="s">
+      <c r="AF5" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="AG5" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="AH5" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="AI5" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="AJ5" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="AK5" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="AL5" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="AM5" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="AN5" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="AO5" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="AP5" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="AQ5" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="AG5" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="AH5" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="AI5" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="AJ5" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="AK5" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="AL5" s="21" t="s">
+      <c r="AR5" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="AS5" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="AT5" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="AU5" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="AV5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="AW5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="AX5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="AY5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="AZ5" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="AM5" s="21" t="s">
+      <c r="BA5" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="BB5" s="51" t="s">
+        <v>135</v>
+      </c>
+      <c r="BC5" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="BD5" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="BE5" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="AN5" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="AO5" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="AP5" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="AQ5" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="AR5" s="21" t="s">
+      <c r="BF5" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="BG5" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="BH5" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="BI5" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="BJ5" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="BK5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="BL5" s="6" t="s">
         <v>135</v>
-      </c>
-      <c r="AS5" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="AT5" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="AU5" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="AV5" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="AW5" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="AX5" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="AY5" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="AZ5" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="BA5" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="BB5" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="BC5" s="52" t="s">
-        <v>135</v>
-      </c>
-      <c r="BD5" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="BE5" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="BF5" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="BG5" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="BH5" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="BI5" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="BJ5" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="BK5" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="BL5" s="6" t="s">
-        <v>134</v>
       </c>
       <c r="BM5" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="BN5" s="6" t="s">
+      <c r="BN5" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="BO5" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="BP5" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="BQ5" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="BR5" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="BO5" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="BP5" s="23" t="s">
+      <c r="BS5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="BT5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="BU5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="BV5" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="BQ5" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="BR5" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="BS5" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="BT5" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="BU5" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="BV5" s="6" t="s">
-        <v>134</v>
-      </c>
       <c r="BW5" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="BX5" s="6" t="s">
         <v>138</v>
       </c>
       <c r="BY5" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="BZ5" s="6" t="s">
         <v>135</v>
       </c>
       <c r="CA5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="CB5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="CC5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="CD5" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="CB5" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="CC5" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="CD5" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="CE5" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="CF5" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="CG5" s="24" t="s">
+      <c r="CE5" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="CF5" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="CH5" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="CI5" s="24" t="s">
+      <c r="CG5" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="CH5" s="23" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="6" spans="1:87" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:86" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
         <v>140</v>
       </c>
@@ -2475,25 +2450,23 @@
       <c r="E6" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="46" t="s">
+        <v>272</v>
+      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="G6" s="47" t="s">
-        <v>275</v>
-      </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2" t="s">
-        <v>144</v>
-      </c>
+      <c r="R6" s="2"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
@@ -2504,43 +2477,43 @@
       <c r="Z6" s="2"/>
       <c r="AA6" s="2"/>
       <c r="AB6" s="2"/>
-      <c r="AC6" s="2"/>
+      <c r="AC6" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="AD6" s="2" t="s">
         <v>145</v>
       </c>
       <c r="AE6" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="AF6" s="2" t="s">
+      <c r="AF6" s="20"/>
+      <c r="AG6" s="20"/>
+      <c r="AH6" s="20"/>
+      <c r="AI6" s="20"/>
+      <c r="AJ6" s="20"/>
+      <c r="AK6" s="20"/>
+      <c r="AL6" s="20"/>
+      <c r="AM6" s="20"/>
+      <c r="AN6" s="20"/>
+      <c r="AO6" s="20"/>
+      <c r="AP6" s="20"/>
+      <c r="AQ6" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="AG6" s="21"/>
-      <c r="AH6" s="21"/>
-      <c r="AI6" s="21"/>
-      <c r="AJ6" s="21"/>
-      <c r="AK6" s="21"/>
-      <c r="AL6" s="21"/>
-      <c r="AM6" s="21"/>
-      <c r="AN6" s="21"/>
-      <c r="AO6" s="21"/>
-      <c r="AP6" s="21"/>
-      <c r="AQ6" s="21"/>
-      <c r="AR6" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="AS6" s="21"/>
+      <c r="AR6" s="20"/>
+      <c r="AS6" s="3"/>
       <c r="AT6" s="3"/>
       <c r="AU6" s="3"/>
-      <c r="AV6" s="3"/>
+      <c r="AV6" s="6"/>
       <c r="AW6" s="6"/>
       <c r="AX6" s="6"/>
       <c r="AY6" s="6"/>
       <c r="AZ6" s="6"/>
       <c r="BA6" s="6"/>
-      <c r="BB6" s="6"/>
-      <c r="BC6" s="52" t="s">
-        <v>281</v>
-      </c>
+      <c r="BB6" s="51" t="s">
+        <v>278</v>
+      </c>
+      <c r="BC6" s="6"/>
       <c r="BD6" s="6"/>
       <c r="BE6" s="6"/>
       <c r="BF6" s="6"/>
@@ -2549,484 +2522,480 @@
       <c r="BI6" s="6"/>
       <c r="BJ6" s="6"/>
       <c r="BK6" s="6"/>
-      <c r="BL6" s="6"/>
+      <c r="BL6" s="6" t="s">
+        <v>148</v>
+      </c>
       <c r="BM6" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="BN6" s="6" t="s">
-        <v>150</v>
-      </c>
+      <c r="BN6" s="6"/>
       <c r="BO6" s="6"/>
       <c r="BP6" s="6"/>
       <c r="BQ6" s="6"/>
-      <c r="BR6" s="6"/>
-      <c r="BS6" s="6" t="s">
-        <v>151</v>
-      </c>
+      <c r="BR6" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="BS6" s="6"/>
       <c r="BT6" s="6"/>
       <c r="BU6" s="6"/>
       <c r="BV6" s="6"/>
       <c r="BW6" s="6"/>
       <c r="BX6" s="6"/>
-      <c r="BY6" s="6"/>
+      <c r="BY6" s="6" t="s">
+        <v>151</v>
+      </c>
       <c r="BZ6" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="CA6" s="6" t="s">
-        <v>153</v>
-      </c>
+      <c r="CA6" s="6"/>
       <c r="CB6" s="6"/>
       <c r="CC6" s="6"/>
-      <c r="CD6" s="6"/>
-      <c r="CE6" s="6" t="s">
+      <c r="CD6" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="CE6" s="23"/>
+      <c r="CF6" s="23"/>
+      <c r="CG6" s="23"/>
+      <c r="CH6" s="23"/>
+    </row>
+    <row r="7" spans="1:86" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="43" t="s">
+        <v>262</v>
+      </c>
+      <c r="B7" s="44" t="s">
+        <v>263</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="CF6" s="24"/>
-      <c r="CG6" s="24"/>
-      <c r="CH6" s="24"/>
-      <c r="CI6" s="24"/>
+      <c r="D7" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F7" s="46" t="s">
+        <v>273</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="I7" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="N7" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="O7" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="P7" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q7" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y7" s="25" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z7" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="AA7" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB7" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="AC7" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="AD7" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="AE7" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="AF7" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="AG7" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="AH7" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="AI7" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="AJ7" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="AK7" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="AL7" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM7" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="AN7" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="AO7" s="26" t="s">
+        <v>191</v>
+      </c>
+      <c r="AP7" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="AQ7" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="AR7" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="AS7" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="AT7" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="AU7" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="AV7" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="AW7" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="AX7" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="AY7" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="AZ7" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="BA7" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="BB7" s="49" t="s">
+        <v>279</v>
+      </c>
+      <c r="BC7" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="BD7" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="BE7" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="BF7" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="BG7" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="BH7" s="28" t="s">
+        <v>208</v>
+      </c>
+      <c r="BI7" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="BJ7" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="BK7" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="BL7" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="BM7" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="BN7" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="BO7" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="BP7" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="BQ7" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="BR7" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="BS7" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="BT7" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="BU7" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="BV7" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="BW7" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="BX7" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="BY7" s="27" t="s">
+        <v>225</v>
+      </c>
+      <c r="BZ7" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="CA7" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="CB7" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="CC7" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="CD7" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="CE7" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="CF7" s="28" t="s">
+        <v>232</v>
+      </c>
+      <c r="CG7" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="CH7" s="28" t="s">
+        <v>234</v>
+      </c>
     </row>
-    <row r="7" spans="1:87" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="44" t="s">
+    <row r="8" spans="1:86" ht="17" x14ac:dyDescent="0.2">
+      <c r="A8" s="43" t="s">
+        <v>264</v>
+      </c>
+      <c r="B8" s="45" t="s">
         <v>265</v>
       </c>
-      <c r="B7" s="45" t="s">
+      <c r="C8" s="28" t="s">
+        <v>242</v>
+      </c>
+      <c r="D8" s="40" t="s">
+        <v>257</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="F8" s="49" t="s">
+        <v>275</v>
+      </c>
+      <c r="H8" s="42"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="28" t="s">
         <v>266</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="G7" s="47" t="s">
+      <c r="L8" s="28"/>
+      <c r="M8" s="34" t="s">
+        <v>267</v>
+      </c>
+      <c r="N8" s="34" t="s">
+        <v>268</v>
+      </c>
+      <c r="O8" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="P8" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q8" s="34" t="s">
+        <v>243</v>
+      </c>
+      <c r="R8" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="S8" s="29"/>
+      <c r="T8" s="29"/>
+      <c r="U8" s="30"/>
+      <c r="V8" s="30"/>
+      <c r="W8" s="35">
+        <v>44177</v>
+      </c>
+      <c r="X8" s="41" t="s">
+        <v>258</v>
+      </c>
+      <c r="Y8" s="29">
+        <v>2.169024E-2</v>
+      </c>
+      <c r="Z8" s="29">
+        <v>2.169024E-2</v>
+      </c>
+      <c r="AA8" s="29">
+        <v>2.169024E-2</v>
+      </c>
+      <c r="AB8" s="29">
+        <v>8</v>
+      </c>
+      <c r="AC8" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD8" s="28" t="s">
+        <v>239</v>
+      </c>
+      <c r="AE8" s="34"/>
+      <c r="AF8" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="AG8" s="34" t="s">
+        <v>258</v>
+      </c>
+      <c r="AH8" s="35">
+        <v>44177</v>
+      </c>
+      <c r="AI8" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="AJ8" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="AK8" s="28">
+        <v>88</v>
+      </c>
+      <c r="AL8" s="28">
+        <v>88</v>
+      </c>
+      <c r="AM8" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="AN8" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="AO8" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="AP8" s="34" t="s">
+        <v>240</v>
+      </c>
+      <c r="AQ8" s="36" t="s">
+        <v>244</v>
+      </c>
+      <c r="AR8" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="AS8" s="28" t="s">
+        <v>246</v>
+      </c>
+      <c r="AT8" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="AU8" s="28"/>
+      <c r="AV8" s="34" t="s">
+        <v>248</v>
+      </c>
+      <c r="AW8" s="28" t="s">
         <v>276</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="J7" s="25" t="s">
-        <v>161</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="L7" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="M7" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="N7" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="O7" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="P7" s="26" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q7" s="26" t="s">
-        <v>168</v>
-      </c>
-      <c r="R7" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="X7" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="Y7" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="Z7" s="26" t="s">
-        <v>177</v>
-      </c>
-      <c r="AA7" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB7" s="26" t="s">
-        <v>179</v>
-      </c>
-      <c r="AC7" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="AD7" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="AE7" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="AF7" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="AG7" s="27" t="s">
-        <v>184</v>
-      </c>
-      <c r="AH7" s="27" t="s">
-        <v>185</v>
-      </c>
-      <c r="AI7" s="27" t="s">
-        <v>186</v>
-      </c>
-      <c r="AJ7" s="27" t="s">
-        <v>187</v>
-      </c>
-      <c r="AK7" s="27" t="s">
-        <v>188</v>
-      </c>
-      <c r="AL7" s="27" t="s">
-        <v>189</v>
-      </c>
-      <c r="AM7" s="27" t="s">
-        <v>190</v>
-      </c>
-      <c r="AN7" s="27" t="s">
-        <v>191</v>
-      </c>
-      <c r="AO7" s="27" t="s">
-        <v>192</v>
-      </c>
-      <c r="AP7" s="27" t="s">
-        <v>193</v>
-      </c>
-      <c r="AQ7" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="AR7" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="AS7" s="27" t="s">
-        <v>196</v>
-      </c>
-      <c r="AT7" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="AU7" s="29" t="s">
-        <v>198</v>
-      </c>
-      <c r="AV7" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="AW7" s="29" t="s">
+      <c r="AX8" s="38" t="s">
+        <v>249</v>
+      </c>
+      <c r="AY8" s="39">
+        <v>44500</v>
+      </c>
+      <c r="AZ8" s="29">
+        <v>0.200098</v>
+      </c>
+      <c r="BA8" s="28" t="s">
+        <v>241</v>
+      </c>
+      <c r="BB8" s="49" t="s">
+        <v>280</v>
+      </c>
+      <c r="BC8" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="BD8">
+        <v>888</v>
+      </c>
+      <c r="BE8" s="29">
+        <v>3</v>
+      </c>
+      <c r="BF8" s="29">
+        <v>1680</v>
+      </c>
+      <c r="BG8" s="29">
+        <v>70</v>
+      </c>
+      <c r="BH8" s="29">
+        <v>1.4E-2</v>
+      </c>
+      <c r="BI8" s="29">
         <v>200</v>
       </c>
-      <c r="AX7" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="AY7" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="AZ7" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="BA7" s="29" t="s">
-        <v>204</v>
-      </c>
-      <c r="BB7" s="29" t="s">
-        <v>205</v>
-      </c>
-      <c r="BC7" s="50" t="s">
-        <v>282</v>
-      </c>
-      <c r="BD7" s="29" t="s">
-        <v>206</v>
-      </c>
-      <c r="BE7" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="BF7" s="29" t="s">
-        <v>207</v>
-      </c>
-      <c r="BG7" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="BH7" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="BI7" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="BJ7" s="29" t="s">
-        <v>211</v>
-      </c>
-      <c r="BK7" s="29" t="s">
-        <v>212</v>
-      </c>
-      <c r="BL7" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="BM7" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="BN7" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="BO7" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="BP7" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="BQ7" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="BR7" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="BS7" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="BT7" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="BU7" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="BV7" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="BW7" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="BX7" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="BY7" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="BZ7" s="28" t="s">
-        <v>227</v>
-      </c>
-      <c r="CA7" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="CB7" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="CC7" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="CD7" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="CE7" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="CF7" s="29" t="s">
-        <v>233</v>
-      </c>
-      <c r="CG7" s="29" t="s">
-        <v>234</v>
-      </c>
-      <c r="CH7" s="29" t="s">
-        <v>235</v>
-      </c>
-      <c r="CI7" s="29" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="8" spans="1:87" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="B8" s="46" t="s">
-        <v>268</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>244</v>
-      </c>
-      <c r="D8" s="41" t="s">
-        <v>260</v>
-      </c>
-      <c r="E8" s="29" t="s">
-        <v>245</v>
-      </c>
-      <c r="F8" s="29" t="s">
-        <v>237</v>
-      </c>
-      <c r="G8" s="50" t="s">
-        <v>278</v>
-      </c>
-      <c r="I8" s="43"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="29" t="s">
-        <v>269</v>
-      </c>
-      <c r="M8" s="29"/>
-      <c r="N8" s="35" t="s">
-        <v>270</v>
-      </c>
-      <c r="O8" s="35" t="s">
-        <v>271</v>
-      </c>
-      <c r="P8" s="29" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q8" s="29" t="s">
-        <v>239</v>
-      </c>
-      <c r="R8" s="35" t="s">
-        <v>246</v>
-      </c>
-      <c r="S8" s="29" t="s">
-        <v>240</v>
-      </c>
-      <c r="T8" s="30"/>
-      <c r="U8" s="30"/>
-      <c r="V8" s="31"/>
-      <c r="W8" s="31"/>
-      <c r="X8" s="36">
-        <v>44177</v>
-      </c>
-      <c r="Y8" s="42" t="s">
-        <v>261</v>
-      </c>
-      <c r="Z8" s="30">
-        <v>2.169024E-2</v>
-      </c>
-      <c r="AA8" s="30">
-        <v>2.169024E-2</v>
-      </c>
-      <c r="AB8" s="30">
-        <v>2.169024E-2</v>
-      </c>
-      <c r="AC8" s="30">
-        <v>8</v>
-      </c>
-      <c r="AD8" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="AE8" s="29" t="s">
-        <v>241</v>
-      </c>
-      <c r="AF8" s="35"/>
-      <c r="AG8" s="35" t="s">
-        <v>255</v>
-      </c>
-      <c r="AH8" s="35" t="s">
-        <v>261</v>
-      </c>
-      <c r="AI8" s="36">
-        <v>44177</v>
-      </c>
-      <c r="AJ8" s="35" t="s">
-        <v>255</v>
-      </c>
-      <c r="AK8" s="35" t="s">
-        <v>255</v>
-      </c>
-      <c r="AL8" s="29">
+      <c r="BJ8" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="BK8" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="BL8" s="34" t="s">
+        <v>250</v>
+      </c>
+      <c r="BM8" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="BN8" s="28">
         <v>88</v>
       </c>
-      <c r="AM8" s="29">
-        <v>88</v>
-      </c>
-      <c r="AN8" s="35" t="s">
-        <v>255</v>
-      </c>
-      <c r="AO8" s="35" t="s">
-        <v>255</v>
-      </c>
-      <c r="AP8" s="35" t="s">
-        <v>255</v>
-      </c>
-      <c r="AQ8" s="35" t="s">
-        <v>242</v>
-      </c>
-      <c r="AR8" s="37" t="s">
-        <v>247</v>
-      </c>
-      <c r="AS8" s="29" t="s">
-        <v>242</v>
-      </c>
-      <c r="AT8" s="29" t="s">
-        <v>249</v>
-      </c>
-      <c r="AU8" s="29" t="s">
-        <v>250</v>
-      </c>
-      <c r="AV8" s="29"/>
-      <c r="AW8" s="35" t="s">
-        <v>251</v>
-      </c>
-      <c r="AX8" s="29" t="s">
-        <v>279</v>
-      </c>
-      <c r="AY8" s="39" t="s">
-        <v>252</v>
-      </c>
-      <c r="AZ8" s="40">
-        <v>44500</v>
-      </c>
-      <c r="BA8" s="30">
-        <v>0.200098</v>
-      </c>
-      <c r="BB8" s="29" t="s">
-        <v>243</v>
-      </c>
-      <c r="BC8" s="50" t="s">
-        <v>283</v>
-      </c>
-      <c r="BD8" s="29" t="s">
-        <v>242</v>
-      </c>
-      <c r="BE8">
-        <v>888</v>
-      </c>
-      <c r="BF8" s="30">
-        <v>3</v>
-      </c>
-      <c r="BG8" s="30">
-        <v>1680</v>
-      </c>
-      <c r="BH8" s="30">
-        <v>70</v>
-      </c>
-      <c r="BI8" s="30">
-        <v>1.4E-2</v>
-      </c>
-      <c r="BJ8" s="30">
-        <v>200</v>
-      </c>
-      <c r="BK8" s="35" t="s">
-        <v>255</v>
-      </c>
-      <c r="BL8" s="35" t="s">
-        <v>255</v>
-      </c>
-      <c r="BM8" s="35" t="s">
-        <v>253</v>
-      </c>
-      <c r="BN8" s="29" t="s">
-        <v>254</v>
-      </c>
-      <c r="BO8" s="29">
-        <v>88</v>
+      <c r="BO8">
+        <v>1</v>
       </c>
       <c r="BP8">
         <v>1</v>
@@ -3034,400 +3003,394 @@
       <c r="BQ8">
         <v>1</v>
       </c>
-      <c r="BR8">
+      <c r="BR8" t="s">
+        <v>253</v>
+      </c>
+      <c r="BS8" t="s">
+        <v>252</v>
+      </c>
+      <c r="BT8" t="s">
+        <v>252</v>
+      </c>
+      <c r="BU8" t="s">
+        <v>252</v>
+      </c>
+      <c r="BV8">
+        <v>88</v>
+      </c>
+      <c r="BW8" t="s">
+        <v>240</v>
+      </c>
+      <c r="BX8" t="s">
+        <v>240</v>
+      </c>
+      <c r="BY8" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="BZ8" s="34"/>
+      <c r="CA8" s="34"/>
+      <c r="CB8" s="34"/>
+      <c r="CC8" s="34"/>
+      <c r="CD8" s="34"/>
+      <c r="CE8" s="28" t="s">
+        <v>276</v>
+      </c>
+      <c r="CF8" s="35">
+        <v>44500</v>
+      </c>
+      <c r="CG8" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="CH8" s="34" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="9" spans="1:86" ht="17" x14ac:dyDescent="0.2">
+      <c r="A9" s="32"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="34" t="s">
+        <v>245</v>
+      </c>
+      <c r="D9" s="40" t="s">
+        <v>257</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="F9" s="49" t="s">
+        <v>274</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>242</v>
+      </c>
+      <c r="H9" s="42"/>
+      <c r="I9" s="33"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="34" t="s">
+        <v>267</v>
+      </c>
+      <c r="N9" s="34" t="s">
+        <v>268</v>
+      </c>
+      <c r="O9" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="P9" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q9" s="34" t="s">
+        <v>243</v>
+      </c>
+      <c r="R9" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="S9" s="29"/>
+      <c r="T9" s="29"/>
+      <c r="U9" s="31"/>
+      <c r="V9" s="31"/>
+      <c r="W9" s="35">
+        <v>44177</v>
+      </c>
+      <c r="X9" s="31"/>
+      <c r="Y9" s="29">
+        <v>2.725352E-2</v>
+      </c>
+      <c r="Z9" s="29">
+        <v>2.725352E-2</v>
+      </c>
+      <c r="AA9" s="29">
+        <v>2.725352E-2</v>
+      </c>
+      <c r="AB9" s="29">
+        <v>8</v>
+      </c>
+      <c r="AC9" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD9" s="28" t="s">
+        <v>239</v>
+      </c>
+      <c r="AE9" s="34"/>
+      <c r="AF9" s="28"/>
+      <c r="AG9" s="28"/>
+      <c r="AH9" s="28"/>
+      <c r="AI9" s="28"/>
+      <c r="AJ9" s="28"/>
+      <c r="AK9" s="28"/>
+      <c r="AL9" s="28"/>
+      <c r="AM9" s="28"/>
+      <c r="AN9" s="28"/>
+      <c r="AO9" s="28"/>
+      <c r="AP9" s="34" t="s">
+        <v>240</v>
+      </c>
+      <c r="AQ9" s="36" t="s">
+        <v>244</v>
+      </c>
+      <c r="AR9" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="AS9" s="28" t="s">
+        <v>246</v>
+      </c>
+      <c r="AT9" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="AU9" s="28"/>
+      <c r="AV9" s="34" t="s">
+        <v>248</v>
+      </c>
+      <c r="AW9" s="28" t="s">
+        <v>276</v>
+      </c>
+      <c r="AX9" s="38" t="s">
+        <v>249</v>
+      </c>
+      <c r="AY9" s="39">
+        <v>44501</v>
+      </c>
+      <c r="AZ9" s="29">
+        <v>0.200098</v>
+      </c>
+      <c r="BA9" s="28" t="s">
+        <v>241</v>
+      </c>
+      <c r="BB9" s="49" t="s">
+        <v>280</v>
+      </c>
+      <c r="BC9" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="BD9">
+        <v>888</v>
+      </c>
+      <c r="BE9" s="29">
+        <v>3</v>
+      </c>
+      <c r="BF9" s="29">
+        <v>1680</v>
+      </c>
+      <c r="BG9" s="29">
+        <v>70</v>
+      </c>
+      <c r="BH9" s="29">
+        <v>1.54E-2</v>
+      </c>
+      <c r="BI9" s="29">
+        <v>220</v>
+      </c>
+      <c r="BJ9" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="BK9" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="BL9" s="34" t="s">
+        <v>250</v>
+      </c>
+      <c r="BM9" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="BN9" s="28">
+        <v>89</v>
+      </c>
+      <c r="BR9" t="s">
+        <v>253</v>
+      </c>
+      <c r="BS9" t="s">
+        <v>252</v>
+      </c>
+      <c r="BT9" t="s">
+        <v>252</v>
+      </c>
+      <c r="BU9" t="s">
+        <v>252</v>
+      </c>
+      <c r="BV9">
+        <v>89</v>
+      </c>
+      <c r="BW9" t="s">
+        <v>240</v>
+      </c>
+      <c r="BX9" t="s">
+        <v>240</v>
+      </c>
+      <c r="BY9" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="BZ9" s="34"/>
+      <c r="CA9" s="34"/>
+      <c r="CB9" s="34"/>
+      <c r="CC9" s="34"/>
+      <c r="CD9" s="34"/>
+      <c r="CE9" s="28" t="s">
+        <v>276</v>
+      </c>
+      <c r="CF9" s="35">
+        <v>44501</v>
+      </c>
+      <c r="CG9" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="CH9" s="34" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="10" spans="1:86" ht="17" x14ac:dyDescent="0.2">
+      <c r="A10" s="32"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="28" t="s">
+        <v>242</v>
+      </c>
+      <c r="D10" s="40" t="s">
+        <v>257</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="F10" s="49" t="s">
+        <v>274</v>
+      </c>
+      <c r="H10" s="42"/>
+      <c r="I10" s="33" t="s">
+        <v>261</v>
+      </c>
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="34" t="s">
+        <v>267</v>
+      </c>
+      <c r="N10" s="34" t="s">
+        <v>268</v>
+      </c>
+      <c r="O10" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="P10" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q10" s="34" t="s">
+        <v>243</v>
+      </c>
+      <c r="R10" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="S10" s="29"/>
+      <c r="T10" s="29"/>
+      <c r="U10" s="30"/>
+      <c r="V10" s="30"/>
+      <c r="W10" s="35">
+        <v>44177</v>
+      </c>
+      <c r="X10" s="30"/>
+      <c r="Y10" s="29">
+        <v>2.169024E-2</v>
+      </c>
+      <c r="Z10" s="29">
+        <v>2.169024E-2</v>
+      </c>
+      <c r="AA10" s="29">
+        <v>2.169024E-2</v>
+      </c>
+      <c r="AB10" s="29">
+        <v>8</v>
+      </c>
+      <c r="AC10" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD10" s="28" t="s">
+        <v>239</v>
+      </c>
+      <c r="AE10" s="34"/>
+      <c r="AF10" s="28"/>
+      <c r="AG10" s="28"/>
+      <c r="AH10" s="35">
+        <v>44177</v>
+      </c>
+      <c r="AI10" s="28"/>
+      <c r="AJ10" s="28"/>
+      <c r="AK10" s="28"/>
+      <c r="AL10" s="28"/>
+      <c r="AM10" s="28"/>
+      <c r="AN10" s="28"/>
+      <c r="AO10" s="28"/>
+      <c r="AP10" s="34" t="s">
+        <v>240</v>
+      </c>
+      <c r="AQ10" s="36" t="s">
+        <v>244</v>
+      </c>
+      <c r="AR10" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="AS10" s="28" t="s">
+        <v>259</v>
+      </c>
+      <c r="AT10" s="28" t="s">
+        <v>260</v>
+      </c>
+      <c r="AU10" s="28"/>
+      <c r="AV10" s="34" t="s">
+        <v>248</v>
+      </c>
+      <c r="AW10" s="28" t="s">
+        <v>276</v>
+      </c>
+      <c r="AX10" s="38" t="s">
+        <v>249</v>
+      </c>
+      <c r="AY10" s="39">
+        <v>44502</v>
+      </c>
+      <c r="AZ10" s="29">
+        <v>0.200098</v>
+      </c>
+      <c r="BA10" s="28" t="s">
+        <v>241</v>
+      </c>
+      <c r="BB10" s="49" t="s">
+        <v>280</v>
+      </c>
+      <c r="BC10" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="BD10">
+        <v>888</v>
+      </c>
+      <c r="BE10" s="29">
+        <v>3</v>
+      </c>
+      <c r="BF10" s="29">
+        <v>1680</v>
+      </c>
+      <c r="BG10" s="29">
+        <v>70</v>
+      </c>
+      <c r="BH10" s="29">
+        <v>1.4E-2</v>
+      </c>
+      <c r="BI10" s="29">
+        <v>200</v>
+      </c>
+      <c r="BJ10" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="BK10" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="BL10" s="34" t="s">
+        <v>250</v>
+      </c>
+      <c r="BM10" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="BN10" s="28">
+        <v>90</v>
+      </c>
+      <c r="BO10">
         <v>1</v>
-      </c>
-      <c r="BS8" t="s">
-        <v>256</v>
-      </c>
-      <c r="BT8" t="s">
-        <v>255</v>
-      </c>
-      <c r="BU8" t="s">
-        <v>255</v>
-      </c>
-      <c r="BV8" t="s">
-        <v>255</v>
-      </c>
-      <c r="BW8">
-        <v>88</v>
-      </c>
-      <c r="BX8" t="s">
-        <v>242</v>
-      </c>
-      <c r="BY8" t="s">
-        <v>242</v>
-      </c>
-      <c r="BZ8" s="29" t="s">
-        <v>257</v>
-      </c>
-      <c r="CA8" s="35"/>
-      <c r="CB8" s="35"/>
-      <c r="CC8" s="35"/>
-      <c r="CD8" s="35"/>
-      <c r="CE8" s="35"/>
-      <c r="CF8" s="29" t="s">
-        <v>279</v>
-      </c>
-      <c r="CG8" s="36">
-        <v>44500</v>
-      </c>
-      <c r="CH8" s="35" t="s">
-        <v>258</v>
-      </c>
-      <c r="CI8" s="35" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="9" spans="1:87" ht="17" x14ac:dyDescent="0.2">
-      <c r="A9" s="33"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="35" t="s">
-        <v>248</v>
-      </c>
-      <c r="D9" s="41" t="s">
-        <v>260</v>
-      </c>
-      <c r="E9" s="29" t="s">
-        <v>245</v>
-      </c>
-      <c r="F9" s="29" t="s">
-        <v>237</v>
-      </c>
-      <c r="G9" s="50" t="s">
-        <v>277</v>
-      </c>
-      <c r="H9" s="29" t="s">
-        <v>244</v>
-      </c>
-      <c r="I9" s="43"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="35" t="s">
-        <v>270</v>
-      </c>
-      <c r="O9" s="35" t="s">
-        <v>271</v>
-      </c>
-      <c r="P9" s="29" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q9" s="29" t="s">
-        <v>239</v>
-      </c>
-      <c r="R9" s="35" t="s">
-        <v>246</v>
-      </c>
-      <c r="S9" s="29" t="s">
-        <v>240</v>
-      </c>
-      <c r="T9" s="30"/>
-      <c r="U9" s="30"/>
-      <c r="V9" s="32"/>
-      <c r="W9" s="32"/>
-      <c r="X9" s="36">
-        <v>44177</v>
-      </c>
-      <c r="Y9" s="32"/>
-      <c r="Z9" s="30">
-        <v>2.725352E-2</v>
-      </c>
-      <c r="AA9" s="30">
-        <v>2.725352E-2</v>
-      </c>
-      <c r="AB9" s="30">
-        <v>2.725352E-2</v>
-      </c>
-      <c r="AC9" s="30">
-        <v>8</v>
-      </c>
-      <c r="AD9" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="AE9" s="29" t="s">
-        <v>241</v>
-      </c>
-      <c r="AF9" s="35"/>
-      <c r="AG9" s="29"/>
-      <c r="AH9" s="29"/>
-      <c r="AI9" s="29"/>
-      <c r="AJ9" s="29"/>
-      <c r="AK9" s="29"/>
-      <c r="AL9" s="29"/>
-      <c r="AM9" s="29"/>
-      <c r="AN9" s="29"/>
-      <c r="AO9" s="29"/>
-      <c r="AP9" s="29"/>
-      <c r="AQ9" s="35" t="s">
-        <v>242</v>
-      </c>
-      <c r="AR9" s="37" t="s">
-        <v>247</v>
-      </c>
-      <c r="AS9" s="29" t="s">
-        <v>242</v>
-      </c>
-      <c r="AT9" s="29" t="s">
-        <v>249</v>
-      </c>
-      <c r="AU9" s="29" t="s">
-        <v>250</v>
-      </c>
-      <c r="AV9" s="29"/>
-      <c r="AW9" s="35" t="s">
-        <v>251</v>
-      </c>
-      <c r="AX9" s="29" t="s">
-        <v>279</v>
-      </c>
-      <c r="AY9" s="39" t="s">
-        <v>252</v>
-      </c>
-      <c r="AZ9" s="40">
-        <v>44501</v>
-      </c>
-      <c r="BA9" s="30">
-        <v>0.200098</v>
-      </c>
-      <c r="BB9" s="29" t="s">
-        <v>243</v>
-      </c>
-      <c r="BC9" s="50" t="s">
-        <v>283</v>
-      </c>
-      <c r="BD9" s="29" t="s">
-        <v>242</v>
-      </c>
-      <c r="BE9">
-        <v>888</v>
-      </c>
-      <c r="BF9" s="30">
-        <v>3</v>
-      </c>
-      <c r="BG9" s="30">
-        <v>1680</v>
-      </c>
-      <c r="BH9" s="30">
-        <v>70</v>
-      </c>
-      <c r="BI9" s="30">
-        <v>1.54E-2</v>
-      </c>
-      <c r="BJ9" s="30">
-        <v>220</v>
-      </c>
-      <c r="BK9" s="35" t="s">
-        <v>255</v>
-      </c>
-      <c r="BL9" s="35" t="s">
-        <v>255</v>
-      </c>
-      <c r="BM9" s="35" t="s">
-        <v>253</v>
-      </c>
-      <c r="BN9" s="29" t="s">
-        <v>254</v>
-      </c>
-      <c r="BO9" s="29">
-        <v>89</v>
-      </c>
-      <c r="BS9" t="s">
-        <v>256</v>
-      </c>
-      <c r="BT9" t="s">
-        <v>255</v>
-      </c>
-      <c r="BU9" t="s">
-        <v>255</v>
-      </c>
-      <c r="BV9" t="s">
-        <v>255</v>
-      </c>
-      <c r="BW9">
-        <v>89</v>
-      </c>
-      <c r="BX9" t="s">
-        <v>242</v>
-      </c>
-      <c r="BY9" t="s">
-        <v>242</v>
-      </c>
-      <c r="BZ9" s="29" t="s">
-        <v>257</v>
-      </c>
-      <c r="CA9" s="35"/>
-      <c r="CB9" s="35"/>
-      <c r="CC9" s="35"/>
-      <c r="CD9" s="35"/>
-      <c r="CE9" s="35"/>
-      <c r="CF9" s="29" t="s">
-        <v>279</v>
-      </c>
-      <c r="CG9" s="36">
-        <v>44501</v>
-      </c>
-      <c r="CH9" s="35" t="s">
-        <v>258</v>
-      </c>
-      <c r="CI9" s="35" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="10" spans="1:87" ht="17" x14ac:dyDescent="0.2">
-      <c r="A10" s="33"/>
-      <c r="B10" s="33"/>
-      <c r="C10" s="29" t="s">
-        <v>244</v>
-      </c>
-      <c r="D10" s="41" t="s">
-        <v>260</v>
-      </c>
-      <c r="E10" s="29" t="s">
-        <v>245</v>
-      </c>
-      <c r="F10" s="29" t="s">
-        <v>237</v>
-      </c>
-      <c r="G10" s="50" t="s">
-        <v>277</v>
-      </c>
-      <c r="I10" s="43"/>
-      <c r="J10" s="34" t="s">
-        <v>264</v>
-      </c>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="35" t="s">
-        <v>270</v>
-      </c>
-      <c r="O10" s="35" t="s">
-        <v>271</v>
-      </c>
-      <c r="P10" s="29" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q10" s="29" t="s">
-        <v>239</v>
-      </c>
-      <c r="R10" s="35" t="s">
-        <v>246</v>
-      </c>
-      <c r="S10" s="29" t="s">
-        <v>240</v>
-      </c>
-      <c r="T10" s="30"/>
-      <c r="U10" s="30"/>
-      <c r="V10" s="31"/>
-      <c r="W10" s="31"/>
-      <c r="X10" s="36">
-        <v>44177</v>
-      </c>
-      <c r="Y10" s="31"/>
-      <c r="Z10" s="30">
-        <v>2.169024E-2</v>
-      </c>
-      <c r="AA10" s="30">
-        <v>2.169024E-2</v>
-      </c>
-      <c r="AB10" s="30">
-        <v>2.169024E-2</v>
-      </c>
-      <c r="AC10" s="30">
-        <v>8</v>
-      </c>
-      <c r="AD10" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="AE10" s="29" t="s">
-        <v>241</v>
-      </c>
-      <c r="AF10" s="35"/>
-      <c r="AG10" s="29"/>
-      <c r="AH10" s="29"/>
-      <c r="AI10" s="36">
-        <v>44177</v>
-      </c>
-      <c r="AJ10" s="29"/>
-      <c r="AK10" s="29"/>
-      <c r="AL10" s="29"/>
-      <c r="AM10" s="29"/>
-      <c r="AN10" s="29"/>
-      <c r="AO10" s="29"/>
-      <c r="AP10" s="29"/>
-      <c r="AQ10" s="35" t="s">
-        <v>242</v>
-      </c>
-      <c r="AR10" s="37" t="s">
-        <v>247</v>
-      </c>
-      <c r="AS10" s="29" t="s">
-        <v>242</v>
-      </c>
-      <c r="AT10" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="AU10" s="29" t="s">
-        <v>263</v>
-      </c>
-      <c r="AV10" s="29"/>
-      <c r="AW10" s="35" t="s">
-        <v>251</v>
-      </c>
-      <c r="AX10" s="29" t="s">
-        <v>279</v>
-      </c>
-      <c r="AY10" s="39" t="s">
-        <v>252</v>
-      </c>
-      <c r="AZ10" s="40">
-        <v>44502</v>
-      </c>
-      <c r="BA10" s="30">
-        <v>0.200098</v>
-      </c>
-      <c r="BB10" s="29" t="s">
-        <v>243</v>
-      </c>
-      <c r="BC10" s="50" t="s">
-        <v>283</v>
-      </c>
-      <c r="BD10" s="29" t="s">
-        <v>242</v>
-      </c>
-      <c r="BE10">
-        <v>888</v>
-      </c>
-      <c r="BF10" s="30">
-        <v>3</v>
-      </c>
-      <c r="BG10" s="30">
-        <v>1680</v>
-      </c>
-      <c r="BH10" s="30">
-        <v>70</v>
-      </c>
-      <c r="BI10" s="30">
-        <v>1.4E-2</v>
-      </c>
-      <c r="BJ10" s="30">
-        <v>200</v>
-      </c>
-      <c r="BK10" s="35" t="s">
-        <v>255</v>
-      </c>
-      <c r="BL10" s="35" t="s">
-        <v>255</v>
-      </c>
-      <c r="BM10" s="35" t="s">
-        <v>253</v>
-      </c>
-      <c r="BN10" s="29" t="s">
-        <v>254</v>
-      </c>
-      <c r="BO10" s="29">
-        <v>90</v>
       </c>
       <c r="BP10">
         <v>1</v>
@@ -3435,49 +3398,46 @@
       <c r="BQ10">
         <v>1</v>
       </c>
-      <c r="BR10">
-        <v>1</v>
+      <c r="BR10" t="s">
+        <v>253</v>
       </c>
       <c r="BS10" t="s">
+        <v>252</v>
+      </c>
+      <c r="BT10" t="s">
+        <v>252</v>
+      </c>
+      <c r="BU10" t="s">
+        <v>252</v>
+      </c>
+      <c r="BV10">
+        <v>90</v>
+      </c>
+      <c r="BW10" t="s">
+        <v>240</v>
+      </c>
+      <c r="BX10" t="s">
+        <v>240</v>
+      </c>
+      <c r="BY10" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="BZ10" s="34"/>
+      <c r="CA10" s="34"/>
+      <c r="CB10" s="34"/>
+      <c r="CC10" s="34"/>
+      <c r="CD10" s="34"/>
+      <c r="CE10" s="28" t="s">
+        <v>276</v>
+      </c>
+      <c r="CF10" s="35">
+        <v>44502</v>
+      </c>
+      <c r="CG10" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="CH10" s="34" t="s">
         <v>256</v>
-      </c>
-      <c r="BT10" t="s">
-        <v>255</v>
-      </c>
-      <c r="BU10" t="s">
-        <v>255</v>
-      </c>
-      <c r="BV10" t="s">
-        <v>255</v>
-      </c>
-      <c r="BW10">
-        <v>90</v>
-      </c>
-      <c r="BX10" t="s">
-        <v>242</v>
-      </c>
-      <c r="BY10" t="s">
-        <v>242</v>
-      </c>
-      <c r="BZ10" s="29" t="s">
-        <v>257</v>
-      </c>
-      <c r="CA10" s="35"/>
-      <c r="CB10" s="35"/>
-      <c r="CC10" s="35"/>
-      <c r="CD10" s="35"/>
-      <c r="CE10" s="35"/>
-      <c r="CF10" s="29" t="s">
-        <v>279</v>
-      </c>
-      <c r="CG10" s="36">
-        <v>44502</v>
-      </c>
-      <c r="CH10" s="35" t="s">
-        <v>258</v>
-      </c>
-      <c r="CI10" s="35" t="s">
-        <v>259</v>
       </c>
     </row>
   </sheetData>

--- a/spec/fixtures/batch_submission_manifest_object_test.xlsx
+++ b/spec/fixtures/batch_submission_manifest_object_test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10410"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/smc101/vagrant/morphosource-vagrant/MorphoSource_SF/spec/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B671E6-D420-0C44-B9DC-22AC65869CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D80F4E03-CB2D-7B46-92D9-BAE9F1B3176C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="280">
   <si>
     <t>Field Section</t>
   </si>
@@ -867,9 +867,6 @@
   </si>
   <si>
     <t>Scolomastax sahlsteini</t>
-  </si>
-  <si>
-    <t>000200015</t>
   </si>
   <si>
     <t>Field Name (Machine Readable)</t>
@@ -1781,13 +1778,13 @@
         <v>53</v>
       </c>
       <c r="BB2" s="50" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="BC2" s="6" t="s">
         <v>54</v>
       </c>
       <c r="BD2" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="BE2" s="6" t="s">
         <v>55</v>
@@ -1895,7 +1892,7 @@
       </c>
       <c r="E3" s="9"/>
       <c r="F3" s="48" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>85</v>
@@ -2451,7 +2448,7 @@
         <v>142</v>
       </c>
       <c r="F6" s="46" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
@@ -2511,7 +2508,7 @@
       <c r="AZ6" s="6"/>
       <c r="BA6" s="6"/>
       <c r="BB6" s="51" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="BC6" s="6"/>
       <c r="BD6" s="6"/>
@@ -2560,10 +2557,10 @@
     </row>
     <row r="7" spans="1:86" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="43" t="s">
+        <v>261</v>
+      </c>
+      <c r="B7" s="44" t="s">
         <v>262</v>
-      </c>
-      <c r="B7" s="44" t="s">
-        <v>263</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>154</v>
@@ -2575,7 +2572,7 @@
         <v>156</v>
       </c>
       <c r="F7" s="46" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>157</v>
@@ -2719,13 +2716,13 @@
         <v>203</v>
       </c>
       <c r="BB7" s="49" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="BC7" s="28" t="s">
         <v>204</v>
       </c>
       <c r="BD7" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="BE7" s="28" t="s">
         <v>205</v>
@@ -2820,10 +2817,10 @@
     </row>
     <row r="8" spans="1:86" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="43" t="s">
+        <v>263</v>
+      </c>
+      <c r="B8" s="45" t="s">
         <v>264</v>
-      </c>
-      <c r="B8" s="45" t="s">
-        <v>265</v>
       </c>
       <c r="C8" s="28" t="s">
         <v>242</v>
@@ -2835,20 +2832,20 @@
         <v>235</v>
       </c>
       <c r="F8" s="49" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H8" s="42"/>
       <c r="I8" s="33"/>
       <c r="J8" s="28"/>
       <c r="K8" s="28" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L8" s="28"/>
       <c r="M8" s="34" t="s">
+        <v>266</v>
+      </c>
+      <c r="N8" s="34" t="s">
         <v>267</v>
-      </c>
-      <c r="N8" s="34" t="s">
-        <v>268</v>
       </c>
       <c r="O8" s="28" t="s">
         <v>236</v>
@@ -2941,7 +2938,7 @@
         <v>248</v>
       </c>
       <c r="AW8" s="28" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AX8" s="38" t="s">
         <v>249</v>
@@ -2956,7 +2953,7 @@
         <v>241</v>
       </c>
       <c r="BB8" s="49" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="BC8" s="28" t="s">
         <v>240</v>
@@ -3033,7 +3030,7 @@
       <c r="CC8" s="34"/>
       <c r="CD8" s="34"/>
       <c r="CE8" s="28" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="CF8" s="35">
         <v>44500</v>
@@ -3058,7 +3055,7 @@
         <v>235</v>
       </c>
       <c r="F9" s="49" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G9" s="28" t="s">
         <v>242</v>
@@ -3069,10 +3066,10 @@
       <c r="K9" s="28"/>
       <c r="L9" s="28"/>
       <c r="M9" s="34" t="s">
+        <v>266</v>
+      </c>
+      <c r="N9" s="34" t="s">
         <v>267</v>
-      </c>
-      <c r="N9" s="34" t="s">
-        <v>268</v>
       </c>
       <c r="O9" s="28" t="s">
         <v>236</v>
@@ -3143,7 +3140,7 @@
         <v>248</v>
       </c>
       <c r="AW9" s="28" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AX9" s="38" t="s">
         <v>249</v>
@@ -3158,7 +3155,7 @@
         <v>241</v>
       </c>
       <c r="BB9" s="49" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="BC9" s="28" t="s">
         <v>240</v>
@@ -3226,7 +3223,7 @@
       <c r="CC9" s="34"/>
       <c r="CD9" s="34"/>
       <c r="CE9" s="28" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="CF9" s="35">
         <v>44501</v>
@@ -3251,19 +3248,17 @@
         <v>235</v>
       </c>
       <c r="F10" s="49" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H10" s="42"/>
-      <c r="I10" s="33" t="s">
-        <v>261</v>
-      </c>
+      <c r="I10" s="33"/>
       <c r="K10" s="28"/>
       <c r="L10" s="28"/>
       <c r="M10" s="34" t="s">
+        <v>266</v>
+      </c>
+      <c r="N10" s="34" t="s">
         <v>267</v>
-      </c>
-      <c r="N10" s="34" t="s">
-        <v>268</v>
       </c>
       <c r="O10" s="28" t="s">
         <v>236</v>
@@ -3336,7 +3331,7 @@
         <v>248</v>
       </c>
       <c r="AW10" s="28" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AX10" s="38" t="s">
         <v>249</v>
@@ -3351,7 +3346,7 @@
         <v>241</v>
       </c>
       <c r="BB10" s="49" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="BC10" s="28" t="s">
         <v>240</v>
@@ -3428,7 +3423,7 @@
       <c r="CC10" s="34"/>
       <c r="CD10" s="34"/>
       <c r="CE10" s="28" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="CF10" s="35">
         <v>44502</v>

--- a/spec/fixtures/batch_submission_manifest_object_test.xlsx
+++ b/spec/fixtures/batch_submission_manifest_object_test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/smc101/vagrant/morphosource-vagrant/MorphoSource_SF/spec/fixtures/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/smc101/vagrant/morphosource-vagrant/MorphoSource/spec/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D80F4E03-CB2D-7B46-92D9-BAE9F1B3176C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC0F9CEC-4C1C-D849-BF1A-EA7DE4C206DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="278">
   <si>
     <t>Field Section</t>
   </si>
@@ -278,9 +278,6 @@
   </si>
   <si>
     <t>Ignore this in most use cases! Parent media filename OR URL endpoint link for downloading parent media file</t>
-  </si>
-  <si>
-    <t>iDigBio UUID for specimen record</t>
   </si>
   <si>
     <t>Collection code modifier (e.g., "VP-", typically designates a sub-collection within a repository. Not a universal element because not all repositories have sub-collections. However, this field is critical when applicable to avoid confusing specimens from different sub-collections. Please make sure you do not incorrectly omit a collection code fromt the specimen identifier</t>
@@ -564,9 +561,6 @@
   </si>
   <si>
     <t>biological_specimen.ms_id</t>
-  </si>
-  <si>
-    <t>biological_specimen.idigbio_uuid</t>
   </si>
   <si>
     <t>biological_specimen.occurrence_id</t>
@@ -1077,14 +1071,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+  <cellXfs count="45">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1097,16 +1091,14 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1116,24 +1108,22 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1144,19 +1134,16 @@
     <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1373,7 +1360,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06ED7EC9-286B-1D49-A57D-A989376D77CC}">
-  <dimension ref="A1:CH10"/>
+  <dimension ref="A1:CG10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="28.6640625" customWidth="1"/>
@@ -1381,7 +1368,7 @@
     <col min="7" max="7" width="21.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:86" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:85" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1397,7 +1384,7 @@
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="46" t="s">
+      <c r="F1" s="42" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="5" t="s">
@@ -1419,8 +1406,8 @@
       <c r="M1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="11" t="s">
-        <v>3</v>
+      <c r="N1" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>4</v>
@@ -1450,7 +1437,7 @@
         <v>4</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y1" s="2" t="s">
         <v>5</v>
@@ -1465,52 +1452,52 @@
         <v>5</v>
       </c>
       <c r="AC1" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AF1" s="20" t="s">
+      <c r="AE1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="AG1" s="20" t="s">
+      <c r="AF1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="AH1" s="20" t="s">
+      <c r="AG1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="AI1" s="20" t="s">
+      <c r="AH1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="AJ1" s="20" t="s">
+      <c r="AI1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="AK1" s="20" t="s">
+      <c r="AJ1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="20" t="s">
+      <c r="AK1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="AM1" s="20" t="s">
+      <c r="AL1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="AN1" s="20" t="s">
+      <c r="AM1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="AO1" s="20" t="s">
+      <c r="AN1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="AP1" s="20" t="s">
+      <c r="AO1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="AQ1" s="20" t="s">
+      <c r="AP1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="AR1" s="20" t="s">
+      <c r="AQ1" s="14" t="s">
         <v>8</v>
+      </c>
+      <c r="AR1" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="AS1" s="3" t="s">
         <v>9</v>
@@ -1518,8 +1505,8 @@
       <c r="AT1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="AU1" s="3" t="s">
-        <v>9</v>
+      <c r="AU1" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="AV1" s="6" t="s">
         <v>10</v>
@@ -1531,7 +1518,7 @@
         <v>10</v>
       </c>
       <c r="AY1" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ1" s="6" t="s">
         <v>11</v>
@@ -1539,7 +1526,7 @@
       <c r="BA1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="BB1" s="50" t="s">
+      <c r="BB1" s="6" t="s">
         <v>11</v>
       </c>
       <c r="BC1" s="6" t="s">
@@ -1609,13 +1596,13 @@
         <v>11</v>
       </c>
       <c r="BY1" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BZ1" s="6" t="s">
         <v>12</v>
       </c>
       <c r="CA1" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CB1" s="6" t="s">
         <v>13</v>
@@ -1623,23 +1610,20 @@
       <c r="CC1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="CD1" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="CE1" s="23" t="s">
+      <c r="CD1" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="CF1" s="23" t="s">
+      <c r="CE1" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="CG1" s="23" t="s">
+      <c r="CF1" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="CH1" s="23" t="s">
+      <c r="CG1" s="20" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:86" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:85" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>15</v>
       </c>
@@ -1649,7 +1633,7 @@
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
-      <c r="F2" s="47"/>
+      <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
       <c r="I2" s="11" t="s">
@@ -1659,225 +1643,224 @@
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
       <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
+      <c r="N2" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="O2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE2" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF2" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG2" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH2" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI2" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ2" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="AK2" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="AL2" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="AM2" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN2" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="AO2" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AP2" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="AQ2" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="AR2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AS2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AT2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AU2" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AV2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="T2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W2" s="2" t="s">
+      <c r="AW2" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AX2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="X2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AE2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF2" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG2" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH2" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="AI2" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ2" s="20" t="s">
+      <c r="AY2" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AZ2" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="BA2" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="BB2" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="BC2" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="BD2" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE2" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF2" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG2" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH2" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI2" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ2" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK2" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL2" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM2" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="BN2" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO2" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP2" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ2" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="BR2" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS2" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT2" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU2" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="BV2" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="BW2" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="BX2" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="BY2" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="BZ2" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="CA2" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="CB2" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="CC2" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="CD2" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="CE2" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="CF2" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="CG2" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="AK2" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="AL2" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="AM2" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="AN2" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="AO2" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="AP2" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="AQ2" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="AR2" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="AS2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AT2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="AU2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="AV2" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="AW2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="AX2" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="AY2" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="AZ2" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="BA2" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="BB2" s="50" t="s">
-        <v>276</v>
-      </c>
-      <c r="BC2" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD2" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="BE2" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="BF2" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="BG2" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="BH2" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="BI2" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="BJ2" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="BK2" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="BL2" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="BM2" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="BN2" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="BO2" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="BP2" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="BQ2" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="BR2" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="BS2" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="BT2" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="BU2" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="BV2" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="BW2" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="BX2" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="BY2" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="BZ2" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="CA2" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="CB2" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="CC2" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="CD2" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="CE2" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="CF2" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="CG2" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="CH2" s="23" t="s">
-        <v>39</v>
-      </c>
     </row>
-    <row r="3" spans="1:86" ht="139.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:85" ht="139.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="7" t="s">
         <v>81</v>
       </c>
@@ -1891,257 +1874,254 @@
         <v>84</v>
       </c>
       <c r="E3" s="9"/>
-      <c r="F3" s="48" t="s">
-        <v>270</v>
+      <c r="F3" s="43" t="s">
+        <v>268</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>85</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="10"/>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
       <c r="M3" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="N3" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="O3" s="12" t="s">
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
       <c r="R3" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="S3" s="12" t="s">
+      <c r="S3" s="2"/>
+      <c r="T3" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="T3" s="2"/>
-      <c r="U3" s="12" t="s">
+      <c r="U3" s="12"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="V3" s="12"/>
-      <c r="W3" s="2"/>
-      <c r="X3" s="2"/>
-      <c r="Y3" s="14" t="s">
+      <c r="Y3" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="Z3" s="14" t="s">
+      <c r="Z3" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="AA3" s="14" t="s">
+      <c r="AA3" s="12" t="s">
         <v>95</v>
       </c>
       <c r="AB3" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="AC3" s="12" t="s">
+      <c r="AC3" s="2"/>
+      <c r="AD3" s="2"/>
+      <c r="AE3" s="14"/>
+      <c r="AF3" s="14"/>
+      <c r="AG3" s="14"/>
+      <c r="AH3" s="14"/>
+      <c r="AI3" s="14"/>
+      <c r="AJ3" s="14"/>
+      <c r="AK3" s="14"/>
+      <c r="AL3" s="14"/>
+      <c r="AM3" s="14"/>
+      <c r="AN3" s="14"/>
+      <c r="AO3" s="14"/>
+      <c r="AP3" s="14"/>
+      <c r="AQ3" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="AD3" s="13"/>
-      <c r="AE3" s="2"/>
-      <c r="AF3" s="20"/>
-      <c r="AG3" s="20"/>
-      <c r="AH3" s="20"/>
-      <c r="AI3" s="20"/>
-      <c r="AJ3" s="15"/>
-      <c r="AK3" s="15"/>
-      <c r="AL3" s="15"/>
-      <c r="AM3" s="15"/>
-      <c r="AN3" s="15"/>
-      <c r="AO3" s="15"/>
-      <c r="AP3" s="15"/>
-      <c r="AQ3" s="15"/>
-      <c r="AR3" s="20" t="s">
+      <c r="AR3" s="3"/>
+      <c r="AS3" s="3"/>
+      <c r="AT3" s="3"/>
+      <c r="AU3" s="6"/>
+      <c r="AV3" s="6"/>
+      <c r="AW3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="AS3" s="16"/>
-      <c r="AT3" s="16"/>
-      <c r="AU3" s="16"/>
-      <c r="AV3" s="6"/>
-      <c r="AW3" s="6"/>
-      <c r="AX3" s="17" t="s">
+      <c r="AX3" s="15"/>
+      <c r="AY3" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="AY3" s="17"/>
-      <c r="AZ3" s="18" t="s">
+      <c r="AZ3" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="BA3" s="18" t="s">
+      <c r="BA3" s="16"/>
+      <c r="BB3" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="BB3" s="18"/>
-      <c r="BC3" s="18" t="s">
+      <c r="BC3" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="BD3" s="18" t="s">
+      <c r="BD3" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="BE3" s="18" t="s">
+      <c r="BE3" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="BF3" s="18" t="s">
+      <c r="BF3" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="BG3" s="18" t="s">
+      <c r="BG3" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="BH3" s="18" t="s">
+      <c r="BH3" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="BI3" s="18" t="s">
+      <c r="BI3" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="BJ3" s="18" t="s">
+      <c r="BJ3" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="BK3" s="17" t="s">
+      <c r="BK3" s="15"/>
+      <c r="BL3" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="BL3" s="17"/>
       <c r="BM3" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="BN3" s="19" t="s">
+      <c r="BN3" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="BO3" s="19" t="s">
+      <c r="BO3" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="BP3" s="19" t="s">
+      <c r="BP3" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="BQ3" s="19" t="s">
+      <c r="BQ3" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="BR3" s="17" t="s">
+      <c r="BR3" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="BS3" s="17" t="s">
+      <c r="BS3" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="BT3" s="17" t="s">
+      <c r="BT3" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="BU3" s="17" t="s">
+      <c r="BU3" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="BV3" s="17" t="s">
+      <c r="BV3" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="BW3" s="17" t="s">
+      <c r="BW3" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="BX3" s="17" t="s">
+      <c r="BX3" s="16"/>
+      <c r="BY3" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="BY3" s="18"/>
-      <c r="BZ3" s="17" t="s">
+      <c r="BZ3" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="CA3" s="17" t="s">
+      <c r="CA3" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="CB3" s="17" t="s">
+      <c r="CB3" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="CC3" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="CC3" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="CD3" s="18" t="s">
+      <c r="CD3" s="20"/>
+      <c r="CE3" s="20"/>
+      <c r="CF3" s="20"/>
+      <c r="CG3" s="20"/>
+    </row>
+    <row r="4" spans="1:85" x14ac:dyDescent="0.15">
+      <c r="A4" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="CE3" s="23"/>
-      <c r="CF3" s="23"/>
-      <c r="CG3" s="23"/>
-      <c r="CH3" s="23"/>
-    </row>
-    <row r="4" spans="1:86" x14ac:dyDescent="0.15">
-      <c r="A4" s="4" t="s">
+      <c r="B4" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="5" t="s">
         <v>128</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>129</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="F4" s="46" t="s">
-        <v>129</v>
+        <v>128</v>
+      </c>
+      <c r="F4" s="42" t="s">
+        <v>128</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
+      <c r="J4" s="11" t="s">
+        <v>129</v>
+      </c>
       <c r="K4" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="N4" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
+        <v>129</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
       <c r="V4" s="2"/>
       <c r="W4" s="2"/>
-      <c r="X4" s="2"/>
+      <c r="X4" s="2" t="s">
+        <v>130</v>
+      </c>
       <c r="Y4" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Z4" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="AA4" s="2" t="s">
-        <v>131</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="AA4" s="2"/>
       <c r="AB4" s="2"/>
       <c r="AC4" s="2"/>
-      <c r="AD4" s="13"/>
-      <c r="AE4" s="2"/>
-      <c r="AF4" s="15"/>
-      <c r="AG4" s="15"/>
-      <c r="AH4" s="15"/>
-      <c r="AI4" s="15"/>
-      <c r="AJ4" s="15"/>
-      <c r="AK4" s="15"/>
-      <c r="AL4" s="15"/>
-      <c r="AM4" s="15"/>
-      <c r="AN4" s="15"/>
-      <c r="AO4" s="15"/>
-      <c r="AP4" s="15"/>
-      <c r="AQ4" s="15"/>
-      <c r="AR4" s="15"/>
-      <c r="AS4" s="16"/>
-      <c r="AT4" s="16"/>
-      <c r="AU4" s="16"/>
+      <c r="AD4" s="2"/>
+      <c r="AE4" s="14"/>
+      <c r="AF4" s="14"/>
+      <c r="AG4" s="14"/>
+      <c r="AH4" s="14"/>
+      <c r="AI4" s="14"/>
+      <c r="AJ4" s="14"/>
+      <c r="AK4" s="14"/>
+      <c r="AL4" s="14"/>
+      <c r="AM4" s="14"/>
+      <c r="AN4" s="14"/>
+      <c r="AO4" s="14"/>
+      <c r="AP4" s="14"/>
+      <c r="AQ4" s="14"/>
+      <c r="AR4" s="3"/>
+      <c r="AS4" s="3"/>
+      <c r="AT4" s="3"/>
+      <c r="AU4" s="6"/>
       <c r="AV4" s="6"/>
       <c r="AW4" s="6"/>
       <c r="AX4" s="6"/>
       <c r="AY4" s="6"/>
       <c r="AZ4" s="6"/>
       <c r="BA4" s="6"/>
-      <c r="BB4" s="50"/>
+      <c r="BB4" s="6"/>
       <c r="BC4" s="6"/>
       <c r="BD4" s="6"/>
       <c r="BE4" s="6"/>
@@ -2169,286 +2149,282 @@
       <c r="CA4" s="6"/>
       <c r="CB4" s="6"/>
       <c r="CC4" s="6"/>
-      <c r="CD4" s="6"/>
-      <c r="CE4" s="23"/>
-      <c r="CF4" s="23"/>
-      <c r="CG4" s="23"/>
-      <c r="CH4" s="23"/>
+      <c r="CD4" s="20"/>
+      <c r="CE4" s="20"/>
+      <c r="CF4" s="20"/>
+      <c r="CG4" s="20"/>
     </row>
-    <row r="5" spans="1:86" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:85" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="C5" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="F5" s="42" t="s">
         <v>134</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="F5" s="46" t="s">
-        <v>135</v>
-      </c>
       <c r="G5" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="N5" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>133</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>134</v>
       </c>
       <c r="Q5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="V5" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="R5" s="2" t="s">
+      <c r="W5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="AB5" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="S5" s="2" t="s">
+      <c r="AC5" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="T5" s="2" t="s">
+      <c r="AD5" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="U5" s="2" t="s">
+      <c r="AE5" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AF5" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AG5" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="AH5" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AI5" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AJ5" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="AK5" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="AL5" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AM5" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AN5" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="AO5" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="AP5" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="V5" s="2" t="s">
+      <c r="AQ5" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="AR5" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="AS5" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="AT5" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="AU5" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="AV5" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="AW5" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="AX5" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="AY5" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="AZ5" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="BA5" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="W5" s="2" t="s">
+      <c r="BB5" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="BC5" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="BD5" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="X5" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y5" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="Z5" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="AA5" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="AB5" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="AC5" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="AD5" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="AE5" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="AF5" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="AG5" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="AH5" s="20" t="s">
+      <c r="BE5" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="AI5" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="AJ5" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="AK5" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="AL5" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="AM5" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN5" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="AO5" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="AP5" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="AQ5" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="AR5" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="AS5" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="AT5" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="AU5" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="AV5" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="AW5" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="AX5" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="AY5" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="AZ5" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="BA5" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="BB5" s="51" t="s">
-        <v>135</v>
-      </c>
-      <c r="BC5" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="BD5" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="BE5" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="BF5" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="BG5" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="BH5" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="BI5" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="BJ5" s="21" t="s">
-        <v>134</v>
+      <c r="BF5" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="BG5" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="BH5" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="BI5" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="BJ5" s="6" t="s">
+        <v>133</v>
       </c>
       <c r="BK5" s="6" t="s">
         <v>134</v>
       </c>
       <c r="BL5" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="BM5" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="BN5" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="BO5" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="BP5" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="BQ5" s="22" t="s">
-        <v>137</v>
+        <v>134</v>
+      </c>
+      <c r="BM5" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="BN5" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="BO5" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="BP5" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="BQ5" s="6" t="s">
+        <v>134</v>
       </c>
       <c r="BR5" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="BS5" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="BT5" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="BU5" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="BV5" s="6" t="s">
         <v>137</v>
       </c>
       <c r="BW5" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BX5" s="6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="BY5" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="BZ5" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="CA5" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="CB5" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="CC5" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="CD5" s="6" t="s">
+      <c r="CD5" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="CE5" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="CE5" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="CF5" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="CG5" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="CH5" s="23" t="s">
-        <v>134</v>
+      <c r="CF5" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="CG5" s="20" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:86" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:85" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="F6" s="46" t="s">
-        <v>271</v>
+        <v>141</v>
+      </c>
+      <c r="F6" s="42" t="s">
+        <v>269</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
@@ -2457,12 +2433,12 @@
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
       <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
+      <c r="N6" s="2"/>
       <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2" t="s">
-        <v>143</v>
-      </c>
+      <c r="P6" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
@@ -2473,43 +2449,43 @@
       <c r="Y6" s="2"/>
       <c r="Z6" s="2"/>
       <c r="AA6" s="2"/>
-      <c r="AB6" s="2"/>
+      <c r="AB6" s="2" t="s">
+        <v>143</v>
+      </c>
       <c r="AC6" s="2" t="s">
         <v>144</v>
       </c>
       <c r="AD6" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="AE6" s="2" t="s">
+      <c r="AE6" s="14"/>
+      <c r="AF6" s="14"/>
+      <c r="AG6" s="14"/>
+      <c r="AH6" s="14"/>
+      <c r="AI6" s="14"/>
+      <c r="AJ6" s="14"/>
+      <c r="AK6" s="14"/>
+      <c r="AL6" s="14"/>
+      <c r="AM6" s="14"/>
+      <c r="AN6" s="14"/>
+      <c r="AO6" s="14"/>
+      <c r="AP6" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="AF6" s="20"/>
-      <c r="AG6" s="20"/>
-      <c r="AH6" s="20"/>
-      <c r="AI6" s="20"/>
-      <c r="AJ6" s="20"/>
-      <c r="AK6" s="20"/>
-      <c r="AL6" s="20"/>
-      <c r="AM6" s="20"/>
-      <c r="AN6" s="20"/>
-      <c r="AO6" s="20"/>
-      <c r="AP6" s="20"/>
-      <c r="AQ6" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="AR6" s="20"/>
+      <c r="AQ6" s="14"/>
+      <c r="AR6" s="3"/>
       <c r="AS6" s="3"/>
       <c r="AT6" s="3"/>
-      <c r="AU6" s="3"/>
+      <c r="AU6" s="6"/>
       <c r="AV6" s="6"/>
       <c r="AW6" s="6"/>
       <c r="AX6" s="6"/>
       <c r="AY6" s="6"/>
       <c r="AZ6" s="6"/>
-      <c r="BA6" s="6"/>
-      <c r="BB6" s="51" t="s">
-        <v>277</v>
-      </c>
+      <c r="BA6" s="44" t="s">
+        <v>275</v>
+      </c>
+      <c r="BB6" s="6"/>
       <c r="BC6" s="6"/>
       <c r="BD6" s="6"/>
       <c r="BE6" s="6"/>
@@ -2518,478 +2494,476 @@
       <c r="BH6" s="6"/>
       <c r="BI6" s="6"/>
       <c r="BJ6" s="6"/>
-      <c r="BK6" s="6"/>
+      <c r="BK6" s="6" t="s">
+        <v>147</v>
+      </c>
       <c r="BL6" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="BM6" s="6" t="s">
-        <v>149</v>
-      </c>
+      <c r="BM6" s="6"/>
       <c r="BN6" s="6"/>
       <c r="BO6" s="6"/>
       <c r="BP6" s="6"/>
-      <c r="BQ6" s="6"/>
-      <c r="BR6" s="6" t="s">
-        <v>150</v>
-      </c>
+      <c r="BQ6" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="BR6" s="6"/>
       <c r="BS6" s="6"/>
       <c r="BT6" s="6"/>
       <c r="BU6" s="6"/>
       <c r="BV6" s="6"/>
       <c r="BW6" s="6"/>
-      <c r="BX6" s="6"/>
+      <c r="BX6" s="6" t="s">
+        <v>150</v>
+      </c>
       <c r="BY6" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="BZ6" s="6" t="s">
-        <v>152</v>
-      </c>
+      <c r="BZ6" s="6"/>
       <c r="CA6" s="6"/>
       <c r="CB6" s="6"/>
-      <c r="CC6" s="6"/>
-      <c r="CD6" s="6" t="s">
+      <c r="CC6" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="CD6" s="20"/>
+      <c r="CE6" s="20"/>
+      <c r="CF6" s="20"/>
+      <c r="CG6" s="20"/>
+    </row>
+    <row r="7" spans="1:85" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="39" t="s">
+        <v>259</v>
+      </c>
+      <c r="B7" s="40" t="s">
+        <v>260</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="CE6" s="23"/>
-      <c r="CF6" s="23"/>
-      <c r="CG6" s="23"/>
-      <c r="CH6" s="23"/>
+      <c r="D7" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="F7" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I7" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="N7" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="O7" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="P7" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="X7" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y7" s="22" t="s">
+        <v>174</v>
+      </c>
+      <c r="Z7" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="AB7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AC7" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="AD7" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="AE7" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="AF7" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="AG7" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="AH7" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="AI7" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="AJ7" s="23" t="s">
+        <v>185</v>
+      </c>
+      <c r="AK7" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="AL7" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="AM7" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="AN7" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="AO7" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="AP7" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="AQ7" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="AR7" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="AS7" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="AT7" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="AU7" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="AV7" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="AW7" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="AX7" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="AY7" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="AZ7" s="25" t="s">
+        <v>201</v>
+      </c>
+      <c r="BA7" s="25" t="s">
+        <v>276</v>
+      </c>
+      <c r="BB7" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="BC7" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="BD7" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="BE7" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF7" s="25" t="s">
+        <v>205</v>
+      </c>
+      <c r="BG7" s="25" t="s">
+        <v>206</v>
+      </c>
+      <c r="BH7" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="BI7" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="BJ7" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="BK7" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="BL7" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="BM7" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="BN7" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="BO7" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="BP7" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="BQ7" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="BR7" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="BS7" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="BT7" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="BU7" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="BV7" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="BW7" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="BX7" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="BY7" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="BZ7" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="CA7" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="CB7" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="CC7" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="CD7" s="25" t="s">
+        <v>229</v>
+      </c>
+      <c r="CE7" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="CF7" s="25" t="s">
+        <v>231</v>
+      </c>
+      <c r="CG7" s="25" t="s">
+        <v>232</v>
+      </c>
     </row>
-    <row r="7" spans="1:86" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="43" t="s">
+    <row r="8" spans="1:85" ht="17" x14ac:dyDescent="0.2">
+      <c r="A8" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="B7" s="44" t="s">
+      <c r="B8" s="41" t="s">
         <v>262</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="F7" s="46" t="s">
+      <c r="C8" s="25" t="s">
+        <v>240</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>255</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>233</v>
+      </c>
+      <c r="F8" s="25" t="s">
         <v>272</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="I7" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="K7" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="N7" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="O7" s="25" t="s">
-        <v>165</v>
-      </c>
-      <c r="P7" s="25" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q7" s="25" t="s">
-        <v>167</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="X7" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y7" s="25" t="s">
-        <v>175</v>
-      </c>
-      <c r="Z7" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="AA7" s="25" t="s">
-        <v>177</v>
-      </c>
-      <c r="AB7" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="AC7" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="AD7" s="25" t="s">
-        <v>180</v>
-      </c>
-      <c r="AE7" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="AF7" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="AG7" s="26" t="s">
-        <v>183</v>
-      </c>
-      <c r="AH7" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="AI7" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="AJ7" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="AK7" s="26" t="s">
-        <v>187</v>
-      </c>
-      <c r="AL7" s="26" t="s">
-        <v>188</v>
-      </c>
-      <c r="AM7" s="26" t="s">
-        <v>189</v>
-      </c>
-      <c r="AN7" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="AO7" s="26" t="s">
-        <v>191</v>
-      </c>
-      <c r="AP7" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="AQ7" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="AR7" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="AS7" s="28" t="s">
-        <v>195</v>
-      </c>
-      <c r="AT7" s="28" t="s">
-        <v>196</v>
-      </c>
-      <c r="AU7" s="28" t="s">
-        <v>197</v>
-      </c>
-      <c r="AV7" s="28" t="s">
-        <v>198</v>
-      </c>
-      <c r="AW7" s="28" t="s">
-        <v>199</v>
-      </c>
-      <c r="AX7" s="6" t="s">
+      <c r="H8" s="38"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="25" t="s">
+        <v>263</v>
+      </c>
+      <c r="K8" s="25"/>
+      <c r="L8" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="M8" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="N8" s="25" t="s">
+        <v>234</v>
+      </c>
+      <c r="O8" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="P8" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q8" s="25" t="s">
+        <v>236</v>
+      </c>
+      <c r="R8" s="26"/>
+      <c r="S8" s="26"/>
+      <c r="T8" s="27"/>
+      <c r="U8" s="27"/>
+      <c r="V8" s="31">
+        <v>44177</v>
+      </c>
+      <c r="W8" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="X8" s="26">
+        <v>2.169024E-2</v>
+      </c>
+      <c r="Y8" s="26">
+        <v>2.169024E-2</v>
+      </c>
+      <c r="Z8" s="26">
+        <v>2.169024E-2</v>
+      </c>
+      <c r="AA8" s="26">
+        <v>8</v>
+      </c>
+      <c r="AB8" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC8" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="AD8" s="30"/>
+      <c r="AE8" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="AF8" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="AG8" s="31">
+        <v>44177</v>
+      </c>
+      <c r="AH8" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="AI8" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="AJ8" s="25">
+        <v>88</v>
+      </c>
+      <c r="AK8" s="25">
+        <v>88</v>
+      </c>
+      <c r="AL8" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="AM8" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="AN8" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="AO8" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="AP8" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="AQ8" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="AR8" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="AS8" s="25" t="s">
+        <v>245</v>
+      </c>
+      <c r="AT8" s="25"/>
+      <c r="AU8" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="AV8" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="AW8" s="34" t="s">
+        <v>247</v>
+      </c>
+      <c r="AX8" s="35">
+        <v>44500</v>
+      </c>
+      <c r="AY8" s="26">
+        <v>0.200098</v>
+      </c>
+      <c r="AZ8" s="25" t="s">
+        <v>239</v>
+      </c>
+      <c r="BA8" s="25" t="s">
+        <v>277</v>
+      </c>
+      <c r="BB8" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="BC8">
+        <v>888</v>
+      </c>
+      <c r="BD8" s="26">
+        <v>3</v>
+      </c>
+      <c r="BE8" s="26">
+        <v>1680</v>
+      </c>
+      <c r="BF8" s="26">
+        <v>70</v>
+      </c>
+      <c r="BG8" s="26">
+        <v>1.4E-2</v>
+      </c>
+      <c r="BH8" s="26">
         <v>200</v>
       </c>
-      <c r="AY7" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="AZ7" s="28" t="s">
-        <v>202</v>
-      </c>
-      <c r="BA7" s="28" t="s">
-        <v>203</v>
-      </c>
-      <c r="BB7" s="49" t="s">
-        <v>278</v>
-      </c>
-      <c r="BC7" s="28" t="s">
-        <v>204</v>
-      </c>
-      <c r="BD7" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="BE7" s="28" t="s">
-        <v>205</v>
-      </c>
-      <c r="BF7" s="28" t="s">
-        <v>206</v>
-      </c>
-      <c r="BG7" s="28" t="s">
-        <v>207</v>
-      </c>
-      <c r="BH7" s="28" t="s">
-        <v>208</v>
-      </c>
-      <c r="BI7" s="28" t="s">
-        <v>209</v>
-      </c>
-      <c r="BJ7" s="28" t="s">
-        <v>210</v>
-      </c>
-      <c r="BK7" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="BL7" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="BM7" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="BN7" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="BO7" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="BP7" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="BQ7" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="BR7" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="BS7" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="BT7" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="BU7" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="BV7" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="BW7" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="BX7" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="BY7" s="27" t="s">
-        <v>225</v>
-      </c>
-      <c r="BZ7" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="CA7" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="CB7" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="CC7" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="CD7" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="CE7" s="28" t="s">
-        <v>231</v>
-      </c>
-      <c r="CF7" s="28" t="s">
-        <v>232</v>
-      </c>
-      <c r="CG7" s="28" t="s">
-        <v>233</v>
-      </c>
-      <c r="CH7" s="28" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="8" spans="1:86" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="43" t="s">
-        <v>263</v>
-      </c>
-      <c r="B8" s="45" t="s">
-        <v>264</v>
-      </c>
-      <c r="C8" s="28" t="s">
-        <v>242</v>
-      </c>
-      <c r="D8" s="40" t="s">
-        <v>257</v>
-      </c>
-      <c r="E8" s="28" t="s">
-        <v>235</v>
-      </c>
-      <c r="F8" s="49" t="s">
-        <v>274</v>
-      </c>
-      <c r="H8" s="42"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28" t="s">
-        <v>265</v>
-      </c>
-      <c r="L8" s="28"/>
-      <c r="M8" s="34" t="s">
-        <v>266</v>
-      </c>
-      <c r="N8" s="34" t="s">
-        <v>267</v>
-      </c>
-      <c r="O8" s="28" t="s">
-        <v>236</v>
-      </c>
-      <c r="P8" s="28" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q8" s="34" t="s">
-        <v>243</v>
-      </c>
-      <c r="R8" s="28" t="s">
-        <v>238</v>
-      </c>
-      <c r="S8" s="29"/>
-      <c r="T8" s="29"/>
-      <c r="U8" s="30"/>
-      <c r="V8" s="30"/>
-      <c r="W8" s="35">
-        <v>44177</v>
-      </c>
-      <c r="X8" s="41" t="s">
-        <v>258</v>
-      </c>
-      <c r="Y8" s="29">
-        <v>2.169024E-2</v>
-      </c>
-      <c r="Z8" s="29">
-        <v>2.169024E-2</v>
-      </c>
-      <c r="AA8" s="29">
-        <v>2.169024E-2</v>
-      </c>
-      <c r="AB8" s="29">
-        <v>8</v>
-      </c>
-      <c r="AC8" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="AD8" s="28" t="s">
-        <v>239</v>
-      </c>
-      <c r="AE8" s="34"/>
-      <c r="AF8" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="AG8" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="AH8" s="35">
-        <v>44177</v>
-      </c>
-      <c r="AI8" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="AJ8" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="AK8" s="28">
+      <c r="BI8" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="BJ8" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="BK8" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="BL8" s="25" t="s">
+        <v>249</v>
+      </c>
+      <c r="BM8" s="25">
         <v>88</v>
       </c>
-      <c r="AL8" s="28">
-        <v>88</v>
-      </c>
-      <c r="AM8" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="AN8" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="AO8" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="AP8" s="34" t="s">
-        <v>240</v>
-      </c>
-      <c r="AQ8" s="36" t="s">
-        <v>244</v>
-      </c>
-      <c r="AR8" s="28" t="s">
-        <v>240</v>
-      </c>
-      <c r="AS8" s="28" t="s">
-        <v>246</v>
-      </c>
-      <c r="AT8" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="AU8" s="28"/>
-      <c r="AV8" s="34" t="s">
-        <v>248</v>
-      </c>
-      <c r="AW8" s="28" t="s">
-        <v>275</v>
-      </c>
-      <c r="AX8" s="38" t="s">
-        <v>249</v>
-      </c>
-      <c r="AY8" s="39">
-        <v>44500</v>
-      </c>
-      <c r="AZ8" s="29">
-        <v>0.200098</v>
-      </c>
-      <c r="BA8" s="28" t="s">
-        <v>241</v>
-      </c>
-      <c r="BB8" s="49" t="s">
-        <v>279</v>
-      </c>
-      <c r="BC8" s="28" t="s">
-        <v>240</v>
-      </c>
-      <c r="BD8">
-        <v>888</v>
-      </c>
-      <c r="BE8" s="29">
-        <v>3</v>
-      </c>
-      <c r="BF8" s="29">
-        <v>1680</v>
-      </c>
-      <c r="BG8" s="29">
-        <v>70</v>
-      </c>
-      <c r="BH8" s="29">
-        <v>1.4E-2</v>
-      </c>
-      <c r="BI8" s="29">
-        <v>200</v>
-      </c>
-      <c r="BJ8" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="BK8" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="BL8" s="34" t="s">
-        <v>250</v>
-      </c>
-      <c r="BM8" s="28" t="s">
-        <v>251</v>
-      </c>
-      <c r="BN8" s="28">
-        <v>88</v>
+      <c r="BN8">
+        <v>1</v>
       </c>
       <c r="BO8">
         <v>1</v>
@@ -2997,392 +2971,388 @@
       <c r="BP8">
         <v>1</v>
       </c>
-      <c r="BQ8">
+      <c r="BQ8" t="s">
+        <v>251</v>
+      </c>
+      <c r="BR8" t="s">
+        <v>250</v>
+      </c>
+      <c r="BS8" t="s">
+        <v>250</v>
+      </c>
+      <c r="BT8" t="s">
+        <v>250</v>
+      </c>
+      <c r="BU8">
+        <v>88</v>
+      </c>
+      <c r="BV8" t="s">
+        <v>238</v>
+      </c>
+      <c r="BW8" t="s">
+        <v>238</v>
+      </c>
+      <c r="BX8" s="25" t="s">
+        <v>252</v>
+      </c>
+      <c r="BY8" s="30"/>
+      <c r="BZ8" s="30"/>
+      <c r="CA8" s="30"/>
+      <c r="CB8" s="30"/>
+      <c r="CC8" s="30"/>
+      <c r="CD8" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="CE8" s="31">
+        <v>44500</v>
+      </c>
+      <c r="CF8" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="CG8" s="30" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="9" spans="1:85" ht="17" x14ac:dyDescent="0.2">
+      <c r="B9" s="33"/>
+      <c r="C9" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>255</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>233</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>271</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>240</v>
+      </c>
+      <c r="H9" s="38"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="N9" s="25" t="s">
+        <v>234</v>
+      </c>
+      <c r="O9" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q9" s="25" t="s">
+        <v>236</v>
+      </c>
+      <c r="R9" s="26"/>
+      <c r="S9" s="26"/>
+      <c r="T9" s="28"/>
+      <c r="U9" s="28"/>
+      <c r="V9" s="31">
+        <v>44177</v>
+      </c>
+      <c r="W9" s="28"/>
+      <c r="X9" s="26">
+        <v>2.725352E-2</v>
+      </c>
+      <c r="Y9" s="26">
+        <v>2.725352E-2</v>
+      </c>
+      <c r="Z9" s="26">
+        <v>2.725352E-2</v>
+      </c>
+      <c r="AA9" s="26">
+        <v>8</v>
+      </c>
+      <c r="AB9" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC9" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="AD9" s="30"/>
+      <c r="AE9" s="25"/>
+      <c r="AF9" s="25"/>
+      <c r="AG9" s="25"/>
+      <c r="AH9" s="25"/>
+      <c r="AI9" s="25"/>
+      <c r="AJ9" s="25"/>
+      <c r="AK9" s="25"/>
+      <c r="AL9" s="25"/>
+      <c r="AM9" s="25"/>
+      <c r="AN9" s="25"/>
+      <c r="AO9" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="AP9" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="AQ9" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="AR9" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="AS9" s="25" t="s">
+        <v>245</v>
+      </c>
+      <c r="AT9" s="25"/>
+      <c r="AU9" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="AV9" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="AW9" s="34" t="s">
+        <v>247</v>
+      </c>
+      <c r="AX9" s="35">
+        <v>44501</v>
+      </c>
+      <c r="AY9" s="26">
+        <v>0.200098</v>
+      </c>
+      <c r="AZ9" s="25" t="s">
+        <v>239</v>
+      </c>
+      <c r="BA9" s="25" t="s">
+        <v>277</v>
+      </c>
+      <c r="BB9" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="BC9">
+        <v>888</v>
+      </c>
+      <c r="BD9" s="26">
+        <v>3</v>
+      </c>
+      <c r="BE9" s="26">
+        <v>1680</v>
+      </c>
+      <c r="BF9" s="26">
+        <v>70</v>
+      </c>
+      <c r="BG9" s="26">
+        <v>1.54E-2</v>
+      </c>
+      <c r="BH9" s="26">
+        <v>220</v>
+      </c>
+      <c r="BI9" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="BJ9" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="BK9" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="BL9" s="25" t="s">
+        <v>249</v>
+      </c>
+      <c r="BM9" s="25">
+        <v>89</v>
+      </c>
+      <c r="BQ9" t="s">
+        <v>251</v>
+      </c>
+      <c r="BR9" t="s">
+        <v>250</v>
+      </c>
+      <c r="BS9" t="s">
+        <v>250</v>
+      </c>
+      <c r="BT9" t="s">
+        <v>250</v>
+      </c>
+      <c r="BU9">
+        <v>89</v>
+      </c>
+      <c r="BV9" t="s">
+        <v>238</v>
+      </c>
+      <c r="BW9" t="s">
+        <v>238</v>
+      </c>
+      <c r="BX9" s="25" t="s">
+        <v>252</v>
+      </c>
+      <c r="BY9" s="30"/>
+      <c r="BZ9" s="30"/>
+      <c r="CA9" s="30"/>
+      <c r="CB9" s="30"/>
+      <c r="CC9" s="30"/>
+      <c r="CD9" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="CE9" s="31">
+        <v>44501</v>
+      </c>
+      <c r="CF9" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="CG9" s="30" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="10" spans="1:85" ht="17" x14ac:dyDescent="0.2">
+      <c r="C10" s="25" t="s">
+        <v>240</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>255</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>233</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>271</v>
+      </c>
+      <c r="H10" s="38"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="M10" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="N10" s="25" t="s">
+        <v>234</v>
+      </c>
+      <c r="O10" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="P10" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q10" s="25" t="s">
+        <v>236</v>
+      </c>
+      <c r="R10" s="26"/>
+      <c r="S10" s="26"/>
+      <c r="T10" s="27"/>
+      <c r="U10" s="27"/>
+      <c r="V10" s="31">
+        <v>44177</v>
+      </c>
+      <c r="W10" s="27"/>
+      <c r="X10" s="26">
+        <v>2.169024E-2</v>
+      </c>
+      <c r="Y10" s="26">
+        <v>2.169024E-2</v>
+      </c>
+      <c r="Z10" s="26">
+        <v>2.169024E-2</v>
+      </c>
+      <c r="AA10" s="26">
+        <v>8</v>
+      </c>
+      <c r="AB10" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC10" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="AD10" s="30"/>
+      <c r="AE10" s="25"/>
+      <c r="AF10" s="25"/>
+      <c r="AG10" s="31">
+        <v>44177</v>
+      </c>
+      <c r="AH10" s="25"/>
+      <c r="AI10" s="25"/>
+      <c r="AJ10" s="25"/>
+      <c r="AK10" s="25"/>
+      <c r="AL10" s="25"/>
+      <c r="AM10" s="25"/>
+      <c r="AN10" s="25"/>
+      <c r="AO10" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="AP10" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="AQ10" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="AR10" s="25" t="s">
+        <v>257</v>
+      </c>
+      <c r="AS10" s="25" t="s">
+        <v>258</v>
+      </c>
+      <c r="AT10" s="25"/>
+      <c r="AU10" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="AV10" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="AW10" s="34" t="s">
+        <v>247</v>
+      </c>
+      <c r="AX10" s="35">
+        <v>44502</v>
+      </c>
+      <c r="AY10" s="26">
+        <v>0.200098</v>
+      </c>
+      <c r="AZ10" s="25" t="s">
+        <v>239</v>
+      </c>
+      <c r="BA10" s="25" t="s">
+        <v>277</v>
+      </c>
+      <c r="BB10" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="BC10">
+        <v>888</v>
+      </c>
+      <c r="BD10" s="26">
+        <v>3</v>
+      </c>
+      <c r="BE10" s="26">
+        <v>1680</v>
+      </c>
+      <c r="BF10" s="26">
+        <v>70</v>
+      </c>
+      <c r="BG10" s="26">
+        <v>1.4E-2</v>
+      </c>
+      <c r="BH10" s="26">
+        <v>200</v>
+      </c>
+      <c r="BI10" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="BJ10" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="BK10" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="BL10" s="25" t="s">
+        <v>249</v>
+      </c>
+      <c r="BM10" s="25">
+        <v>90</v>
+      </c>
+      <c r="BN10">
         <v>1</v>
-      </c>
-      <c r="BR8" t="s">
-        <v>253</v>
-      </c>
-      <c r="BS8" t="s">
-        <v>252</v>
-      </c>
-      <c r="BT8" t="s">
-        <v>252</v>
-      </c>
-      <c r="BU8" t="s">
-        <v>252</v>
-      </c>
-      <c r="BV8">
-        <v>88</v>
-      </c>
-      <c r="BW8" t="s">
-        <v>240</v>
-      </c>
-      <c r="BX8" t="s">
-        <v>240</v>
-      </c>
-      <c r="BY8" s="28" t="s">
-        <v>254</v>
-      </c>
-      <c r="BZ8" s="34"/>
-      <c r="CA8" s="34"/>
-      <c r="CB8" s="34"/>
-      <c r="CC8" s="34"/>
-      <c r="CD8" s="34"/>
-      <c r="CE8" s="28" t="s">
-        <v>275</v>
-      </c>
-      <c r="CF8" s="35">
-        <v>44500</v>
-      </c>
-      <c r="CG8" s="34" t="s">
-        <v>255</v>
-      </c>
-      <c r="CH8" s="34" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="9" spans="1:86" ht="17" x14ac:dyDescent="0.2">
-      <c r="A9" s="32"/>
-      <c r="B9" s="37"/>
-      <c r="C9" s="34" t="s">
-        <v>245</v>
-      </c>
-      <c r="D9" s="40" t="s">
-        <v>257</v>
-      </c>
-      <c r="E9" s="28" t="s">
-        <v>235</v>
-      </c>
-      <c r="F9" s="49" t="s">
-        <v>273</v>
-      </c>
-      <c r="G9" s="28" t="s">
-        <v>242</v>
-      </c>
-      <c r="H9" s="42"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="28"/>
-      <c r="M9" s="34" t="s">
-        <v>266</v>
-      </c>
-      <c r="N9" s="34" t="s">
-        <v>267</v>
-      </c>
-      <c r="O9" s="28" t="s">
-        <v>236</v>
-      </c>
-      <c r="P9" s="28" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q9" s="34" t="s">
-        <v>243</v>
-      </c>
-      <c r="R9" s="28" t="s">
-        <v>238</v>
-      </c>
-      <c r="S9" s="29"/>
-      <c r="T9" s="29"/>
-      <c r="U9" s="31"/>
-      <c r="V9" s="31"/>
-      <c r="W9" s="35">
-        <v>44177</v>
-      </c>
-      <c r="X9" s="31"/>
-      <c r="Y9" s="29">
-        <v>2.725352E-2</v>
-      </c>
-      <c r="Z9" s="29">
-        <v>2.725352E-2</v>
-      </c>
-      <c r="AA9" s="29">
-        <v>2.725352E-2</v>
-      </c>
-      <c r="AB9" s="29">
-        <v>8</v>
-      </c>
-      <c r="AC9" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="AD9" s="28" t="s">
-        <v>239</v>
-      </c>
-      <c r="AE9" s="34"/>
-      <c r="AF9" s="28"/>
-      <c r="AG9" s="28"/>
-      <c r="AH9" s="28"/>
-      <c r="AI9" s="28"/>
-      <c r="AJ9" s="28"/>
-      <c r="AK9" s="28"/>
-      <c r="AL9" s="28"/>
-      <c r="AM9" s="28"/>
-      <c r="AN9" s="28"/>
-      <c r="AO9" s="28"/>
-      <c r="AP9" s="34" t="s">
-        <v>240</v>
-      </c>
-      <c r="AQ9" s="36" t="s">
-        <v>244</v>
-      </c>
-      <c r="AR9" s="28" t="s">
-        <v>240</v>
-      </c>
-      <c r="AS9" s="28" t="s">
-        <v>246</v>
-      </c>
-      <c r="AT9" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="AU9" s="28"/>
-      <c r="AV9" s="34" t="s">
-        <v>248</v>
-      </c>
-      <c r="AW9" s="28" t="s">
-        <v>275</v>
-      </c>
-      <c r="AX9" s="38" t="s">
-        <v>249</v>
-      </c>
-      <c r="AY9" s="39">
-        <v>44501</v>
-      </c>
-      <c r="AZ9" s="29">
-        <v>0.200098</v>
-      </c>
-      <c r="BA9" s="28" t="s">
-        <v>241</v>
-      </c>
-      <c r="BB9" s="49" t="s">
-        <v>279</v>
-      </c>
-      <c r="BC9" s="28" t="s">
-        <v>240</v>
-      </c>
-      <c r="BD9">
-        <v>888</v>
-      </c>
-      <c r="BE9" s="29">
-        <v>3</v>
-      </c>
-      <c r="BF9" s="29">
-        <v>1680</v>
-      </c>
-      <c r="BG9" s="29">
-        <v>70</v>
-      </c>
-      <c r="BH9" s="29">
-        <v>1.54E-2</v>
-      </c>
-      <c r="BI9" s="29">
-        <v>220</v>
-      </c>
-      <c r="BJ9" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="BK9" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="BL9" s="34" t="s">
-        <v>250</v>
-      </c>
-      <c r="BM9" s="28" t="s">
-        <v>251</v>
-      </c>
-      <c r="BN9" s="28">
-        <v>89</v>
-      </c>
-      <c r="BR9" t="s">
-        <v>253</v>
-      </c>
-      <c r="BS9" t="s">
-        <v>252</v>
-      </c>
-      <c r="BT9" t="s">
-        <v>252</v>
-      </c>
-      <c r="BU9" t="s">
-        <v>252</v>
-      </c>
-      <c r="BV9">
-        <v>89</v>
-      </c>
-      <c r="BW9" t="s">
-        <v>240</v>
-      </c>
-      <c r="BX9" t="s">
-        <v>240</v>
-      </c>
-      <c r="BY9" s="28" t="s">
-        <v>254</v>
-      </c>
-      <c r="BZ9" s="34"/>
-      <c r="CA9" s="34"/>
-      <c r="CB9" s="34"/>
-      <c r="CC9" s="34"/>
-      <c r="CD9" s="34"/>
-      <c r="CE9" s="28" t="s">
-        <v>275</v>
-      </c>
-      <c r="CF9" s="35">
-        <v>44501</v>
-      </c>
-      <c r="CG9" s="34" t="s">
-        <v>255</v>
-      </c>
-      <c r="CH9" s="34" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="10" spans="1:86" ht="17" x14ac:dyDescent="0.2">
-      <c r="A10" s="32"/>
-      <c r="B10" s="32"/>
-      <c r="C10" s="28" t="s">
-        <v>242</v>
-      </c>
-      <c r="D10" s="40" t="s">
-        <v>257</v>
-      </c>
-      <c r="E10" s="28" t="s">
-        <v>235</v>
-      </c>
-      <c r="F10" s="49" t="s">
-        <v>273</v>
-      </c>
-      <c r="H10" s="42"/>
-      <c r="I10" s="33"/>
-      <c r="K10" s="28"/>
-      <c r="L10" s="28"/>
-      <c r="M10" s="34" t="s">
-        <v>266</v>
-      </c>
-      <c r="N10" s="34" t="s">
-        <v>267</v>
-      </c>
-      <c r="O10" s="28" t="s">
-        <v>236</v>
-      </c>
-      <c r="P10" s="28" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q10" s="34" t="s">
-        <v>243</v>
-      </c>
-      <c r="R10" s="28" t="s">
-        <v>238</v>
-      </c>
-      <c r="S10" s="29"/>
-      <c r="T10" s="29"/>
-      <c r="U10" s="30"/>
-      <c r="V10" s="30"/>
-      <c r="W10" s="35">
-        <v>44177</v>
-      </c>
-      <c r="X10" s="30"/>
-      <c r="Y10" s="29">
-        <v>2.169024E-2</v>
-      </c>
-      <c r="Z10" s="29">
-        <v>2.169024E-2</v>
-      </c>
-      <c r="AA10" s="29">
-        <v>2.169024E-2</v>
-      </c>
-      <c r="AB10" s="29">
-        <v>8</v>
-      </c>
-      <c r="AC10" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="AD10" s="28" t="s">
-        <v>239</v>
-      </c>
-      <c r="AE10" s="34"/>
-      <c r="AF10" s="28"/>
-      <c r="AG10" s="28"/>
-      <c r="AH10" s="35">
-        <v>44177</v>
-      </c>
-      <c r="AI10" s="28"/>
-      <c r="AJ10" s="28"/>
-      <c r="AK10" s="28"/>
-      <c r="AL10" s="28"/>
-      <c r="AM10" s="28"/>
-      <c r="AN10" s="28"/>
-      <c r="AO10" s="28"/>
-      <c r="AP10" s="34" t="s">
-        <v>240</v>
-      </c>
-      <c r="AQ10" s="36" t="s">
-        <v>244</v>
-      </c>
-      <c r="AR10" s="28" t="s">
-        <v>240</v>
-      </c>
-      <c r="AS10" s="28" t="s">
-        <v>259</v>
-      </c>
-      <c r="AT10" s="28" t="s">
-        <v>260</v>
-      </c>
-      <c r="AU10" s="28"/>
-      <c r="AV10" s="34" t="s">
-        <v>248</v>
-      </c>
-      <c r="AW10" s="28" t="s">
-        <v>275</v>
-      </c>
-      <c r="AX10" s="38" t="s">
-        <v>249</v>
-      </c>
-      <c r="AY10" s="39">
-        <v>44502</v>
-      </c>
-      <c r="AZ10" s="29">
-        <v>0.200098</v>
-      </c>
-      <c r="BA10" s="28" t="s">
-        <v>241</v>
-      </c>
-      <c r="BB10" s="49" t="s">
-        <v>279</v>
-      </c>
-      <c r="BC10" s="28" t="s">
-        <v>240</v>
-      </c>
-      <c r="BD10">
-        <v>888</v>
-      </c>
-      <c r="BE10" s="29">
-        <v>3</v>
-      </c>
-      <c r="BF10" s="29">
-        <v>1680</v>
-      </c>
-      <c r="BG10" s="29">
-        <v>70</v>
-      </c>
-      <c r="BH10" s="29">
-        <v>1.4E-2</v>
-      </c>
-      <c r="BI10" s="29">
-        <v>200</v>
-      </c>
-      <c r="BJ10" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="BK10" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="BL10" s="34" t="s">
-        <v>250</v>
-      </c>
-      <c r="BM10" s="28" t="s">
-        <v>251</v>
-      </c>
-      <c r="BN10" s="28">
-        <v>90</v>
       </c>
       <c r="BO10">
         <v>1</v>
@@ -3390,49 +3360,46 @@
       <c r="BP10">
         <v>1</v>
       </c>
-      <c r="BQ10">
-        <v>1</v>
+      <c r="BQ10" t="s">
+        <v>251</v>
       </c>
       <c r="BR10" t="s">
+        <v>250</v>
+      </c>
+      <c r="BS10" t="s">
+        <v>250</v>
+      </c>
+      <c r="BT10" t="s">
+        <v>250</v>
+      </c>
+      <c r="BU10">
+        <v>90</v>
+      </c>
+      <c r="BV10" t="s">
+        <v>238</v>
+      </c>
+      <c r="BW10" t="s">
+        <v>238</v>
+      </c>
+      <c r="BX10" s="25" t="s">
+        <v>252</v>
+      </c>
+      <c r="BY10" s="30"/>
+      <c r="BZ10" s="30"/>
+      <c r="CA10" s="30"/>
+      <c r="CB10" s="30"/>
+      <c r="CC10" s="30"/>
+      <c r="CD10" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="CE10" s="31">
+        <v>44502</v>
+      </c>
+      <c r="CF10" s="30" t="s">
         <v>253</v>
       </c>
-      <c r="BS10" t="s">
-        <v>252</v>
-      </c>
-      <c r="BT10" t="s">
-        <v>252</v>
-      </c>
-      <c r="BU10" t="s">
-        <v>252</v>
-      </c>
-      <c r="BV10">
-        <v>90</v>
-      </c>
-      <c r="BW10" t="s">
-        <v>240</v>
-      </c>
-      <c r="BX10" t="s">
-        <v>240</v>
-      </c>
-      <c r="BY10" s="28" t="s">
+      <c r="CG10" s="30" t="s">
         <v>254</v>
-      </c>
-      <c r="BZ10" s="34"/>
-      <c r="CA10" s="34"/>
-      <c r="CB10" s="34"/>
-      <c r="CC10" s="34"/>
-      <c r="CD10" s="34"/>
-      <c r="CE10" s="28" t="s">
-        <v>275</v>
-      </c>
-      <c r="CF10" s="35">
-        <v>44502</v>
-      </c>
-      <c r="CG10" s="34" t="s">
-        <v>255</v>
-      </c>
-      <c r="CH10" s="34" t="s">
-        <v>256</v>
       </c>
     </row>
   </sheetData>
